--- a/zafarabad.xlsx
+++ b/zafarabad.xlsx
@@ -16,48 +16,96 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
-  <si>
-    <t>YT8853710649004</t>
-  </si>
-  <si>
-    <t>YT8853750051669</t>
-  </si>
-  <si>
-    <t>JT5470609785165</t>
-  </si>
-  <si>
-    <t>YT7611861643639</t>
-  </si>
-  <si>
-    <t>JT5470655322014</t>
-  </si>
-  <si>
-    <t>JT5470765271182</t>
-  </si>
-  <si>
-    <t>YT8853209009683</t>
-  </si>
-  <si>
-    <t>JT5469769935052</t>
-  </si>
-  <si>
-    <t>YT8854297254274</t>
-  </si>
-  <si>
-    <t>JT5470477898072</t>
-  </si>
-  <si>
-    <t>981515578846:</t>
-  </si>
-  <si>
-    <t>YT8853758485251</t>
-  </si>
-  <si>
-    <t>SF1571242718187</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="30">
   <si>
     <t>Track</t>
+  </si>
+  <si>
+    <t>ROHILA</t>
+  </si>
+  <si>
+    <t>NIGORA</t>
+  </si>
+  <si>
+    <t>ANVAR</t>
+  </si>
+  <si>
+    <t>KIBRIYO</t>
+  </si>
+  <si>
+    <t>JT5498044681933</t>
+  </si>
+  <si>
+    <t>YT8880292978538</t>
+  </si>
+  <si>
+    <t>JT5498130519084</t>
+  </si>
+  <si>
+    <t>ALISHER</t>
+  </si>
+  <si>
+    <t>YT8880510987456</t>
+  </si>
+  <si>
+    <t>SAID</t>
+  </si>
+  <si>
+    <t>PARVINA</t>
+  </si>
+  <si>
+    <t>YT7628954567668</t>
+  </si>
+  <si>
+    <t>YT8879913736413</t>
+  </si>
+  <si>
+    <t>YT8879882443578</t>
+  </si>
+  <si>
+    <t>JT9001972082680</t>
+  </si>
+  <si>
+    <t>JT5498569535322</t>
+  </si>
+  <si>
+    <t>JT5498684503822</t>
+  </si>
+  <si>
+    <t>ZULAYHO</t>
+  </si>
+  <si>
+    <t>JT5498880650303</t>
+  </si>
+  <si>
+    <t>JT5498262384603</t>
+  </si>
+  <si>
+    <t>YT8879925973530</t>
+  </si>
+  <si>
+    <t>013507474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ismoilzoda N </t>
+  </si>
+  <si>
+    <t>JT5498515169938</t>
+  </si>
+  <si>
+    <t>MUZHDA</t>
+  </si>
+  <si>
+    <t>FIRDAVS</t>
+  </si>
+  <si>
+    <t>Sherali</t>
+  </si>
+  <si>
+    <t>Aziza</t>
+  </si>
+  <si>
+    <t>465447506810494</t>
   </si>
 </sst>
 </file>
@@ -93,9 +141,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -399,165 +451,432 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A31"/>
+  <dimension ref="A1:F60"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.88671875" customWidth="1"/>
+    <col min="1" max="1" width="16.88671875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="13" customWidth="1"/>
+    <col min="4" max="4" width="13.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="1">
+        <v>773428109156580</v>
+      </c>
+      <c r="C2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="1">
+        <v>777420209995112</v>
+      </c>
+      <c r="C3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="1">
+        <v>79115916921709</v>
+      </c>
+      <c r="C4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="1">
+        <v>9817512182414</v>
+      </c>
+      <c r="C5" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="1">
+        <v>9817475375924</v>
+      </c>
+      <c r="C6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="1">
+        <v>79013823518038</v>
+      </c>
+      <c r="C7" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" t="s">
+        <v>4</v>
+      </c>
+      <c r="D9">
+        <v>929589803</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" s="1">
+        <v>777420320755106</v>
+      </c>
+      <c r="C13" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13">
+        <v>926111168</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" s="1">
+        <v>777420362773842</v>
+      </c>
+      <c r="C15" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" s="1">
+        <v>777421365313677</v>
+      </c>
+      <c r="C17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D17">
+        <v>929264050</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" s="1">
+        <v>777421365892035</v>
+      </c>
+      <c r="C18" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" s="1">
+        <v>777420190077415</v>
+      </c>
+      <c r="C20" t="s">
+        <v>11</v>
+      </c>
+      <c r="D20">
+        <v>921779435</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C21" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" s="1">
+        <v>465444445672611</v>
+      </c>
+      <c r="C22" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" s="1">
+        <v>777420148088605</v>
+      </c>
+      <c r="C23" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A25" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C25" t="s">
+        <v>1</v>
+      </c>
+      <c r="D25">
+        <v>920171229</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A26" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" s="1">
-        <v>773413206562154</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A4" s="1">
-        <v>465212686698645</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
+      <c r="C26" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A27" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C27" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A28" s="1">
+        <v>777421046930615</v>
+      </c>
+      <c r="C28" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A29" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C29" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A31" s="1">
+        <v>465447154216665</v>
+      </c>
+      <c r="C31" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A7" s="1">
-        <v>78591051194575</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A9" s="1">
-        <v>465211716662045</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A10" s="1">
-        <v>465205906122183</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A12" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A13" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A14" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A15" s="1">
-        <v>777394602879200</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A16" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A17" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A18" s="1">
-        <v>78590897791657</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A19" s="1">
-        <v>9815155788467</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A20" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A21" s="1">
-        <v>777395463852473</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A22" s="1">
-        <v>777396456829877</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A23" s="1">
-        <v>9815113293267</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A24" s="1">
-        <v>78591226903390</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A25" s="1">
-        <v>777395448947375</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A26" s="1">
-        <v>777395463531124</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A27" s="1">
-        <v>9821902126641</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A28" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A29" s="1">
-        <v>465212296995694</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A30" s="1">
-        <v>777395667606956</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A31" s="1" t="s">
-        <v>12</v>
+      <c r="D31">
+        <v>927528798</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A32" s="1">
+        <v>465445838248752</v>
+      </c>
+      <c r="C32" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A33" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C33" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A34" s="1">
+        <v>777421232224929</v>
+      </c>
+      <c r="C34" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A35" s="1">
+        <v>79116252056460</v>
+      </c>
+      <c r="C35" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A36" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C36" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A37" s="1">
+        <v>465445620423811</v>
+      </c>
+      <c r="C37" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A39" s="1">
+        <v>465443036459439</v>
+      </c>
+      <c r="C39" t="s">
+        <v>18</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F39">
+        <v>2.6880000000000002</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A40" s="1">
+        <v>9817508074958</v>
+      </c>
+      <c r="C40" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A41" s="1">
+        <v>777420364234201</v>
+      </c>
+      <c r="C41" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A42" s="1">
+        <v>9817450914859</v>
+      </c>
+      <c r="C42" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A43" s="1">
+        <v>9817455768664</v>
+      </c>
+      <c r="C43" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A44" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C44" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A45" s="1">
+        <v>777420107395099</v>
+      </c>
+      <c r="C45" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A46" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C46" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A47" s="1">
+        <v>9817494430164</v>
+      </c>
+      <c r="C47" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A48" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C48" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A49" s="1">
+        <v>777420415699128</v>
+      </c>
+      <c r="C49" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A51" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C51" t="s">
+        <v>23</v>
+      </c>
+      <c r="D51">
+        <v>878870899</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A53" s="1">
+        <v>9817528972077</v>
+      </c>
+      <c r="C53" t="s">
+        <v>25</v>
+      </c>
+      <c r="D53">
+        <v>923335522</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A54" s="1">
+        <v>777421096212600</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A56" s="1">
+        <v>777421190698415</v>
+      </c>
+      <c r="C56" t="s">
+        <v>26</v>
+      </c>
+      <c r="D56">
+        <v>928770009</v>
+      </c>
+      <c r="F56">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A58" s="1">
+        <v>9817479807223</v>
+      </c>
+      <c r="C58" t="s">
+        <v>27</v>
+      </c>
+      <c r="D58">
+        <v>927711266</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A60" s="1">
+        <v>79116064173156</v>
+      </c>
+      <c r="C60" t="s">
+        <v>28</v>
+      </c>
+      <c r="D60">
+        <v>928959444</v>
       </c>
     </row>
   </sheetData>

--- a/zafarabad.xlsx
+++ b/zafarabad.xlsx
@@ -12,6 +12,7 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="122211"/>
+  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
@@ -459,12 +460,12 @@
     <col min="4" max="4" width="13.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>773428109156580</v>
       </c>
@@ -472,7 +473,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>777420209995112</v>
       </c>
@@ -480,7 +481,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>79115916921709</v>
       </c>
@@ -488,7 +489,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>9817512182414</v>
       </c>
@@ -496,7 +497,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>9817475375924</v>
       </c>
@@ -504,7 +505,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>79013823518038</v>
       </c>
@@ -512,7 +513,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>5</v>
       </c>
@@ -523,7 +524,7 @@
         <v>929589803</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>6</v>
       </c>
@@ -531,7 +532,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>7</v>
       </c>
@@ -539,7 +540,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>777420320755106</v>
       </c>
@@ -549,21 +550,30 @@
       <c r="D13">
         <v>926111168</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F13">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C14" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F14">
+        <v>0.51</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>777420362773842</v>
       </c>
       <c r="C15" t="s">
         <v>8</v>
+      </c>
+      <c r="F15">
+        <v>1.32</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">

--- a/zafarabad.xlsx
+++ b/zafarabad.xlsx
@@ -11,13 +11,12 @@
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="122211"/>
-  <fileRecoveryPr repairLoad="1"/>
+  <calcPr calcId="145621"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="47">
   <si>
     <t>Track</t>
   </si>
@@ -107,6 +106,57 @@
   </si>
   <si>
     <t>465447506810494</t>
+  </si>
+  <si>
+    <t>ALISHER004</t>
+  </si>
+  <si>
+    <t>MUHIBSHOH</t>
+  </si>
+  <si>
+    <t>BAKHTIGUL</t>
+  </si>
+  <si>
+    <t>SUHROB</t>
+  </si>
+  <si>
+    <t>NAIMJON</t>
+  </si>
+  <si>
+    <t>FAYYOZ0888</t>
+  </si>
+  <si>
+    <t>AZIZA</t>
+  </si>
+  <si>
+    <t>ISMOIL</t>
+  </si>
+  <si>
+    <t>ISMOILZODA N</t>
+  </si>
+  <si>
+    <t>SITORA ZFD</t>
+  </si>
+  <si>
+    <t>MARHABO</t>
+  </si>
+  <si>
+    <t>YT8879492297615</t>
+  </si>
+  <si>
+    <t>Anvar</t>
+  </si>
+  <si>
+    <t>номаш</t>
+  </si>
+  <si>
+    <t>штукаш</t>
+  </si>
+  <si>
+    <t>пулаш</t>
+  </si>
+  <si>
+    <t>+</t>
   </si>
 </sst>
 </file>
@@ -130,7 +180,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -138,11 +188,57 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -151,6 +247,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -452,7 +556,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F60"/>
+  <dimension ref="A1:G79"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.88671875" style="1" customWidth="1"/>
@@ -818,7 +922,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
         <v>777420415699128</v>
       </c>
@@ -826,7 +930,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
         <v>24</v>
       </c>
@@ -837,7 +941,7 @@
         <v>878870899</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" s="1">
         <v>9817528972077</v>
       </c>
@@ -848,12 +952,12 @@
         <v>923335522</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" s="1">
         <v>777421096212600</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" s="1">
         <v>777421190698415</v>
       </c>
@@ -867,7 +971,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" s="1">
         <v>9817479807223</v>
       </c>
@@ -878,7 +982,7 @@
         <v>927711266</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" s="1">
         <v>79116064173156</v>
       </c>
@@ -887,6 +991,233 @@
       </c>
       <c r="D60">
         <v>928959444</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A61" s="4"/>
+      <c r="B61" s="5"/>
+      <c r="C61" s="6"/>
+      <c r="D61" s="6"/>
+      <c r="E61" s="6"/>
+      <c r="F61" s="6"/>
+      <c r="G61" s="5"/>
+    </row>
+    <row r="62" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A62" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C62" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D62" s="8"/>
+      <c r="E62" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="F62" s="9" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C63" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E63">
+        <v>9</v>
+      </c>
+      <c r="F63">
+        <v>109</v>
+      </c>
+      <c r="G63" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C64" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E64">
+        <v>8</v>
+      </c>
+      <c r="F64">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C65" t="s">
+        <v>42</v>
+      </c>
+      <c r="F65">
+        <v>18.399999999999999</v>
+      </c>
+      <c r="G65" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C66" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E66">
+        <v>2</v>
+      </c>
+      <c r="F66">
+        <v>46.75</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C67" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E67">
+        <v>1</v>
+      </c>
+      <c r="F67">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C68" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E68">
+        <v>1</v>
+      </c>
+      <c r="F68">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C69" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E69">
+        <v>1</v>
+      </c>
+      <c r="F69">
+        <v>146</v>
+      </c>
+      <c r="G69" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A70" s="1">
+        <v>777420502615652</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E70">
+        <v>1</v>
+      </c>
+      <c r="F70">
+        <v>2</v>
+      </c>
+      <c r="G70" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C71" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E71">
+        <v>2</v>
+      </c>
+      <c r="F71">
+        <v>48</v>
+      </c>
+      <c r="G71" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C72" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E72">
+        <v>2</v>
+      </c>
+      <c r="F72">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C73" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E73">
+        <v>3</v>
+      </c>
+      <c r="F73">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C74" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E74">
+        <v>1</v>
+      </c>
+      <c r="F74">
+        <v>3</v>
+      </c>
+      <c r="G74" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C75" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E75">
+        <v>1</v>
+      </c>
+      <c r="F75">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C76" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E76">
+        <v>4</v>
+      </c>
+      <c r="F76">
+        <v>27.6</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C77" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E77">
+        <v>17</v>
+      </c>
+      <c r="F77">
+        <v>93</v>
+      </c>
+      <c r="G77" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C78" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E78">
+        <v>25</v>
+      </c>
+      <c r="F78">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F79">
+        <f>SUM(F63:F78)</f>
+        <v>753.75</v>
       </c>
     </row>
   </sheetData>

--- a/zafarabad.xlsx
+++ b/zafarabad.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="86">
   <si>
     <t>Track</t>
   </si>
@@ -157,6 +157,123 @@
   </si>
   <si>
     <t>+</t>
+  </si>
+  <si>
+    <t>YT8881827269921</t>
+  </si>
+  <si>
+    <t>JT5499593076310</t>
+  </si>
+  <si>
+    <t>RAJABALI</t>
+  </si>
+  <si>
+    <t>007998786</t>
+  </si>
+  <si>
+    <t>UMEDJON</t>
+  </si>
+  <si>
+    <t>JT5499505166782</t>
+  </si>
+  <si>
+    <t>muzhda</t>
+  </si>
+  <si>
+    <t>YT8881014957527</t>
+  </si>
+  <si>
+    <t>JT5499824273016</t>
+  </si>
+  <si>
+    <t>JT5498633122296</t>
+  </si>
+  <si>
+    <t>YT8881001428247</t>
+  </si>
+  <si>
+    <t>YT8881016845806</t>
+  </si>
+  <si>
+    <t>MUSTAFOJON</t>
+  </si>
+  <si>
+    <t>YT8881713805039</t>
+  </si>
+  <si>
+    <t>076149944</t>
+  </si>
+  <si>
+    <t>MADINA</t>
+  </si>
+  <si>
+    <t>JT5499420492228</t>
+  </si>
+  <si>
+    <t>JT5499555318372</t>
+  </si>
+  <si>
+    <t>YT8881256136317</t>
+  </si>
+  <si>
+    <t>ROHILa</t>
+  </si>
+  <si>
+    <t>NILUFAR</t>
+  </si>
+  <si>
+    <t>YT8881203079304</t>
+  </si>
+  <si>
+    <t>JT5499459270971</t>
+  </si>
+  <si>
+    <t>YT8881205713280</t>
+  </si>
+  <si>
+    <t>JT5499581951689</t>
+  </si>
+  <si>
+    <t>VASLIDDIN</t>
+  </si>
+  <si>
+    <t>JT5499557335871</t>
+  </si>
+  <si>
+    <t>YT8881264556325</t>
+  </si>
+  <si>
+    <t>JT5499357097713</t>
+  </si>
+  <si>
+    <t>JT5499474471835</t>
+  </si>
+  <si>
+    <t>TOHIR</t>
+  </si>
+  <si>
+    <t>021950010</t>
+  </si>
+  <si>
+    <t>JT5499708160992</t>
+  </si>
+  <si>
+    <t>JT5499254571451</t>
+  </si>
+  <si>
+    <t>YT8880982299813</t>
+  </si>
+  <si>
+    <t>AKO ALISHER</t>
+  </si>
+  <si>
+    <t>JAMSHED</t>
+  </si>
+  <si>
+    <t>YT8881710489346</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
@@ -556,12 +673,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G79"/>
+  <dimension ref="A1:J174"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.88671875" style="1" customWidth="1"/>
     <col min="3" max="3" width="13" customWidth="1"/>
     <col min="4" max="4" width="13.109375" customWidth="1"/>
+    <col min="11" max="11" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
@@ -1000,7 +1118,7 @@
       <c r="D61" s="6"/>
       <c r="E61" s="6"/>
       <c r="F61" s="6"/>
-      <c r="G61" s="5"/>
+      <c r="G61" s="6"/>
     </row>
     <row r="62" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A62" s="1" t="s">
@@ -1041,6 +1159,9 @@
       <c r="F64">
         <v>15</v>
       </c>
+      <c r="G64" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C65" t="s">
@@ -1063,6 +1184,9 @@
       <c r="F66">
         <v>46.75</v>
       </c>
+      <c r="G66" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C67" s="1" t="s">
@@ -1074,6 +1198,9 @@
       <c r="F67">
         <v>12</v>
       </c>
+      <c r="G67" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C68" s="1" t="s">
@@ -1085,6 +1212,9 @@
       <c r="F68">
         <v>4</v>
       </c>
+      <c r="G68" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C69" s="1" t="s">
@@ -1141,6 +1271,9 @@
       <c r="F72">
         <v>1</v>
       </c>
+      <c r="G72" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C73" s="1" t="s">
@@ -1203,7 +1336,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C78" s="1" t="s">
         <v>11</v>
       </c>
@@ -1213,11 +1346,548 @@
       <c r="F78">
         <v>185</v>
       </c>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F79">
+      <c r="G78" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E79" s="7">
+        <f>SUM(E63:E78)</f>
+        <v>78</v>
+      </c>
+      <c r="F79" s="9">
         <f>SUM(F63:F78)</f>
         <v>753.75</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A82" s="1">
+        <v>79115562559722</v>
+      </c>
+      <c r="C82" t="s">
+        <v>11</v>
+      </c>
+      <c r="D82">
+        <v>921779435</v>
+      </c>
+      <c r="F82">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A83" s="1">
+        <v>79116352158884</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A84" s="1">
+        <v>777421947371815</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A85" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A86" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A87" s="1">
+        <v>777422365205500</v>
+      </c>
+      <c r="J87" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A88" s="1">
+        <v>777422098989110</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A89" s="1">
+        <v>777422227310805</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A91" s="1">
+        <v>79117070893183</v>
+      </c>
+      <c r="C91" t="s">
+        <v>10</v>
+      </c>
+      <c r="D91">
+        <v>929264050</v>
+      </c>
+      <c r="F91">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A93" s="1">
+        <v>9817599918493</v>
+      </c>
+      <c r="C93" t="s">
+        <v>49</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F93">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A94" s="1">
+        <v>9817597042198</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A96" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C96" t="s">
+        <v>51</v>
+      </c>
+      <c r="D96">
+        <v>925882853</v>
+      </c>
+      <c r="F96">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A98" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C98" t="s">
+        <v>53</v>
+      </c>
+      <c r="D98">
+        <v>923335522</v>
+      </c>
+      <c r="F98">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A99" s="1">
+        <v>777421102032945</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A100" s="1">
+        <v>465453312175650</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A101" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A102" s="1">
+        <v>79117054093610</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A103" s="1">
+        <v>9817561906196</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A104" s="1">
+        <v>9817577879969</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A105" s="1">
+        <v>465455321353258</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A106" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A107" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A108" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A110" s="1">
+        <v>465459292330949</v>
+      </c>
+      <c r="C110" t="s">
+        <v>59</v>
+      </c>
+      <c r="D110">
+        <v>928252494</v>
+      </c>
+      <c r="F110">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A111" s="1">
+        <v>465457764900348</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A112" s="1">
+        <v>9817583571857</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A113" s="1">
+        <v>777421979396975</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A114" s="1">
+        <v>777422057138983</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A115" s="1">
+        <v>777422279578535</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A116" s="1">
+        <v>79117415228084</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A117" s="1">
+        <v>777422047937564</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A118" s="1">
+        <v>9817587676356</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A119" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A121" s="1">
+        <v>435243081637711</v>
+      </c>
+      <c r="C121" t="s">
+        <v>34</v>
+      </c>
+      <c r="D121" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="F121">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A122" s="1">
+        <v>79014648854833</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A124" s="1">
+        <v>777422232180626</v>
+      </c>
+      <c r="C124" t="s">
+        <v>62</v>
+      </c>
+      <c r="D124">
+        <v>557009840</v>
+      </c>
+      <c r="F124">
+        <v>70.5</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A125" s="1">
+        <v>79117395794341</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A126" s="1">
+        <v>777422086167392</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A127" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A128" s="1">
+        <v>9817590201640</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A129" s="1">
+        <v>79117436311943</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A130" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A131" s="1">
+        <v>9817606613366</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A132" s="1">
+        <v>777421855554896</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A133" s="1">
+        <v>465456795812468</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A134" s="1">
+        <v>79117509710669</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A135" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A137" s="1">
+        <v>465448606440063</v>
+      </c>
+      <c r="C137" t="s">
+        <v>66</v>
+      </c>
+      <c r="D137">
+        <v>920171229</v>
+      </c>
+      <c r="F137">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A138" s="1">
+        <v>777420974852832</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A139" s="1">
+        <v>465451760956911</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A141" s="1">
+        <v>79117465527523</v>
+      </c>
+      <c r="C141" t="s">
+        <v>67</v>
+      </c>
+      <c r="D141">
+        <v>975413355</v>
+      </c>
+      <c r="F141">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A142" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A143" s="1">
+        <v>9817607428330</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A144" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A145" s="1">
+        <v>9817587706895</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A146" s="1">
+        <v>9817585314171</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A147" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A148" s="1">
+        <v>9817611933106</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A149" s="1">
+        <v>465450172258904</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A150" s="1">
+        <v>777422249209050</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A151" s="1">
+        <v>79117774445858</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A152" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A153" s="1">
+        <v>9817601310341</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A155" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C155" t="s">
+        <v>72</v>
+      </c>
+      <c r="D155">
+        <v>929279300</v>
+      </c>
+      <c r="F155">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A156" s="1">
+        <v>465457357410239</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A157" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A158" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A159" s="1">
+        <v>9817598337810</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A160" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A162" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C162" t="s">
+        <v>77</v>
+      </c>
+      <c r="D162" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="F162">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A163" s="1">
+        <v>9817572476799</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A164" s="1">
+        <v>777421616975217</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A165" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A166" s="1">
+        <v>777421939569475</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A168" s="1">
+        <v>79116860524513</v>
+      </c>
+      <c r="C168" t="s">
+        <v>32</v>
+      </c>
+      <c r="D168">
+        <v>875266000</v>
+      </c>
+      <c r="F168">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A169" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A171" s="1">
+        <v>79117696250946</v>
+      </c>
+      <c r="C171" t="s">
+        <v>82</v>
+      </c>
+      <c r="F171">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A173" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C173" t="s">
+        <v>83</v>
+      </c>
+      <c r="D173">
+        <v>926666568</v>
+      </c>
+      <c r="F173">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="174" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A174" s="1">
+        <v>8258794480420</v>
       </c>
     </row>
   </sheetData>

--- a/zafarabad.xlsx
+++ b/zafarabad.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="112">
   <si>
     <t>Track</t>
   </si>
@@ -274,15 +274,108 @@
   </si>
   <si>
     <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  </t>
+  </si>
+  <si>
+    <t>MEHRUBON</t>
+  </si>
+  <si>
+    <t xml:space="preserve">               </t>
+  </si>
+  <si>
+    <t xml:space="preserve">HILOLA </t>
+  </si>
+  <si>
+    <t>Rajabali</t>
+  </si>
+  <si>
+    <t>alisher mirashurov</t>
+  </si>
+  <si>
+    <t>EHROMJON</t>
+  </si>
+  <si>
+    <t>SF5112110102446</t>
+  </si>
+  <si>
+    <t>YT8881971825187</t>
+  </si>
+  <si>
+    <t>YT8882105763850</t>
+  </si>
+  <si>
+    <t>alisher</t>
+  </si>
+  <si>
+    <t>NORMUROD</t>
+  </si>
+  <si>
+    <t>UMEDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36TA </t>
+  </si>
+  <si>
+    <t>A PARVINA</t>
+  </si>
+  <si>
+    <t>ALISHER0004</t>
+  </si>
+  <si>
+    <t>SADOQAT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M RAHMON </t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BEHRUZ </t>
+  </si>
+  <si>
+    <t>SHAHROM</t>
+  </si>
+  <si>
+    <t>DILDORA</t>
+  </si>
+  <si>
+    <t>SUNATULLO</t>
+  </si>
+  <si>
+    <t>INTIZORA</t>
+  </si>
+  <si>
+    <t>OZODA</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="16"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -355,23 +448,44 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -673,13 +787,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J174"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:J234"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.88671875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="13" customWidth="1"/>
-    <col min="4" max="4" width="13.109375" customWidth="1"/>
-    <col min="11" max="11" width="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.44140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="19.77734375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="19.21875" style="1" customWidth="1"/>
+    <col min="5" max="6" width="8.88671875" style="1"/>
+    <col min="7" max="7" width="8.88671875" style="8"/>
+    <col min="8" max="10" width="8.88671875" style="1"/>
+    <col min="11" max="11" width="10" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
@@ -691,7 +810,7 @@
       <c r="A2" s="1">
         <v>773428109156580</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
         <v>3</v>
       </c>
     </row>
@@ -699,7 +818,7 @@
       <c r="A3" s="1">
         <v>777420209995112</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="1" t="s">
         <v>3</v>
       </c>
     </row>
@@ -707,7 +826,7 @@
       <c r="A4" s="1">
         <v>79115916921709</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="1" t="s">
         <v>3</v>
       </c>
     </row>
@@ -715,7 +834,7 @@
       <c r="A5" s="1">
         <v>9817512182414</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="1" t="s">
         <v>3</v>
       </c>
     </row>
@@ -723,7 +842,7 @@
       <c r="A6" s="1">
         <v>9817475375924</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="1" t="s">
         <v>3</v>
       </c>
     </row>
@@ -731,7 +850,7 @@
       <c r="A7" s="1">
         <v>79013823518038</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="1" t="s">
         <v>3</v>
       </c>
     </row>
@@ -739,10 +858,10 @@
       <c r="A9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="1">
         <v>929589803</v>
       </c>
     </row>
@@ -750,7 +869,7 @@
       <c r="A10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -758,7 +877,7 @@
       <c r="A11" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -766,13 +885,13 @@
       <c r="A13" s="1">
         <v>777420320755106</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="1">
         <v>926111168</v>
       </c>
-      <c r="F13">
+      <c r="F13" s="1">
         <v>5.5</v>
       </c>
     </row>
@@ -780,10 +899,10 @@
       <c r="A14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F14">
+      <c r="F14" s="1">
         <v>0.51</v>
       </c>
     </row>
@@ -791,10 +910,10 @@
       <c r="A15" s="1">
         <v>777420362773842</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F15">
+      <c r="F15" s="1">
         <v>1.32</v>
       </c>
     </row>
@@ -802,10 +921,10 @@
       <c r="A17" s="1">
         <v>777421365313677</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D17">
+      <c r="D17" s="1">
         <v>929264050</v>
       </c>
     </row>
@@ -813,7 +932,7 @@
       <c r="A18" s="1">
         <v>777421365892035</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="1" t="s">
         <v>10</v>
       </c>
     </row>
@@ -821,10 +940,10 @@
       <c r="A20" s="1">
         <v>777420190077415</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D20">
+      <c r="D20" s="1">
         <v>921779435</v>
       </c>
     </row>
@@ -832,7 +951,7 @@
       <c r="A21" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" s="1" t="s">
         <v>11</v>
       </c>
     </row>
@@ -840,7 +959,7 @@
       <c r="A22" s="1">
         <v>465444445672611</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C22" s="1" t="s">
         <v>11</v>
       </c>
     </row>
@@ -848,18 +967,18 @@
       <c r="A23" s="1">
         <v>777420148088605</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A25" s="3" t="s">
+      <c r="A25" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C25" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D25">
+      <c r="D25" s="1">
         <v>920171229</v>
       </c>
     </row>
@@ -867,7 +986,7 @@
       <c r="A26" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C26" s="1" t="s">
         <v>1</v>
       </c>
     </row>
@@ -875,7 +994,7 @@
       <c r="A27" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C27" s="1" t="s">
         <v>1</v>
       </c>
     </row>
@@ -883,7 +1002,7 @@
       <c r="A28" s="1">
         <v>777421046930615</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C28" s="1" t="s">
         <v>1</v>
       </c>
     </row>
@@ -891,7 +1010,7 @@
       <c r="A29" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C29" s="1" t="s">
         <v>1</v>
       </c>
     </row>
@@ -899,10 +1018,10 @@
       <c r="A31" s="1">
         <v>465447154216665</v>
       </c>
-      <c r="C31" t="s">
+      <c r="C31" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D31">
+      <c r="D31" s="1">
         <v>927528798</v>
       </c>
     </row>
@@ -910,7 +1029,7 @@
       <c r="A32" s="1">
         <v>465445838248752</v>
       </c>
-      <c r="C32" t="s">
+      <c r="C32" s="1" t="s">
         <v>2</v>
       </c>
     </row>
@@ -918,7 +1037,7 @@
       <c r="A33" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C33" t="s">
+      <c r="C33" s="1" t="s">
         <v>2</v>
       </c>
     </row>
@@ -926,7 +1045,7 @@
       <c r="A34" s="1">
         <v>777421232224929</v>
       </c>
-      <c r="C34" t="s">
+      <c r="C34" s="1" t="s">
         <v>2</v>
       </c>
     </row>
@@ -934,7 +1053,7 @@
       <c r="A35" s="1">
         <v>79116252056460</v>
       </c>
-      <c r="C35" t="s">
+      <c r="C35" s="1" t="s">
         <v>2</v>
       </c>
     </row>
@@ -942,7 +1061,7 @@
       <c r="A36" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C36" t="s">
+      <c r="C36" s="1" t="s">
         <v>2</v>
       </c>
     </row>
@@ -950,7 +1069,7 @@
       <c r="A37" s="1">
         <v>465445620423811</v>
       </c>
-      <c r="C37" t="s">
+      <c r="C37" s="1" t="s">
         <v>2</v>
       </c>
     </row>
@@ -958,13 +1077,13 @@
       <c r="A39" s="1">
         <v>465443036459439</v>
       </c>
-      <c r="C39" t="s">
+      <c r="C39" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D39" s="2" t="s">
+      <c r="D39" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="F39">
+      <c r="F39" s="1">
         <v>2.6880000000000002</v>
       </c>
     </row>
@@ -972,7 +1091,7 @@
       <c r="A40" s="1">
         <v>9817508074958</v>
       </c>
-      <c r="C40" t="s">
+      <c r="C40" s="1" t="s">
         <v>18</v>
       </c>
     </row>
@@ -980,7 +1099,7 @@
       <c r="A41" s="1">
         <v>777420364234201</v>
       </c>
-      <c r="C41" t="s">
+      <c r="C41" s="1" t="s">
         <v>18</v>
       </c>
     </row>
@@ -988,7 +1107,7 @@
       <c r="A42" s="1">
         <v>9817450914859</v>
       </c>
-      <c r="C42" t="s">
+      <c r="C42" s="1" t="s">
         <v>18</v>
       </c>
     </row>
@@ -996,7 +1115,7 @@
       <c r="A43" s="1">
         <v>9817455768664</v>
       </c>
-      <c r="C43" t="s">
+      <c r="C43" s="1" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1004,7 +1123,7 @@
       <c r="A44" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C44" t="s">
+      <c r="C44" s="1" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1012,7 +1131,7 @@
       <c r="A45" s="1">
         <v>777420107395099</v>
       </c>
-      <c r="C45" t="s">
+      <c r="C45" s="1" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1020,7 +1139,7 @@
       <c r="A46" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C46" t="s">
+      <c r="C46" s="1" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1028,7 +1147,7 @@
       <c r="A47" s="1">
         <v>9817494430164</v>
       </c>
-      <c r="C47" t="s">
+      <c r="C47" s="1" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1036,7 +1155,7 @@
       <c r="A48" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C48" t="s">
+      <c r="C48" s="1" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1044,7 +1163,7 @@
       <c r="A49" s="1">
         <v>777420415699128</v>
       </c>
-      <c r="C49" t="s">
+      <c r="C49" s="1" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1052,10 +1171,10 @@
       <c r="A51" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C51" t="s">
+      <c r="C51" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D51">
+      <c r="D51" s="1">
         <v>878870899</v>
       </c>
     </row>
@@ -1063,10 +1182,10 @@
       <c r="A53" s="1">
         <v>9817528972077</v>
       </c>
-      <c r="C53" t="s">
+      <c r="C53" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D53">
+      <c r="D53" s="1">
         <v>923335522</v>
       </c>
     </row>
@@ -1079,13 +1198,13 @@
       <c r="A56" s="1">
         <v>777421190698415</v>
       </c>
-      <c r="C56" t="s">
+      <c r="C56" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D56">
+      <c r="D56" s="1">
         <v>928770009</v>
       </c>
-      <c r="F56">
+      <c r="F56" s="1">
         <v>0.7</v>
       </c>
     </row>
@@ -1093,10 +1212,10 @@
       <c r="A58" s="1">
         <v>9817479807223</v>
       </c>
-      <c r="C58" t="s">
+      <c r="C58" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D58">
+      <c r="D58" s="1">
         <v>927711266</v>
       </c>
     </row>
@@ -1104,34 +1223,34 @@
       <c r="A60" s="1">
         <v>79116064173156</v>
       </c>
-      <c r="C60" t="s">
+      <c r="C60" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D60">
+      <c r="D60" s="1">
         <v>928959444</v>
       </c>
     </row>
-    <row r="61" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="4"/>
-      <c r="B61" s="5"/>
-      <c r="C61" s="6"/>
-      <c r="D61" s="6"/>
-      <c r="E61" s="6"/>
-      <c r="F61" s="6"/>
-      <c r="G61" s="6"/>
-    </row>
-    <row r="62" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:7" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A61" s="3"/>
+      <c r="B61" s="3"/>
+      <c r="C61" s="2"/>
+      <c r="D61" s="2"/>
+      <c r="E61" s="2"/>
+      <c r="F61" s="2"/>
+      <c r="G61" s="9"/>
+    </row>
+    <row r="62" spans="1:7" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A62" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C62" s="7" t="s">
+      <c r="C62" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="D62" s="8"/>
-      <c r="E62" s="8" t="s">
+      <c r="D62" s="4"/>
+      <c r="E62" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="F62" s="9" t="s">
+      <c r="F62" s="7" t="s">
         <v>45</v>
       </c>
     </row>
@@ -1139,13 +1258,13 @@
       <c r="C63" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E63">
+      <c r="E63" s="1">
         <v>9</v>
       </c>
-      <c r="F63">
+      <c r="F63" s="1">
         <v>109</v>
       </c>
-      <c r="G63" t="s">
+      <c r="G63" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -1153,24 +1272,24 @@
       <c r="C64" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E64">
+      <c r="E64" s="1">
         <v>8</v>
       </c>
-      <c r="F64">
+      <c r="F64" s="1">
         <v>15</v>
       </c>
-      <c r="G64" t="s">
+      <c r="G64" s="8" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="C65" t="s">
+      <c r="C65" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="F65">
+      <c r="F65" s="1">
         <v>18.399999999999999</v>
       </c>
-      <c r="G65" t="s">
+      <c r="G65" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -1178,13 +1297,13 @@
       <c r="C66" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E66">
+      <c r="E66" s="1">
         <v>2</v>
       </c>
-      <c r="F66">
+      <c r="F66" s="1">
         <v>46.75</v>
       </c>
-      <c r="G66" t="s">
+      <c r="G66" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -1192,13 +1311,13 @@
       <c r="C67" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E67">
+      <c r="E67" s="1">
         <v>1</v>
       </c>
-      <c r="F67">
+      <c r="F67" s="1">
         <v>12</v>
       </c>
-      <c r="G67" t="s">
+      <c r="G67" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -1206,13 +1325,13 @@
       <c r="C68" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E68">
+      <c r="E68" s="1">
         <v>1</v>
       </c>
-      <c r="F68">
+      <c r="F68" s="1">
         <v>4</v>
       </c>
-      <c r="G68" t="s">
+      <c r="G68" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -1220,13 +1339,13 @@
       <c r="C69" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="E69">
+      <c r="E69" s="1">
         <v>1</v>
       </c>
-      <c r="F69">
+      <c r="F69" s="1">
         <v>146</v>
       </c>
-      <c r="G69" t="s">
+      <c r="G69" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -1237,13 +1356,13 @@
       <c r="C70" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E70">
+      <c r="E70" s="1">
         <v>1</v>
       </c>
-      <c r="F70">
+      <c r="F70" s="1">
         <v>2</v>
       </c>
-      <c r="G70" t="s">
+      <c r="G70" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -1251,13 +1370,13 @@
       <c r="C71" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="E71">
+      <c r="E71" s="1">
         <v>2</v>
       </c>
-      <c r="F71">
+      <c r="F71" s="1">
         <v>48</v>
       </c>
-      <c r="G71" t="s">
+      <c r="G71" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -1265,13 +1384,13 @@
       <c r="C72" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E72">
+      <c r="E72" s="1">
         <v>2</v>
       </c>
-      <c r="F72">
+      <c r="F72" s="1">
         <v>1</v>
       </c>
-      <c r="G72" t="s">
+      <c r="G72" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -1279,10 +1398,10 @@
       <c r="C73" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E73">
+      <c r="E73" s="1">
         <v>3</v>
       </c>
-      <c r="F73">
+      <c r="F73" s="1">
         <v>15</v>
       </c>
     </row>
@@ -1290,13 +1409,13 @@
       <c r="C74" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="E74">
+      <c r="E74" s="1">
         <v>1</v>
       </c>
-      <c r="F74">
+      <c r="F74" s="1">
         <v>3</v>
       </c>
-      <c r="G74" t="s">
+      <c r="G74" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -1304,10 +1423,10 @@
       <c r="C75" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="E75">
+      <c r="E75" s="1">
         <v>1</v>
       </c>
-      <c r="F75">
+      <c r="F75" s="1">
         <v>28</v>
       </c>
     </row>
@@ -1315,10 +1434,10 @@
       <c r="C76" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="E76">
+      <c r="E76" s="1">
         <v>4</v>
       </c>
-      <c r="F76">
+      <c r="F76" s="1">
         <v>27.6</v>
       </c>
     </row>
@@ -1326,36 +1445,36 @@
       <c r="C77" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E77">
+      <c r="E77" s="1">
         <v>17</v>
       </c>
-      <c r="F77">
+      <c r="F77" s="1">
         <v>93</v>
       </c>
-      <c r="G77" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G77" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C78" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E78">
+      <c r="E78" s="1">
         <v>25</v>
       </c>
-      <c r="F78">
+      <c r="F78" s="1">
         <v>185</v>
       </c>
-      <c r="G78" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E79" s="7">
+      <c r="G78" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E79" s="6">
         <f>SUM(E63:E78)</f>
         <v>78</v>
       </c>
-      <c r="F79" s="9">
+      <c r="F79" s="7">
         <f>SUM(F63:F78)</f>
         <v>753.75</v>
       </c>
@@ -1364,14 +1483,17 @@
       <c r="A82" s="1">
         <v>79115562559722</v>
       </c>
-      <c r="C82" t="s">
+      <c r="C82" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D82">
+      <c r="D82" s="1">
         <v>921779435</v>
       </c>
-      <c r="F82">
+      <c r="F82" s="1">
         <v>44</v>
+      </c>
+      <c r="G82" s="8" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.3">
@@ -1398,7 +1520,7 @@
       <c r="A87" s="1">
         <v>777422365205500</v>
       </c>
-      <c r="J87" t="s">
+      <c r="J87" s="1" t="s">
         <v>85</v>
       </c>
     </row>
@@ -1416,13 +1538,13 @@
       <c r="A91" s="1">
         <v>79117070893183</v>
       </c>
-      <c r="C91" t="s">
+      <c r="C91" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D91">
+      <c r="D91" s="1">
         <v>929264050</v>
       </c>
-      <c r="F91">
+      <c r="F91" s="1">
         <v>29</v>
       </c>
     </row>
@@ -1430,13 +1552,13 @@
       <c r="A93" s="1">
         <v>9817599918493</v>
       </c>
-      <c r="C93" t="s">
+      <c r="C93" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D93" s="2" t="s">
+      <c r="D93" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="F93">
+      <c r="F93" s="1">
         <v>3</v>
       </c>
     </row>
@@ -1449,13 +1571,13 @@
       <c r="A96" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C96" t="s">
+      <c r="C96" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D96">
+      <c r="D96" s="1">
         <v>925882853</v>
       </c>
-      <c r="F96">
+      <c r="F96" s="1">
         <v>1</v>
       </c>
     </row>
@@ -1463,13 +1585,13 @@
       <c r="A98" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C98" t="s">
+      <c r="C98" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D98">
+      <c r="D98" s="1">
         <v>923335522</v>
       </c>
-      <c r="F98">
+      <c r="F98" s="1">
         <v>117</v>
       </c>
     </row>
@@ -1527,13 +1649,13 @@
       <c r="A110" s="1">
         <v>465459292330949</v>
       </c>
-      <c r="C110" t="s">
+      <c r="C110" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="D110">
+      <c r="D110" s="1">
         <v>928252494</v>
       </c>
-      <c r="F110">
+      <c r="F110" s="1">
         <v>46</v>
       </c>
     </row>
@@ -1547,92 +1669,101 @@
         <v>9817583571857</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A113" s="1">
         <v>777421979396975</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A114" s="1">
         <v>777422057138983</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A115" s="1">
         <v>777422279578535</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A116" s="1">
         <v>79117415228084</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A117" s="1">
         <v>777422047937564</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A118" s="1">
         <v>9817587676356</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A119" s="1" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A121" s="1">
         <v>435243081637711</v>
       </c>
-      <c r="C121" t="s">
+      <c r="C121" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D121" s="2" t="s">
+      <c r="D121" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="F121">
+      <c r="F121" s="1">
         <v>14</v>
       </c>
-    </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G121" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A122" s="1">
         <v>79014648854833</v>
       </c>
-    </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G122" s="8" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A124" s="1">
         <v>777422232180626</v>
       </c>
-      <c r="C124" t="s">
+      <c r="C124" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="D124">
+      <c r="D124" s="1">
         <v>557009840</v>
       </c>
-      <c r="F124">
+      <c r="F124" s="1">
         <v>70.5</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A125" s="1">
         <v>79117395794341</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A126" s="1">
         <v>777422086167392</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A127" s="1" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A128" s="1">
         <v>9817590201640</v>
+      </c>
+      <c r="G128" s="8" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.3">
@@ -1674,13 +1805,13 @@
       <c r="A137" s="1">
         <v>465448606440063</v>
       </c>
-      <c r="C137" t="s">
+      <c r="C137" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="D137">
+      <c r="D137" s="1">
         <v>920171229</v>
       </c>
-      <c r="F137">
+      <c r="F137" s="1">
         <v>8.5</v>
       </c>
     </row>
@@ -1698,13 +1829,13 @@
       <c r="A141" s="1">
         <v>79117465527523</v>
       </c>
-      <c r="C141" t="s">
+      <c r="C141" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="D141">
+      <c r="D141" s="1">
         <v>975413355</v>
       </c>
-      <c r="F141">
+      <c r="F141" s="1">
         <v>54</v>
       </c>
     </row>
@@ -1723,175 +1854,825 @@
         <v>69</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A145" s="1">
         <v>9817587706895</v>
       </c>
     </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A146" s="1">
         <v>9817585314171</v>
       </c>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A147" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A148" s="1">
         <v>9817611933106</v>
       </c>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A149" s="1">
         <v>465450172258904</v>
       </c>
     </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A150" s="1">
         <v>777422249209050</v>
       </c>
     </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A151" s="1">
         <v>79117774445858</v>
       </c>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A152" s="1" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A153" s="1">
         <v>9817601310341</v>
       </c>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A155" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="C155" t="s">
+      <c r="C155" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D155">
+      <c r="D155" s="1">
         <v>929279300</v>
       </c>
-      <c r="F155">
+      <c r="F155" s="1">
         <v>141</v>
       </c>
-    </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G155" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A156" s="1">
         <v>465457357410239</v>
       </c>
     </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A157" s="1" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A158" s="1" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A159" s="1">
         <v>9817598337810</v>
       </c>
     </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A160" s="1" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A162" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="C162" t="s">
+      <c r="C162" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="D162" s="2" t="s">
+      <c r="D162" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="F162">
+      <c r="F162" s="1">
         <v>15</v>
       </c>
-    </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G162" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A163" s="1">
         <v>9817572476799</v>
       </c>
     </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A164" s="1">
         <v>777421616975217</v>
       </c>
     </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A165" s="1" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A166" s="1">
         <v>777421939569475</v>
       </c>
     </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A168" s="1">
         <v>79116860524513</v>
       </c>
-      <c r="C168" t="s">
+      <c r="C168" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D168">
+      <c r="D168" s="1">
         <v>875266000</v>
       </c>
-      <c r="F168">
+      <c r="F168" s="1">
         <v>8</v>
       </c>
     </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A169" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A171" s="1">
         <v>79117696250946</v>
       </c>
-      <c r="C171" t="s">
+      <c r="C171" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="F171">
+      <c r="F171" s="1">
         <v>7</v>
       </c>
-    </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G171" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="173" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A173" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="C173" t="s">
+      <c r="C173" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D173">
+      <c r="D173" s="1">
         <v>926666568</v>
       </c>
-      <c r="F173">
+      <c r="F173" s="1">
         <v>114</v>
       </c>
     </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A174" s="1">
         <v>8258794480420</v>
       </c>
     </row>
+    <row r="175" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G175" s="8" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="178" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C178" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="F178" s="1">
+        <v>6</v>
+      </c>
+      <c r="G178" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="186" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C186" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D186" s="1">
+        <v>555572809</v>
+      </c>
+    </row>
+    <row r="189" spans="1:7" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A189" s="11">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="190" spans="1:7" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A190" s="6"/>
+      <c r="B190" s="4">
+        <v>197</v>
+      </c>
+      <c r="C190" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="D190" s="4">
+        <v>9261111168</v>
+      </c>
+      <c r="E190" s="4">
+        <v>22</v>
+      </c>
+      <c r="F190" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="G190" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="193" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A193" s="1">
+        <v>777423531486346</v>
+      </c>
+      <c r="B193" s="1">
+        <v>303</v>
+      </c>
+      <c r="C193" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D193" s="1">
+        <v>927370091</v>
+      </c>
+    </row>
+    <row r="194" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A194" s="1">
+        <v>79118373286841</v>
+      </c>
+      <c r="B194" s="1">
+        <v>319</v>
+      </c>
+      <c r="C194" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="195" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A195" s="1">
+        <v>79015519961480</v>
+      </c>
+      <c r="B195" s="1">
+        <v>162</v>
+      </c>
+      <c r="C195" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="196" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A196" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B196" s="1">
+        <v>151</v>
+      </c>
+      <c r="C196" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="197" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A197" s="1">
+        <v>79118367875866</v>
+      </c>
+      <c r="B197" s="1">
+        <v>54</v>
+      </c>
+      <c r="C197" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="198" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A198" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B198" s="1">
+        <v>118</v>
+      </c>
+      <c r="C198" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="199" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A199" s="1">
+        <v>79118257588609</v>
+      </c>
+      <c r="B199" s="1">
+        <v>53</v>
+      </c>
+      <c r="C199" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="200" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A200" s="1">
+        <v>79118276902896</v>
+      </c>
+      <c r="B200" s="1">
+        <v>65</v>
+      </c>
+      <c r="C200" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="D200" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="201" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A201" s="1">
+        <v>465465103750961</v>
+      </c>
+      <c r="B201" s="1">
+        <v>43</v>
+      </c>
+      <c r="C201" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="202" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A202" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B202" s="1">
+        <v>52</v>
+      </c>
+      <c r="C202" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="203" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A203" s="1">
+        <v>777423269005541</v>
+      </c>
+      <c r="B203" s="1">
+        <v>84</v>
+      </c>
+      <c r="C203" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="204" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B204" s="1">
+        <v>64.400000000000006</v>
+      </c>
+      <c r="C204" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="205" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B205" s="1">
+        <v>50.6</v>
+      </c>
+      <c r="C205" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="F205" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="206" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B206" s="1">
+        <v>46</v>
+      </c>
+      <c r="C206" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="207" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B207" s="1">
+        <v>48.3</v>
+      </c>
+      <c r="C207" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="208" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B208" s="1">
+        <v>51.75</v>
+      </c>
+      <c r="C208" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="209" spans="1:7" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B209" s="1">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="210" spans="1:7" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A210" s="6"/>
+      <c r="B210" s="4">
+        <f>SUM(B193:B209)</f>
+        <v>1726.05</v>
+      </c>
+      <c r="C210" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D210" s="4">
+        <v>927370091</v>
+      </c>
+      <c r="E210" s="4"/>
+      <c r="F210" s="4"/>
+      <c r="G210" s="12"/>
+    </row>
+    <row r="211" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B211" s="1">
+        <v>15</v>
+      </c>
+      <c r="C211" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D211" s="1">
+        <v>112011777</v>
+      </c>
+      <c r="E211" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="F211" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="212" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B212" s="1">
+        <v>46</v>
+      </c>
+      <c r="C212" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D212" s="1">
+        <v>928448707</v>
+      </c>
+      <c r="E212" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="G212" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="213" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B213" s="1">
+        <v>21</v>
+      </c>
+      <c r="C213" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D213" s="1">
+        <v>555199996</v>
+      </c>
+      <c r="E213" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="G213" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="214" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B214" s="1">
+        <v>12</v>
+      </c>
+      <c r="C214" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="D214" s="1">
+        <v>929423172</v>
+      </c>
+      <c r="E214" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="F214" s="1">
+        <v>7</v>
+      </c>
+      <c r="G214" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="215" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B215" s="1">
+        <v>68</v>
+      </c>
+      <c r="C215" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D215" s="1">
+        <v>929279300</v>
+      </c>
+      <c r="E215" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="G215" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="216" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B216" s="1">
+        <v>45</v>
+      </c>
+      <c r="C216" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E216" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="G216" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="217" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B217" s="1">
+        <v>6</v>
+      </c>
+      <c r="C217" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D217" s="1">
+        <v>555572809</v>
+      </c>
+      <c r="E217" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="G217" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="218" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B218" s="1">
+        <v>72.45</v>
+      </c>
+      <c r="C218" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D218" s="1">
+        <v>557009840</v>
+      </c>
+      <c r="E218" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="G218" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="219" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B219" s="1">
+        <v>11.25</v>
+      </c>
+      <c r="C219" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D219" s="1">
+        <v>975413355</v>
+      </c>
+      <c r="E219" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="F219" s="1">
+        <v>4</v>
+      </c>
+      <c r="G219" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="220" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B220" s="1">
+        <v>17.25</v>
+      </c>
+      <c r="C220" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D220" s="1">
+        <v>992007998786</v>
+      </c>
+      <c r="E220" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="F220" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="221" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B221" s="1">
+        <v>143.75</v>
+      </c>
+      <c r="C221" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D221" s="1">
+        <v>923335522</v>
+      </c>
+      <c r="E221" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="G221" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="222" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B222" s="1">
+        <v>101</v>
+      </c>
+      <c r="C222" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="G222" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="223" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B223" s="1">
+        <v>31</v>
+      </c>
+      <c r="C223" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="D223" s="1">
+        <v>111905191</v>
+      </c>
+      <c r="F223" s="1">
+        <v>12</v>
+      </c>
+      <c r="G223" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="224" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B224" s="1">
+        <v>66.7</v>
+      </c>
+      <c r="C224" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="D224" s="1">
+        <v>975990050</v>
+      </c>
+      <c r="E224" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="F224" s="1">
+        <v>20</v>
+      </c>
+      <c r="G224" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="225" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B225" s="1">
+        <v>247</v>
+      </c>
+      <c r="C225" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E225" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="G225" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="226" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B226" s="1">
+        <v>10</v>
+      </c>
+      <c r="C226" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D226" s="1">
+        <v>929589803</v>
+      </c>
+      <c r="E226" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="F226" s="1">
+        <v>5</v>
+      </c>
+      <c r="G226" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="227" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B227" s="1">
+        <v>216</v>
+      </c>
+      <c r="C227" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G227" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="228" spans="1:7" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A228" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B228" s="10">
+        <v>5</v>
+      </c>
+      <c r="C228" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D228" s="1">
+        <v>877328108</v>
+      </c>
+      <c r="E228" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="F228" s="1">
+        <v>2</v>
+      </c>
+      <c r="G228" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="229" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B229" s="1">
+        <v>21</v>
+      </c>
+      <c r="C229" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="D229" s="1">
+        <v>926600610</v>
+      </c>
+      <c r="E229" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="G229" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="230" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B230" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="C230" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="D230" s="1">
+        <v>789060649</v>
+      </c>
+      <c r="E230" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="231" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B231" s="1">
+        <v>1</v>
+      </c>
+      <c r="C231" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D231" s="1">
+        <v>927619239</v>
+      </c>
+      <c r="E231" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="G231" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="232" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B232" s="1">
+        <v>1</v>
+      </c>
+      <c r="C232" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D232" s="1">
+        <v>929990996</v>
+      </c>
+      <c r="E232" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="233" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B233" s="1">
+        <v>2.7</v>
+      </c>
+      <c r="C233" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="D233" s="1">
+        <v>927107034</v>
+      </c>
+      <c r="E233" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="G233" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="234" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B234" s="1">
+        <v>141</v>
+      </c>
+      <c r="C234" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D234" s="1">
+        <v>785266000</v>
+      </c>
+      <c r="G234" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="0" orientation="portrait" horizontalDpi="0" verticalDpi="0" copies="0"/>
 </worksheet>
 </file>
 

--- a/zafarabad.xlsx
+++ b/zafarabad.xlsx
@@ -12,11 +12,12 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="145621"/>
+  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="164">
   <si>
     <t>Track</t>
   </si>
@@ -352,13 +353,169 @@
   </si>
   <si>
     <t>OZODA</t>
+  </si>
+  <si>
+    <t>JT5502070896573</t>
+  </si>
+  <si>
+    <t>10luly</t>
+  </si>
+  <si>
+    <t>marhabo</t>
+  </si>
+  <si>
+    <t>ismoilzoda N</t>
+  </si>
+  <si>
+    <t>JT5502063985498</t>
+  </si>
+  <si>
+    <t>YT8884336503775</t>
+  </si>
+  <si>
+    <t>BEHRUZ</t>
+  </si>
+  <si>
+    <t>JT5502586459458</t>
+  </si>
+  <si>
+    <t>JT5502515695069</t>
+  </si>
+  <si>
+    <t>JT5502578278301</t>
+  </si>
+  <si>
+    <t>JT5502579705752</t>
+  </si>
+  <si>
+    <t>MUNIRA</t>
+  </si>
+  <si>
+    <t>TEL:009338407</t>
+  </si>
+  <si>
+    <t>JT5502253986072</t>
+  </si>
+  <si>
+    <t>JT5502242836349</t>
+  </si>
+  <si>
+    <t>YT8883878440548</t>
+  </si>
+  <si>
+    <t>YT8884117072986</t>
+  </si>
+  <si>
+    <t>YT8884489615042</t>
+  </si>
+  <si>
+    <t>YT8883878678840</t>
+  </si>
+  <si>
+    <t>YT8883891190132</t>
+  </si>
+  <si>
+    <t>YT8883903450609</t>
+  </si>
+  <si>
+    <t>YT8883932774068</t>
+  </si>
+  <si>
+    <t>JT5502803401712</t>
+  </si>
+  <si>
+    <t>YT8883889378511</t>
+  </si>
+  <si>
+    <t>JT9001357075546</t>
+  </si>
+  <si>
+    <t>JT5502741718081</t>
+  </si>
+  <si>
+    <t>JT5502038877683</t>
+  </si>
+  <si>
+    <t>YT8884426509513</t>
+  </si>
+  <si>
+    <t>JT5502695633268</t>
+  </si>
+  <si>
+    <t>JT5502750696507</t>
+  </si>
+  <si>
+    <t>JT5502797492566</t>
+  </si>
+  <si>
+    <t>49.5+25.5+83+42.6+46</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>ALISHER 1777</t>
+  </si>
+  <si>
+    <t>YT8884120626190</t>
+  </si>
+  <si>
+    <t>JT5501949529727</t>
+  </si>
+  <si>
+    <t>JT5502224005826</t>
+  </si>
+  <si>
+    <t>JT5502298396291</t>
+  </si>
+  <si>
+    <t>RAUF</t>
+  </si>
+  <si>
+    <t>21+65.6</t>
+  </si>
+  <si>
+    <t>42.7+47.15</t>
+  </si>
+  <si>
+    <t>alisher sanginov</t>
+  </si>
+  <si>
+    <t>YT8883447163830</t>
+  </si>
+  <si>
+    <t>bobojon</t>
+  </si>
+  <si>
+    <t>64+59</t>
+  </si>
+  <si>
+    <t>sumaya</t>
+  </si>
+  <si>
+    <t>JT5503266812933</t>
+  </si>
+  <si>
+    <t>Nurmurod holiqov</t>
+  </si>
+  <si>
+    <t>Muzhda</t>
+  </si>
+  <si>
+    <t>Nargis Oqilova</t>
+  </si>
+  <si>
+    <t>YT8884258229922</t>
+  </si>
+  <si>
+    <t>YT8884389671506</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -377,6 +534,14 @@
     <font>
       <sz val="16"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -445,10 +610,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -486,8 +652,15 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -787,15 +960,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J234"/>
+  <dimension ref="A1:J359"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.88671875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="10.44140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="24.6640625" style="1" customWidth="1"/>
     <col min="3" max="3" width="19.77734375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="19.21875" style="1" customWidth="1"/>
-    <col min="5" max="6" width="8.88671875" style="1"/>
-    <col min="7" max="7" width="8.88671875" style="8"/>
+    <col min="4" max="4" width="25" style="1" customWidth="1"/>
+    <col min="5" max="5" width="8.88671875" style="1"/>
+    <col min="6" max="6" width="8.88671875" style="8"/>
+    <col min="7" max="7" width="13.33203125" style="8" bestFit="1" customWidth="1"/>
     <col min="8" max="10" width="8.88671875" style="1"/>
     <col min="11" max="11" width="10" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="16384" width="8.88671875" style="1"/>
@@ -891,7 +1065,7 @@
       <c r="D13" s="1">
         <v>926111168</v>
       </c>
-      <c r="F13" s="1">
+      <c r="F13" s="8">
         <v>5.5</v>
       </c>
     </row>
@@ -902,7 +1076,7 @@
       <c r="C14" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F14" s="1">
+      <c r="F14" s="8">
         <v>0.51</v>
       </c>
     </row>
@@ -913,7 +1087,7 @@
       <c r="C15" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F15" s="1">
+      <c r="F15" s="8">
         <v>1.32</v>
       </c>
     </row>
@@ -1083,7 +1257,7 @@
       <c r="D39" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="F39" s="1">
+      <c r="F39" s="8">
         <v>2.6880000000000002</v>
       </c>
     </row>
@@ -1204,7 +1378,7 @@
       <c r="D56" s="1">
         <v>928770009</v>
       </c>
-      <c r="F56" s="1">
+      <c r="F56" s="8">
         <v>0.7</v>
       </c>
     </row>
@@ -1236,7 +1410,7 @@
       <c r="C61" s="2"/>
       <c r="D61" s="2"/>
       <c r="E61" s="2"/>
-      <c r="F61" s="2"/>
+      <c r="F61" s="9"/>
       <c r="G61" s="9"/>
     </row>
     <row r="62" spans="1:7" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -1250,7 +1424,7 @@
       <c r="E62" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="F62" s="7" t="s">
+      <c r="F62" s="12" t="s">
         <v>45</v>
       </c>
     </row>
@@ -1261,7 +1435,7 @@
       <c r="E63" s="1">
         <v>9</v>
       </c>
-      <c r="F63" s="1">
+      <c r="F63" s="8">
         <v>109</v>
       </c>
       <c r="G63" s="8" t="s">
@@ -1275,7 +1449,7 @@
       <c r="E64" s="1">
         <v>8</v>
       </c>
-      <c r="F64" s="1">
+      <c r="F64" s="8">
         <v>15</v>
       </c>
       <c r="G64" s="8" t="s">
@@ -1286,7 +1460,7 @@
       <c r="C65" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="F65" s="1">
+      <c r="F65" s="8">
         <v>18.399999999999999</v>
       </c>
       <c r="G65" s="8" t="s">
@@ -1300,7 +1474,7 @@
       <c r="E66" s="1">
         <v>2</v>
       </c>
-      <c r="F66" s="1">
+      <c r="F66" s="8">
         <v>46.75</v>
       </c>
       <c r="G66" s="8" t="s">
@@ -1314,7 +1488,7 @@
       <c r="E67" s="1">
         <v>1</v>
       </c>
-      <c r="F67" s="1">
+      <c r="F67" s="8">
         <v>12</v>
       </c>
       <c r="G67" s="8" t="s">
@@ -1328,7 +1502,7 @@
       <c r="E68" s="1">
         <v>1</v>
       </c>
-      <c r="F68" s="1">
+      <c r="F68" s="8">
         <v>4</v>
       </c>
       <c r="G68" s="8" t="s">
@@ -1342,7 +1516,7 @@
       <c r="E69" s="1">
         <v>1</v>
       </c>
-      <c r="F69" s="1">
+      <c r="F69" s="8">
         <v>146</v>
       </c>
       <c r="G69" s="8" t="s">
@@ -1359,7 +1533,7 @@
       <c r="E70" s="1">
         <v>1</v>
       </c>
-      <c r="F70" s="1">
+      <c r="F70" s="8">
         <v>2</v>
       </c>
       <c r="G70" s="8" t="s">
@@ -1373,7 +1547,7 @@
       <c r="E71" s="1">
         <v>2</v>
       </c>
-      <c r="F71" s="1">
+      <c r="F71" s="8">
         <v>48</v>
       </c>
       <c r="G71" s="8" t="s">
@@ -1387,7 +1561,7 @@
       <c r="E72" s="1">
         <v>2</v>
       </c>
-      <c r="F72" s="1">
+      <c r="F72" s="8">
         <v>1</v>
       </c>
       <c r="G72" s="8" t="s">
@@ -1401,7 +1575,7 @@
       <c r="E73" s="1">
         <v>3</v>
       </c>
-      <c r="F73" s="1">
+      <c r="F73" s="8">
         <v>15</v>
       </c>
     </row>
@@ -1412,7 +1586,7 @@
       <c r="E74" s="1">
         <v>1</v>
       </c>
-      <c r="F74" s="1">
+      <c r="F74" s="8">
         <v>3</v>
       </c>
       <c r="G74" s="8" t="s">
@@ -1426,7 +1600,7 @@
       <c r="E75" s="1">
         <v>1</v>
       </c>
-      <c r="F75" s="1">
+      <c r="F75" s="8">
         <v>28</v>
       </c>
     </row>
@@ -1437,7 +1611,7 @@
       <c r="E76" s="1">
         <v>4</v>
       </c>
-      <c r="F76" s="1">
+      <c r="F76" s="8">
         <v>27.6</v>
       </c>
     </row>
@@ -1448,7 +1622,7 @@
       <c r="E77" s="1">
         <v>17</v>
       </c>
-      <c r="F77" s="1">
+      <c r="F77" s="8">
         <v>93</v>
       </c>
       <c r="G77" s="8" t="s">
@@ -1462,7 +1636,7 @@
       <c r="E78" s="1">
         <v>25</v>
       </c>
-      <c r="F78" s="1">
+      <c r="F78" s="8">
         <v>185</v>
       </c>
       <c r="G78" s="8" t="s">
@@ -1474,7 +1648,7 @@
         <f>SUM(E63:E78)</f>
         <v>78</v>
       </c>
-      <c r="F79" s="7">
+      <c r="F79" s="12">
         <f>SUM(F63:F78)</f>
         <v>753.75</v>
       </c>
@@ -1489,7 +1663,7 @@
       <c r="D82" s="1">
         <v>921779435</v>
       </c>
-      <c r="F82" s="1">
+      <c r="F82" s="8">
         <v>44</v>
       </c>
       <c r="G82" s="8" t="s">
@@ -1544,7 +1718,7 @@
       <c r="D91" s="1">
         <v>929264050</v>
       </c>
-      <c r="F91" s="1">
+      <c r="F91" s="8">
         <v>29</v>
       </c>
     </row>
@@ -1558,7 +1732,7 @@
       <c r="D93" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="F93" s="1">
+      <c r="F93" s="8">
         <v>3</v>
       </c>
     </row>
@@ -1577,7 +1751,7 @@
       <c r="D96" s="1">
         <v>925882853</v>
       </c>
-      <c r="F96" s="1">
+      <c r="F96" s="8">
         <v>1</v>
       </c>
     </row>
@@ -1591,7 +1765,7 @@
       <c r="D98" s="1">
         <v>923335522</v>
       </c>
-      <c r="F98" s="1">
+      <c r="F98" s="8">
         <v>117</v>
       </c>
     </row>
@@ -1655,7 +1829,7 @@
       <c r="D110" s="1">
         <v>928252494</v>
       </c>
-      <c r="F110" s="1">
+      <c r="F110" s="8">
         <v>46</v>
       </c>
     </row>
@@ -1714,7 +1888,7 @@
       <c r="D121" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="F121" s="1">
+      <c r="F121" s="8">
         <v>14</v>
       </c>
       <c r="G121" s="8" t="s">
@@ -1739,7 +1913,7 @@
       <c r="D124" s="1">
         <v>557009840</v>
       </c>
-      <c r="F124" s="1">
+      <c r="F124" s="8">
         <v>70.5</v>
       </c>
     </row>
@@ -1811,7 +1985,7 @@
       <c r="D137" s="1">
         <v>920171229</v>
       </c>
-      <c r="F137" s="1">
+      <c r="F137" s="8">
         <v>8.5</v>
       </c>
     </row>
@@ -1835,7 +2009,7 @@
       <c r="D141" s="1">
         <v>975413355</v>
       </c>
-      <c r="F141" s="1">
+      <c r="F141" s="8">
         <v>54</v>
       </c>
     </row>
@@ -1909,7 +2083,7 @@
       <c r="D155" s="1">
         <v>929279300</v>
       </c>
-      <c r="F155" s="1">
+      <c r="F155" s="8">
         <v>141</v>
       </c>
       <c r="G155" s="8" t="s">
@@ -1951,7 +2125,7 @@
       <c r="D162" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="F162" s="1">
+      <c r="F162" s="8">
         <v>15</v>
       </c>
       <c r="G162" s="8" t="s">
@@ -1988,7 +2162,7 @@
       <c r="D168" s="1">
         <v>875266000</v>
       </c>
-      <c r="F168" s="1">
+      <c r="F168" s="8">
         <v>8</v>
       </c>
     </row>
@@ -2004,7 +2178,7 @@
       <c r="C171" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="F171" s="1">
+      <c r="F171" s="8">
         <v>7</v>
       </c>
       <c r="G171" s="8" t="s">
@@ -2021,7 +2195,7 @@
       <c r="D173" s="1">
         <v>926666568</v>
       </c>
-      <c r="F173" s="1">
+      <c r="F173" s="8">
         <v>114</v>
       </c>
     </row>
@@ -2039,7 +2213,7 @@
       <c r="C178" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="F178" s="1">
+      <c r="F178" s="8">
         <v>6</v>
       </c>
       <c r="G178" s="8" t="s">
@@ -2073,7 +2247,7 @@
       <c r="E190" s="4">
         <v>22</v>
       </c>
-      <c r="F190" s="7" t="s">
+      <c r="F190" s="12" t="s">
         <v>85</v>
       </c>
       <c r="G190" s="8" t="s">
@@ -2222,7 +2396,7 @@
       <c r="C205" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="F205" s="1" t="s">
+      <c r="F205" s="8" t="s">
         <v>99</v>
       </c>
     </row>
@@ -2268,7 +2442,7 @@
         <v>927370091</v>
       </c>
       <c r="E210" s="4"/>
-      <c r="F210" s="4"/>
+      <c r="F210" s="13"/>
       <c r="G210" s="12"/>
     </row>
     <row r="211" spans="1:7" x14ac:dyDescent="0.3">
@@ -2284,7 +2458,7 @@
       <c r="E211" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="F211" s="1">
+      <c r="F211" s="8">
         <v>3</v>
       </c>
     </row>
@@ -2335,7 +2509,7 @@
       <c r="E214" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="F214" s="1">
+      <c r="F214" s="8">
         <v>7</v>
       </c>
       <c r="G214" s="8" t="s">
@@ -2420,7 +2594,7 @@
       <c r="E219" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="F219" s="1">
+      <c r="F219" s="8">
         <v>4</v>
       </c>
       <c r="G219" s="8" t="s">
@@ -2440,7 +2614,7 @@
       <c r="E220" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="F220" s="1">
+      <c r="F220" s="8">
         <v>3</v>
       </c>
     </row>
@@ -2482,7 +2656,7 @@
       <c r="D223" s="1">
         <v>111905191</v>
       </c>
-      <c r="F223" s="1">
+      <c r="F223" s="8">
         <v>12</v>
       </c>
       <c r="G223" s="8" t="s">
@@ -2502,14 +2676,14 @@
       <c r="E224" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="F224" s="1">
+      <c r="F224" s="8">
         <v>20</v>
       </c>
       <c r="G224" s="8" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="225" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B225" s="1">
         <v>247</v>
       </c>
@@ -2523,7 +2697,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="226" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B226" s="1">
         <v>10</v>
       </c>
@@ -2536,14 +2710,14 @@
       <c r="E226" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="F226" s="1">
+      <c r="F226" s="8">
         <v>5</v>
       </c>
       <c r="G226" s="8" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="227" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B227" s="1">
         <v>216</v>
       </c>
@@ -2554,7 +2728,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="228" spans="1:7" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:10" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A228" s="1" t="s">
         <v>105</v>
       </c>
@@ -2570,14 +2744,14 @@
       <c r="E228" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="F228" s="1">
+      <c r="F228" s="8">
         <v>2</v>
       </c>
       <c r="G228" s="8" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="229" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B229" s="1">
         <v>21</v>
       </c>
@@ -2594,7 +2768,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="230" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B230" s="1">
         <v>1.5</v>
       </c>
@@ -2607,8 +2781,11 @@
       <c r="E230" s="1" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="231" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G230" s="8" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="231" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B231" s="1">
         <v>1</v>
       </c>
@@ -2625,7 +2802,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="232" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B232" s="1">
         <v>1</v>
       </c>
@@ -2639,7 +2816,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="233" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B233" s="1">
         <v>2.7</v>
       </c>
@@ -2656,7 +2833,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="234" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B234" s="1">
         <v>141</v>
       </c>
@@ -2670,7 +2847,738 @@
         <v>46</v>
       </c>
     </row>
+    <row r="236" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="237" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B237" s="4"/>
+      <c r="C237" s="4"/>
+      <c r="D237" s="4"/>
+      <c r="E237" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="F237" s="13"/>
+      <c r="G237" s="13"/>
+      <c r="H237" s="4"/>
+      <c r="I237" s="4"/>
+      <c r="J237" s="7"/>
+    </row>
+    <row r="238" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A238" s="1">
+        <v>465482477918590</v>
+      </c>
+      <c r="B238" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C238" s="1">
+        <v>929008811</v>
+      </c>
+      <c r="D238" s="1">
+        <v>24.15</v>
+      </c>
+      <c r="E238" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="239" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A239" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="240" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A240" s="1">
+        <v>9817833727780</v>
+      </c>
+      <c r="B240" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C240" s="1">
+        <v>878870899</v>
+      </c>
+      <c r="D240" s="1">
+        <v>23</v>
+      </c>
+      <c r="E240" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="241" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A241" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="242" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A242" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="243" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A243" s="1">
+        <v>9817824222503</v>
+      </c>
+    </row>
+    <row r="244" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A244" s="1">
+        <v>9817814907148</v>
+      </c>
+    </row>
+    <row r="245" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A245" s="1">
+        <v>777423826557941</v>
+      </c>
+      <c r="B245" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C245" s="1">
+        <v>877328108</v>
+      </c>
+      <c r="D245" s="1">
+        <v>29</v>
+      </c>
+      <c r="E245" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="246" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A246" s="1">
+        <v>79119333092366</v>
+      </c>
+    </row>
+    <row r="247" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A247" s="1">
+        <v>79119513045156</v>
+      </c>
+    </row>
+    <row r="248" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A248" s="1">
+        <v>777424563328445</v>
+      </c>
+    </row>
+    <row r="250" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B250" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C250" s="1">
+        <v>992007998786</v>
+      </c>
+      <c r="D250" s="1">
+        <v>44</v>
+      </c>
+      <c r="E250" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="251" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A251" s="1">
+        <v>79119334943698</v>
+      </c>
+    </row>
+    <row r="252" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A252" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="253" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A253" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="254" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A254" s="1">
+        <v>79119373863903</v>
+      </c>
+    </row>
+    <row r="255" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A255" s="1">
+        <v>9817726240838</v>
+      </c>
+    </row>
+    <row r="256" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A256" s="1">
+        <v>777423915519907</v>
+      </c>
+    </row>
+    <row r="257" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A257" s="1">
+        <v>465469564298701</v>
+      </c>
+    </row>
+    <row r="258" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A258" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="259" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A259" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="261" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B261" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C261" s="1">
+        <v>975413355</v>
+      </c>
+      <c r="D261" s="1">
+        <v>9.5</v>
+      </c>
+      <c r="E261" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="262" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A262" s="1">
+        <v>9817833357257</v>
+      </c>
+    </row>
+    <row r="263" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A263" s="1">
+        <v>465478836046637</v>
+      </c>
+    </row>
+    <row r="264" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A264" s="1">
+        <v>465478907911956</v>
+      </c>
+    </row>
+    <row r="266" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B266" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="C266" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="D266" s="1">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="267" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A267" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="268" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A268" s="1">
+        <v>465480645383240</v>
+      </c>
+    </row>
+    <row r="269" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A269" s="1">
+        <v>777424220162412</v>
+      </c>
+    </row>
+    <row r="270" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A270" s="1">
+        <v>79120061484942</v>
+      </c>
+    </row>
+    <row r="271" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A271" s="1">
+        <v>777424713674098</v>
+      </c>
+    </row>
+    <row r="272" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A272" s="1">
+        <v>777424752557155</v>
+      </c>
+    </row>
+    <row r="273" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A273" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="274" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A274" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="275" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A275" s="1">
+        <v>79016630818351</v>
+      </c>
+    </row>
+    <row r="276" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A276" s="1">
+        <v>79119699371877</v>
+      </c>
+    </row>
+    <row r="277" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A277" s="1">
+        <v>79119623086735</v>
+      </c>
+    </row>
+    <row r="278" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A278" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="280" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B280" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C280" s="1">
+        <v>927107034</v>
+      </c>
+      <c r="D280" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="E280" s="1">
+        <v>246.6</v>
+      </c>
+    </row>
+    <row r="281" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A281" s="1">
+        <v>777424241079598</v>
+      </c>
+    </row>
+    <row r="282" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A282" s="1">
+        <v>465478784045939</v>
+      </c>
+    </row>
+    <row r="283" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A283" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="284" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A284" s="1">
+        <v>9817817261348</v>
+      </c>
+    </row>
+    <row r="285" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A285" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="286" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A286" s="1">
+        <v>465476500993347</v>
+      </c>
+    </row>
+    <row r="287" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A287" s="1">
+        <v>465479013210690</v>
+      </c>
+    </row>
+    <row r="288" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A288" s="1">
+        <v>79120018634046</v>
+      </c>
+    </row>
+    <row r="289" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A289" s="1">
+        <v>9817817233388</v>
+      </c>
+    </row>
+    <row r="290" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A290" s="1" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="291" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A291" s="1">
+        <v>465478695635802</v>
+      </c>
+    </row>
+    <row r="292" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A292" s="1">
+        <v>79119902597646</v>
+      </c>
+    </row>
+    <row r="293" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A293" s="1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="294" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A294" s="1">
+        <v>79120061027112</v>
+      </c>
+    </row>
+    <row r="295" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A295" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="296" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A296" s="1">
+        <v>777424417209334</v>
+      </c>
+    </row>
+    <row r="297" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A297" s="1">
+        <v>777424168124852</v>
+      </c>
+    </row>
+    <row r="298" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A298" s="1">
+        <v>465476542484994</v>
+      </c>
+    </row>
+    <row r="299" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A299" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="300" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A300" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="301" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A301" s="1">
+        <v>465478890570558</v>
+      </c>
+    </row>
+    <row r="302" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A302" s="1">
+        <v>9817802550951</v>
+      </c>
+    </row>
+    <row r="303" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A303" s="1" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="304" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A304" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="305" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A305" s="1">
+        <v>777424342650506</v>
+      </c>
+    </row>
+    <row r="306" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A306" s="1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="307" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A307" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="308" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A308" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="309" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A309" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="310" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A310" s="1">
+        <v>79119935578123</v>
+      </c>
+    </row>
+    <row r="311" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A311" s="1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="312" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A312" s="1">
+        <v>777424450392984</v>
+      </c>
+    </row>
+    <row r="314" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B314" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="D314" s="1">
+        <v>27.6</v>
+      </c>
+    </row>
+    <row r="315" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A315" s="1">
+        <v>777423826557941</v>
+      </c>
+    </row>
+    <row r="316" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A316" s="1">
+        <v>777424563328445</v>
+      </c>
+    </row>
+    <row r="318" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B318" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D318" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="E318" s="1">
+        <v>86.6</v>
+      </c>
+    </row>
+    <row r="319" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A319" s="1" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="320" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A320" s="1">
+        <v>79119353172438</v>
+      </c>
+    </row>
+    <row r="321" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A321" s="1">
+        <v>79119680373126</v>
+      </c>
+    </row>
+    <row r="322" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A322" s="1">
+        <v>79119364223825</v>
+      </c>
+    </row>
+    <row r="323" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A323" s="1">
+        <v>465481632912782</v>
+      </c>
+    </row>
+    <row r="324" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A324" s="1">
+        <v>9817744360683</v>
+      </c>
+    </row>
+    <row r="325" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A325" s="1">
+        <v>79119682173315</v>
+      </c>
+    </row>
+    <row r="326" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A326" s="1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="327" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A327" s="1">
+        <v>465480494417993</v>
+      </c>
+    </row>
+    <row r="328" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A328" s="1" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="329" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A329" s="1" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="330" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A330" s="1">
+        <v>465470049614367</v>
+      </c>
+    </row>
+    <row r="332" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B332" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="C332" s="1">
+        <v>114441122</v>
+      </c>
+      <c r="D332" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="E332" s="1">
+        <v>89.85</v>
+      </c>
+    </row>
+    <row r="333" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A333" s="1">
+        <v>9817844495105</v>
+      </c>
+    </row>
+    <row r="334" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A334" s="1">
+        <v>9817874570506</v>
+      </c>
+    </row>
+    <row r="335" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A335" s="1">
+        <v>9817842086178</v>
+      </c>
+    </row>
+    <row r="336" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A336" s="1">
+        <v>79120384923273</v>
+      </c>
+    </row>
+    <row r="337" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A337" s="1">
+        <v>777424953542826</v>
+      </c>
+    </row>
+    <row r="338" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A338" s="1">
+        <v>777424993812033</v>
+      </c>
+    </row>
+    <row r="339" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A339" s="1">
+        <v>79120332036445</v>
+      </c>
+    </row>
+    <row r="340" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A340" s="1">
+        <v>79120328238119</v>
+      </c>
+    </row>
+    <row r="343" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B343" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="D343" s="1">
+        <v>12.7</v>
+      </c>
+      <c r="F343" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="344" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A344" s="1" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="345" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A345" s="1">
+        <v>777424019456798</v>
+      </c>
+    </row>
+    <row r="347" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B347" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="C347" s="1">
+        <v>903320005</v>
+      </c>
+      <c r="D347" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E347" s="1">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="348" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A348" s="1">
+        <v>79120038283526</v>
+      </c>
+    </row>
+    <row r="349" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A349" s="1">
+        <v>777424361174079</v>
+      </c>
+    </row>
+    <row r="350" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A350" s="1">
+        <v>465479229384518</v>
+      </c>
+    </row>
+    <row r="352" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A352" s="1">
+        <v>777423993882325</v>
+      </c>
+      <c r="B352" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C352" s="1">
+        <v>927619239</v>
+      </c>
+      <c r="F352" s="8" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="353" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A353" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="B353" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="C353" s="1">
+        <v>111710460</v>
+      </c>
+      <c r="D353" s="1">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="F353" s="8" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="354" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A354" s="1">
+        <v>79119416390403</v>
+      </c>
+      <c r="B354" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C354" s="1">
+        <v>928448707</v>
+      </c>
+    </row>
+    <row r="355" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A355" s="1">
+        <v>465471994471730</v>
+      </c>
+      <c r="B355" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C355" s="1">
+        <v>975990050</v>
+      </c>
+    </row>
+    <row r="356" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A356" s="1">
+        <v>79016454897614</v>
+      </c>
+      <c r="B356" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C356" s="1">
+        <v>926666568</v>
+      </c>
+      <c r="F356" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="357" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A357" s="1">
+        <v>465473534442564</v>
+      </c>
+      <c r="B357" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="C357" s="1">
+        <v>923335522</v>
+      </c>
+    </row>
+    <row r="358" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A358" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B358" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="C358" s="1">
+        <v>928620319</v>
+      </c>
+      <c r="F358" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="359" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A359" s="1" t="s">
+        <v>163</v>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C266" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="0" orientation="portrait" horizontalDpi="0" verticalDpi="0" copies="0"/>
 </worksheet>

--- a/zafarabad.xlsx
+++ b/zafarabad.xlsx
@@ -12,12 +12,11 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="145621"/>
-  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="165">
   <si>
     <t>Track</t>
   </si>
@@ -509,6 +508,9 @@
   </si>
   <si>
     <t>YT8884389671506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    </t>
   </si>
 </sst>
 </file>
@@ -3566,6 +3568,9 @@
       <c r="C358" s="1">
         <v>928620319</v>
       </c>
+      <c r="D358" s="1" t="s">
+        <v>164</v>
+      </c>
       <c r="F358" s="8" t="s">
         <v>46</v>
       </c>

--- a/zafarabad.xlsx
+++ b/zafarabad.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="238">
   <si>
     <t>Track</t>
   </si>
@@ -450,9 +450,6 @@
     <t>49.5+25.5+83+42.6+46</t>
   </si>
   <si>
-    <t>-</t>
-  </si>
-  <si>
     <t>ALISHER 1777</t>
   </si>
   <si>
@@ -511,13 +508,235 @@
   </si>
   <si>
     <t xml:space="preserve">    </t>
+  </si>
+  <si>
+    <t>JT5505282889514</t>
+  </si>
+  <si>
+    <t>YT7632675835236</t>
+  </si>
+  <si>
+    <t>RASHID  0166</t>
+  </si>
+  <si>
+    <t>ARASH</t>
+  </si>
+  <si>
+    <t>JT5503614888010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">feychka </t>
+  </si>
+  <si>
+    <t>t000012506</t>
+  </si>
+  <si>
+    <t>JT5504825809292</t>
+  </si>
+  <si>
+    <t>rabe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">zayka </t>
+  </si>
+  <si>
+    <t xml:space="preserve">nargis oqilova </t>
+  </si>
+  <si>
+    <t>sunatullo</t>
+  </si>
+  <si>
+    <t>davlat</t>
+  </si>
+  <si>
+    <t>JT5505201778852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">firuz </t>
+  </si>
+  <si>
+    <t>YT8885905743570</t>
+  </si>
+  <si>
+    <t xml:space="preserve">habibullo </t>
+  </si>
+  <si>
+    <t xml:space="preserve">alisher </t>
+  </si>
+  <si>
+    <t>maftuna</t>
+  </si>
+  <si>
+    <t>dalersho</t>
+  </si>
+  <si>
+    <t>YT8886196738528</t>
+  </si>
+  <si>
+    <t>nulufar</t>
+  </si>
+  <si>
+    <t>ruzikhon</t>
+  </si>
+  <si>
+    <t>yosamin</t>
+  </si>
+  <si>
+    <t>t002771712</t>
+  </si>
+  <si>
+    <t>JT3169788112207</t>
+  </si>
+  <si>
+    <t>GAYRAT</t>
+  </si>
+  <si>
+    <t>BUNYOD</t>
+  </si>
+  <si>
+    <t>JUSHQIN</t>
+  </si>
+  <si>
+    <t>JT5504998948258</t>
+  </si>
+  <si>
+    <t>JT5505255975481</t>
+  </si>
+  <si>
+    <t>dilshoda</t>
+  </si>
+  <si>
+    <t>YT8885969781930</t>
+  </si>
+  <si>
+    <t>Hilola</t>
+  </si>
+  <si>
+    <t>174+6.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sumaya </t>
+  </si>
+  <si>
+    <t>YT8884560989732</t>
+  </si>
+  <si>
+    <t>YT8884549928833</t>
+  </si>
+  <si>
+    <t>YT8884867106797</t>
+  </si>
+  <si>
+    <t>YT8884855694613</t>
+  </si>
+  <si>
+    <t>JT5503723040860</t>
+  </si>
+  <si>
+    <t>JT5503788424481</t>
+  </si>
+  <si>
+    <t>ULUGBEK</t>
+  </si>
+  <si>
+    <t>T073167337</t>
+  </si>
+  <si>
+    <t>JT5503934267516</t>
+  </si>
+  <si>
+    <t>JT5503946278929</t>
+  </si>
+  <si>
+    <t>JT5503909880771</t>
+  </si>
+  <si>
+    <t>JT5503665519773</t>
+  </si>
+  <si>
+    <t>JT5503980623746</t>
+  </si>
+  <si>
+    <t>YT7631737508840</t>
+  </si>
+  <si>
+    <t>Ogabek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MADINA </t>
+  </si>
+  <si>
+    <t>YT8884777619042</t>
+  </si>
+  <si>
+    <t>JT9001470362258</t>
+  </si>
+  <si>
+    <t>YT8884756076626</t>
+  </si>
+  <si>
+    <t>YT7631927398745</t>
+  </si>
+  <si>
+    <t>YT8884843406758</t>
+  </si>
+  <si>
+    <t>JT5503598011345</t>
+  </si>
+  <si>
+    <t>JT5503356984126</t>
+  </si>
+  <si>
+    <t>JT5503622166402</t>
+  </si>
+  <si>
+    <t>YT8884779828624</t>
+  </si>
+  <si>
+    <t>YT8884755194668</t>
+  </si>
+  <si>
+    <t>YT8884852002725</t>
+  </si>
+  <si>
+    <t>rauf</t>
+  </si>
+  <si>
+    <t>YT8884901508329</t>
+  </si>
+  <si>
+    <t>YT8885213220312</t>
+  </si>
+  <si>
+    <t>YT8884929245680</t>
+  </si>
+  <si>
+    <t>JT5503731539655</t>
+  </si>
+  <si>
+    <t>YT8884665198192</t>
+  </si>
+  <si>
+    <t>JT5503943390671</t>
+  </si>
+  <si>
+    <t>YT8884280552889</t>
+  </si>
+  <si>
+    <t>JT5503756413585</t>
+  </si>
+  <si>
+    <t>JT5503312311887</t>
+  </si>
+  <si>
+    <t>t002337873</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -544,6 +763,14 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -616,7 +843,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -658,6 +885,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -962,8 +1195,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J359"/>
-  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:J517"/>
+  <sheetFormatPr defaultRowHeight="15.6" outlineLevelRow="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.88671875" style="1" customWidth="1"/>
     <col min="2" max="2" width="24.6640625" style="1" customWidth="1"/>
@@ -1430,7 +1663,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:7" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C63" s="1" t="s">
         <v>8</v>
       </c>
@@ -1444,7 +1677,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:7" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C64" s="1" t="s">
         <v>30</v>
       </c>
@@ -1458,7 +1691,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:7" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C65" s="1" t="s">
         <v>42</v>
       </c>
@@ -1469,7 +1702,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:7" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C66" s="1" t="s">
         <v>31</v>
       </c>
@@ -1483,7 +1716,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:7" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C67" s="1" t="s">
         <v>4</v>
       </c>
@@ -1497,7 +1730,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:7" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C68" s="1" t="s">
         <v>32</v>
       </c>
@@ -1511,7 +1744,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:7" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C69" s="1" t="s">
         <v>33</v>
       </c>
@@ -1525,7 +1758,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:7" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A70" s="1">
         <v>777420502615652</v>
       </c>
@@ -1542,7 +1775,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:7" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C71" s="1" t="s">
         <v>35</v>
       </c>
@@ -1556,7 +1789,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:7" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C72" s="1" t="s">
         <v>36</v>
       </c>
@@ -1570,7 +1803,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:7" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C73" s="1" t="s">
         <v>18</v>
       </c>
@@ -1581,7 +1814,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:7" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C74" s="1" t="s">
         <v>37</v>
       </c>
@@ -1595,7 +1828,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:7" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C75" s="1" t="s">
         <v>38</v>
       </c>
@@ -1606,7 +1839,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:7" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C76" s="1" t="s">
         <v>39</v>
       </c>
@@ -1617,7 +1850,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:7" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C77" s="1" t="s">
         <v>40</v>
       </c>
@@ -1631,7 +1864,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="78" spans="1:7" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:7" ht="16.2" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C78" s="1" t="s">
         <v>11</v>
       </c>
@@ -2256,7 +2489,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="193" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:7" ht="21" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="A193" s="1">
         <v>777423531486346</v>
       </c>
@@ -2269,8 +2502,11 @@
       <c r="D193" s="1">
         <v>927370091</v>
       </c>
-    </row>
-    <row r="194" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E193" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="194" spans="1:7" ht="21" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="A194" s="1">
         <v>79118373286841</v>
       </c>
@@ -2280,8 +2516,11 @@
       <c r="C194" s="1" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="195" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E194" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="195" spans="1:7" ht="21" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="A195" s="1">
         <v>79015519961480</v>
       </c>
@@ -2291,8 +2530,11 @@
       <c r="C195" s="1" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="196" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E195" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="196" spans="1:7" ht="21" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="A196" s="1" t="s">
         <v>93</v>
       </c>
@@ -2302,8 +2544,11 @@
       <c r="C196" s="1" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="197" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E196" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="197" spans="1:7" ht="21" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="A197" s="1">
         <v>79118367875866</v>
       </c>
@@ -2313,8 +2558,11 @@
       <c r="C197" s="1" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="198" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E197" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="198" spans="1:7" ht="21" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="A198" s="1" t="s">
         <v>94</v>
       </c>
@@ -2324,8 +2572,11 @@
       <c r="C198" s="1" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="199" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E198" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="199" spans="1:7" ht="21" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="A199" s="1">
         <v>79118257588609</v>
       </c>
@@ -2335,8 +2586,14 @@
       <c r="C199" s="1" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="200" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E199" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="G199" s="8" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="200" spans="1:7" ht="21" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="A200" s="1">
         <v>79118276902896</v>
       </c>
@@ -2349,8 +2606,11 @@
       <c r="D200" s="1" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="201" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E200" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="201" spans="1:7" ht="21" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="A201" s="1">
         <v>465465103750961</v>
       </c>
@@ -2360,8 +2620,11 @@
       <c r="C201" s="1" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="202" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E201" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="202" spans="1:7" ht="21" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="A202" s="1" t="s">
         <v>95</v>
       </c>
@@ -2371,8 +2634,11 @@
       <c r="C202" s="1" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="203" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E202" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="203" spans="1:7" ht="21" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="A203" s="1">
         <v>777423269005541</v>
       </c>
@@ -2382,53 +2648,74 @@
       <c r="C203" s="1" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="204" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E203" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="204" spans="1:7" ht="21" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B204" s="1">
         <v>64.400000000000006</v>
       </c>
       <c r="C204" s="1" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="205" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E204" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="205" spans="1:7" ht="21" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B205" s="1">
         <v>50.6</v>
       </c>
       <c r="C205" s="1" t="s">
         <v>104</v>
       </c>
+      <c r="E205" s="15" t="s">
+        <v>46</v>
+      </c>
       <c r="F205" s="8" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="206" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:7" ht="21" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B206" s="1">
         <v>46</v>
       </c>
       <c r="C206" s="1" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="207" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E206" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="207" spans="1:7" ht="21" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B207" s="1">
         <v>48.3</v>
       </c>
       <c r="C207" s="1" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="208" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E207" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="208" spans="1:7" ht="21" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B208" s="1">
         <v>51.75</v>
       </c>
       <c r="C208" s="1" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="209" spans="1:7" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E208" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="209" spans="1:7" ht="21.6" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B209" s="1">
         <v>61</v>
+      </c>
+      <c r="E209" s="15" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="210" spans="1:7" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -2463,6 +2750,9 @@
       <c r="F211" s="8">
         <v>3</v>
       </c>
+      <c r="G211" s="8" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="212" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B212" s="1">
@@ -2619,6 +2909,9 @@
       <c r="F220" s="8">
         <v>3</v>
       </c>
+      <c r="G220" s="8" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B221" s="1">
@@ -2784,7 +3077,7 @@
         <v>104</v>
       </c>
       <c r="G230" s="8" t="s">
-        <v>144</v>
+        <v>46</v>
       </c>
     </row>
     <row r="231" spans="1:10" x14ac:dyDescent="0.3">
@@ -2816,6 +3109,9 @@
       </c>
       <c r="E232" s="1" t="s">
         <v>104</v>
+      </c>
+      <c r="G232" s="8" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="233" spans="1:10" x14ac:dyDescent="0.3">
@@ -3289,7 +3585,7 @@
     </row>
     <row r="314" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B314" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D314" s="1">
         <v>27.6</v>
@@ -3310,7 +3606,7 @@
         <v>59</v>
       </c>
       <c r="D318" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E318" s="1">
         <v>86.6</v>
@@ -3318,7 +3614,7 @@
     </row>
     <row r="319" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A319" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="320" spans="1:5" x14ac:dyDescent="0.3">
@@ -3353,7 +3649,7 @@
     </row>
     <row r="326" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A326" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="327" spans="1:5" x14ac:dyDescent="0.3">
@@ -3363,12 +3659,12 @@
     </row>
     <row r="328" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A328" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="329" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A329" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="330" spans="1:5" x14ac:dyDescent="0.3">
@@ -3378,13 +3674,13 @@
     </row>
     <row r="332" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B332" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C332" s="1">
         <v>114441122</v>
       </c>
       <c r="D332" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E332" s="1">
         <v>89.85</v>
@@ -3430,9 +3726,14 @@
         <v>79120328238119</v>
       </c>
     </row>
+    <row r="341" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A341" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
     <row r="343" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B343" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D343" s="1">
         <v>12.7</v>
@@ -3443,7 +3744,7 @@
     </row>
     <row r="344" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A344" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="345" spans="1:6" x14ac:dyDescent="0.3">
@@ -3453,13 +3754,13 @@
     </row>
     <row r="347" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B347" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C347" s="1">
         <v>903320005</v>
       </c>
       <c r="D347" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E347" s="1">
         <v>123</v>
@@ -3496,10 +3797,10 @@
     </row>
     <row r="353" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A353" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B353" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C353" s="1">
         <v>111710460</v>
@@ -3516,7 +3817,7 @@
         <v>79119416390403</v>
       </c>
       <c r="B354" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C354" s="1">
         <v>928448707</v>
@@ -3552,7 +3853,7 @@
         <v>465473534442564</v>
       </c>
       <c r="B357" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C357" s="1">
         <v>923335522</v>
@@ -3560,16 +3861,16 @@
     </row>
     <row r="358" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A358" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B358" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C358" s="1">
         <v>928620319</v>
       </c>
       <c r="D358" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F358" s="8" t="s">
         <v>46</v>
@@ -3577,7 +3878,1027 @@
     </row>
     <row r="359" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A359" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
+      </c>
+    </row>
+    <row r="361" spans="1:6" ht="16.2" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="362" spans="1:6" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A362" s="6"/>
+      <c r="B362" s="4"/>
+      <c r="C362" s="16">
+        <v>46218</v>
+      </c>
+      <c r="D362" s="4"/>
+      <c r="E362" s="4"/>
+      <c r="F362" s="12"/>
+    </row>
+    <row r="364" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A364" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B364" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="D364" s="1">
+        <v>19.600000000000001</v>
+      </c>
+      <c r="E364" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="365" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A365" s="1" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="367" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A367" s="1">
+        <v>777425532295679</v>
+      </c>
+      <c r="B367" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C367" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="D367" s="1">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="368" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A368" s="1">
+        <v>79120737015066</v>
+      </c>
+    </row>
+    <row r="369" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A369" s="1">
+        <v>465484039936407</v>
+      </c>
+    </row>
+    <row r="370" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A370" s="1">
+        <v>777425492400505</v>
+      </c>
+    </row>
+    <row r="371" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A371" s="1">
+        <v>9817917146012</v>
+      </c>
+    </row>
+    <row r="372" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A372" s="1" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="373" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A373" s="1">
+        <v>79120808394858</v>
+      </c>
+    </row>
+    <row r="374" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A374" s="1">
+        <v>9817949573418</v>
+      </c>
+      <c r="B374" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="C374" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="D374" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="376" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A376" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="B376" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C376" s="1">
+        <v>788870899</v>
+      </c>
+      <c r="D376" s="1">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="377" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A377" s="1">
+        <v>777425644089342</v>
+      </c>
+      <c r="B377" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="C377" s="1">
+        <v>557528888</v>
+      </c>
+      <c r="D377" s="1">
+        <v>9.1999999999999993</v>
+      </c>
+    </row>
+    <row r="379" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A379" s="1">
+        <v>9817958820639</v>
+      </c>
+      <c r="B379" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="C379" s="1">
+        <v>927324849</v>
+      </c>
+      <c r="D379" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="380" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A380" s="1">
+        <v>79121420106957</v>
+      </c>
+    </row>
+    <row r="381" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A381" s="1">
+        <v>79121527527448</v>
+      </c>
+    </row>
+    <row r="382" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A382" s="1">
+        <v>79120513891281</v>
+      </c>
+      <c r="B382" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="C382" s="1">
+        <v>928620319</v>
+      </c>
+      <c r="D382" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="383" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A383" s="1">
+        <v>465485939540824</v>
+      </c>
+    </row>
+    <row r="384" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A384" s="1">
+        <v>465485672986262</v>
+      </c>
+    </row>
+    <row r="385" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A385" s="1">
+        <v>777425075185916</v>
+      </c>
+      <c r="B385" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="C385" s="1">
+        <v>927619239</v>
+      </c>
+      <c r="D385" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="386" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A386" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="B386" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="C386" s="1">
+        <v>551117410</v>
+      </c>
+      <c r="D386" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="387" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A387" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B387" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="C387" s="1">
+        <v>926006881</v>
+      </c>
+      <c r="D387" s="1">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="388" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A388" s="1">
+        <v>465502104232434</v>
+      </c>
+    </row>
+    <row r="389" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A389" s="1">
+        <v>9817943793166</v>
+      </c>
+      <c r="B389" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="C389" s="1">
+        <v>787740466</v>
+      </c>
+      <c r="D389" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="390" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A390" s="1">
+        <v>773430169099707</v>
+      </c>
+      <c r="B390" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="C390" s="1">
+        <v>112011777</v>
+      </c>
+      <c r="D390" s="1">
+        <v>40.299999999999997</v>
+      </c>
+    </row>
+    <row r="391" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A391" s="1">
+        <v>9817951581468</v>
+      </c>
+      <c r="B391" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="C391" s="1">
+        <v>921114585</v>
+      </c>
+      <c r="D391" s="1">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="392" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A392" s="1">
+        <v>465486424671792</v>
+      </c>
+      <c r="B392" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="C392" s="1">
+        <v>929999377</v>
+      </c>
+      <c r="D392" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="393" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A393" s="1" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="394" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A394" s="1">
+        <v>465501494935518</v>
+      </c>
+    </row>
+    <row r="395" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A395" s="1">
+        <v>777424952568763</v>
+      </c>
+      <c r="B395" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="C395" s="1">
+        <v>975413355</v>
+      </c>
+      <c r="D395" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="396" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A396" s="1">
+        <v>465494207464740</v>
+      </c>
+      <c r="B396" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="C396" s="1">
+        <v>926092296</v>
+      </c>
+      <c r="D396" s="1">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="397" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A397" s="1">
+        <v>465484052406977</v>
+      </c>
+    </row>
+    <row r="398" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A398" s="1">
+        <v>777426778488134</v>
+      </c>
+      <c r="B398" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="C398" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="D398" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="399" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A399" s="1">
+        <v>79121636735126</v>
+      </c>
+    </row>
+    <row r="400" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A400" s="1">
+        <v>79121727019157</v>
+      </c>
+    </row>
+    <row r="401" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A401" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B401" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C401" s="1">
+        <v>927427222</v>
+      </c>
+      <c r="D401" s="1">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="402" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A402" s="1">
+        <v>465486045639866</v>
+      </c>
+      <c r="B402" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="C402" s="1">
+        <v>934145544</v>
+      </c>
+      <c r="D402" s="1">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="403" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A403" s="1">
+        <v>777425029418984</v>
+      </c>
+    </row>
+    <row r="404" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A404" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="B404" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="C404" s="1">
+        <v>928977321</v>
+      </c>
+      <c r="D404" s="1">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="405" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A405" s="1" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="406" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A406" s="1">
+        <v>79121799191425</v>
+      </c>
+    </row>
+    <row r="407" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A407" s="1">
+        <v>777426502141976</v>
+      </c>
+    </row>
+    <row r="408" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A408" s="1">
+        <v>465501199601972</v>
+      </c>
+    </row>
+    <row r="409" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A409" s="1">
+        <v>79121618345607</v>
+      </c>
+    </row>
+    <row r="410" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A410" s="1">
+        <v>9817966082788</v>
+      </c>
+    </row>
+    <row r="411" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A411" s="1">
+        <v>79121981513759</v>
+      </c>
+      <c r="B411" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="C411" s="1">
+        <v>928230848</v>
+      </c>
+    </row>
+    <row r="412" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A412" s="1">
+        <v>79121800010852</v>
+      </c>
+    </row>
+    <row r="413" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A413" s="1">
+        <v>9817971903882</v>
+      </c>
+    </row>
+    <row r="414" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A414" s="1">
+        <v>9817955045050</v>
+      </c>
+    </row>
+    <row r="415" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A415" s="1">
+        <v>79121608498840</v>
+      </c>
+    </row>
+    <row r="416" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A416" s="1" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="417" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A417" s="1">
+        <v>65684684654</v>
+      </c>
+    </row>
+    <row r="418" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A418" s="1">
+        <v>777425546939086</v>
+      </c>
+      <c r="B418" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="C418" s="1">
+        <v>555572809</v>
+      </c>
+      <c r="D418" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="419" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A419" s="1">
+        <v>465493047946239</v>
+      </c>
+    </row>
+    <row r="420" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A420" s="1">
+        <v>777425538961039</v>
+      </c>
+    </row>
+    <row r="421" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A421" s="1">
+        <v>9817900423455</v>
+      </c>
+    </row>
+    <row r="422" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A422" s="1">
+        <v>777426457494875</v>
+      </c>
+    </row>
+    <row r="423" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A423" s="1">
+        <v>79121004489806</v>
+      </c>
+      <c r="B423" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C423" s="1">
+        <v>111710460</v>
+      </c>
+      <c r="D423" s="1">
+        <v>56.4</v>
+      </c>
+    </row>
+    <row r="424" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A424" s="1">
+        <v>777425561922513</v>
+      </c>
+    </row>
+    <row r="425" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A425" s="1">
+        <v>9817883876957</v>
+      </c>
+    </row>
+    <row r="426" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A426" s="1" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="427" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A427" s="1" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="428" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A428" s="1" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="429" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A429" s="1" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="430" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A430" s="1">
+        <v>465483610812509</v>
+      </c>
+    </row>
+    <row r="431" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A431" s="1" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="432" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A432" s="1">
+        <v>79120583583816</v>
+      </c>
+    </row>
+    <row r="433" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A433" s="1">
+        <v>777425217523315</v>
+      </c>
+    </row>
+    <row r="434" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A434" s="1">
+        <v>79121035460932</v>
+      </c>
+    </row>
+    <row r="435" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A435" s="1" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="436" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A436" s="1">
+        <v>465493030554901</v>
+      </c>
+    </row>
+    <row r="437" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A437" s="1">
+        <v>79120859994050</v>
+      </c>
+    </row>
+    <row r="438" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A438" s="1">
+        <v>465493030554901</v>
+      </c>
+    </row>
+    <row r="439" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A439" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="B439" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="C439" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="D439" s="1">
+        <v>56.4</v>
+      </c>
+    </row>
+    <row r="440" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A440" s="1">
+        <v>9817857282681</v>
+      </c>
+      <c r="D440" s="1">
+        <v>40.25</v>
+      </c>
+    </row>
+    <row r="441" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A441" s="1">
+        <v>79120771222043</v>
+      </c>
+    </row>
+    <row r="442" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A442" s="1">
+        <v>79120571661088</v>
+      </c>
+    </row>
+    <row r="443" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A443" s="1">
+        <v>465485289856256</v>
+      </c>
+    </row>
+    <row r="444" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A444" s="1">
+        <v>9817855386753</v>
+      </c>
+    </row>
+    <row r="445" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A445" s="1" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="446" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A446" s="1" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="447" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A447" s="1" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="448" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A448" s="1">
+        <v>9817903095048</v>
+      </c>
+    </row>
+    <row r="449" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A449" s="1" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="450" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A450" s="1" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="451" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A451" s="1">
+        <v>777425354589800</v>
+      </c>
+    </row>
+    <row r="452" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A452" s="1">
+        <v>777425292337950</v>
+      </c>
+    </row>
+    <row r="453" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A453" s="1">
+        <v>465485363226456</v>
+      </c>
+    </row>
+    <row r="454" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A454" s="1">
+        <v>773430615417672</v>
+      </c>
+    </row>
+    <row r="455" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A455" s="1">
+        <v>777425328442133</v>
+      </c>
+    </row>
+    <row r="456" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A456" s="1">
+        <v>773430619143253</v>
+      </c>
+    </row>
+    <row r="457" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A457" s="1">
+        <v>9817858283449</v>
+      </c>
+    </row>
+    <row r="458" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A458" s="1">
+        <v>79121667178404</v>
+      </c>
+      <c r="B458" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="C458" s="1">
+        <v>872221188</v>
+      </c>
+      <c r="D458" s="1">
+        <v>43.7</v>
+      </c>
+    </row>
+    <row r="459" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A459" s="1">
+        <v>9817956925032</v>
+      </c>
+      <c r="D459" s="1">
+        <v>53.76</v>
+      </c>
+    </row>
+    <row r="460" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A460" s="1">
+        <v>9817966084147</v>
+      </c>
+    </row>
+    <row r="461" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A461" s="1">
+        <v>777426806685057</v>
+      </c>
+    </row>
+    <row r="462" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A462" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="B462" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="C462" s="1">
+        <v>557009840</v>
+      </c>
+      <c r="D462" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="463" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A463" s="1">
+        <v>465484249602894</v>
+      </c>
+      <c r="D463" s="1">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="464" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A464" s="1" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="465" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A465" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="466" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A466" s="1">
+        <v>79121247992132</v>
+      </c>
+    </row>
+    <row r="467" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A467" s="1">
+        <v>465494472191076</v>
+      </c>
+    </row>
+    <row r="468" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A468" s="1">
+        <v>9817914022790</v>
+      </c>
+    </row>
+    <row r="469" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A469" s="1">
+        <v>777425497747169</v>
+      </c>
+    </row>
+    <row r="470" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A470" s="1">
+        <v>79120925438667</v>
+      </c>
+    </row>
+    <row r="471" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A471" s="1" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="472" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A472" s="1" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="473" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A473" s="1">
+        <v>9817917440595</v>
+      </c>
+    </row>
+    <row r="474" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A474" s="1">
+        <v>465495973466450</v>
+      </c>
+    </row>
+    <row r="475" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A475" s="1">
+        <v>465494671170125</v>
+      </c>
+    </row>
+    <row r="476" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A476" s="1">
+        <v>777425437843233</v>
+      </c>
+    </row>
+    <row r="477" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A477" s="1">
+        <v>9817904648526</v>
+      </c>
+    </row>
+    <row r="479" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A479" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="B479" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C479" s="1">
+        <v>927682009</v>
+      </c>
+      <c r="D479" s="1">
+        <v>50.6</v>
+      </c>
+    </row>
+    <row r="480" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A480" s="1">
+        <v>79120926941206</v>
+      </c>
+      <c r="D480" s="1">
+        <v>49.5</v>
+      </c>
+    </row>
+    <row r="481" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A481" s="1" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="482" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A482" s="1">
+        <v>777425512853696</v>
+      </c>
+    </row>
+    <row r="483" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A483" s="1" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="484" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A484" s="1" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="485" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A485" s="1">
+        <v>9817914931482</v>
+      </c>
+    </row>
+    <row r="486" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A486" s="1" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="487" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A487" s="1">
+        <v>777425552263142</v>
+      </c>
+    </row>
+    <row r="488" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A488" s="1">
+        <v>777425614036297</v>
+      </c>
+    </row>
+    <row r="489" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A489" s="1">
+        <v>9817907816815</v>
+      </c>
+    </row>
+    <row r="490" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A490" s="1">
+        <v>777425556295308</v>
+      </c>
+    </row>
+    <row r="491" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A491" s="1">
+        <v>79120994662956</v>
+      </c>
+    </row>
+    <row r="492" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A492" s="1">
+        <v>777425406799771</v>
+      </c>
+    </row>
+    <row r="493" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A493" s="1">
+        <v>777425635070207</v>
+      </c>
+    </row>
+    <row r="494" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A494" s="1">
+        <v>777425442675982</v>
+      </c>
+    </row>
+    <row r="495" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A495" s="1">
+        <v>465483864393112</v>
+      </c>
+    </row>
+    <row r="496" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A496" s="1">
+        <v>9817911190682</v>
+      </c>
+    </row>
+    <row r="497" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A497" s="1">
+        <v>465493029458794</v>
+      </c>
+    </row>
+    <row r="498" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A498" s="1">
+        <v>9817886341964</v>
+      </c>
+    </row>
+    <row r="499" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A499" s="1" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="501" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A501" s="1">
+        <v>777424986197449</v>
+      </c>
+      <c r="B501" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="C501" s="1">
+        <v>114441122</v>
+      </c>
+      <c r="D501" s="1">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="502" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A502" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="D502" s="1">
+        <v>39.1</v>
+      </c>
+    </row>
+    <row r="503" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A503" s="1">
+        <v>777425376893025</v>
+      </c>
+    </row>
+    <row r="504" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A504" s="1">
+        <v>777425078148667</v>
+      </c>
+    </row>
+    <row r="505" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A505" s="1">
+        <v>79120492216951</v>
+      </c>
+    </row>
+    <row r="506" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A506" s="1">
+        <v>773430488632225</v>
+      </c>
+    </row>
+    <row r="507" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A507" s="1" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="508" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A508" s="1" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="509" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A509" s="1">
+        <v>777424939805614</v>
+      </c>
+    </row>
+    <row r="510" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A510" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="511" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A511" s="1" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="512" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A512" s="1">
+        <v>777424952193652</v>
+      </c>
+    </row>
+    <row r="513" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A513" s="1" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="514" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A514" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="515" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A515" s="1">
+        <v>79120273943032</v>
+      </c>
+    </row>
+    <row r="516" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A516" s="1" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="517" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A517" s="1" t="s">
+        <v>236</v>
       </c>
     </row>
   </sheetData>

--- a/zafarabad.xlsx
+++ b/zafarabad.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="299">
   <si>
     <t>Track</t>
   </si>
@@ -730,13 +730,196 @@
   </si>
   <si>
     <t>t002337873</t>
+  </si>
+  <si>
+    <t>DALERSHOH</t>
+  </si>
+  <si>
+    <t>JT5505439599036</t>
+  </si>
+  <si>
+    <t>YT8886715622217</t>
+  </si>
+  <si>
+    <t>FARIDUN</t>
+  </si>
+  <si>
+    <t>T008778177</t>
+  </si>
+  <si>
+    <t>YT7632094972824</t>
+  </si>
+  <si>
+    <t>JT5505896621144</t>
+  </si>
+  <si>
+    <t>YT8887180283699</t>
+  </si>
+  <si>
+    <t>YT8887499234380</t>
+  </si>
+  <si>
+    <t>JT5505842113414</t>
+  </si>
+  <si>
+    <t>YT8886672643157</t>
+  </si>
+  <si>
+    <t>JT5506545455404</t>
+  </si>
+  <si>
+    <t>SADORAT</t>
+  </si>
+  <si>
+    <t>YT8887474259342</t>
+  </si>
+  <si>
+    <t>OYGUL</t>
+  </si>
+  <si>
+    <t>JT5505709983398</t>
+  </si>
+  <si>
+    <t>T002337873</t>
+  </si>
+  <si>
+    <t>MAFTUNA</t>
+  </si>
+  <si>
+    <t>JT5505579885426</t>
+  </si>
+  <si>
+    <t>RASHID</t>
+  </si>
+  <si>
+    <t>YT7632865575296</t>
+  </si>
+  <si>
+    <t>YT7632865500214</t>
+  </si>
+  <si>
+    <t>YT8887233456818</t>
+  </si>
+  <si>
+    <t>YT8887110380694</t>
+  </si>
+  <si>
+    <t>YT8886765884971</t>
+  </si>
+  <si>
+    <t>YT7632553701941</t>
+  </si>
+  <si>
+    <t>YT7633058282366</t>
+  </si>
+  <si>
+    <t>SAFARALI</t>
+  </si>
+  <si>
+    <t>MAHFUZA</t>
+  </si>
+  <si>
+    <t>JT5505554534455</t>
+  </si>
+  <si>
+    <t>JT5505607338561</t>
+  </si>
+  <si>
+    <t>JT5505661002107</t>
+  </si>
+  <si>
+    <t>JT5504948709547</t>
+  </si>
+  <si>
+    <t>JT5504948725054</t>
+  </si>
+  <si>
+    <t>JT5504985858847</t>
+  </si>
+  <si>
+    <t>YT8886915531472</t>
+  </si>
+  <si>
+    <t>JT5504942213349</t>
+  </si>
+  <si>
+    <t>JT5505595034152</t>
+  </si>
+  <si>
+    <t>YT8886995204480</t>
+  </si>
+  <si>
+    <t>FEECHKA</t>
+  </si>
+  <si>
+    <t>T000012506</t>
+  </si>
+  <si>
+    <t>JT5504307726856</t>
+  </si>
+  <si>
+    <t>RABE</t>
+  </si>
+  <si>
+    <t>JT5504898039627</t>
+  </si>
+  <si>
+    <t>YT8886581615609</t>
+  </si>
+  <si>
+    <t>YT8886635357071</t>
+  </si>
+  <si>
+    <t>YOSAMIN</t>
+  </si>
+  <si>
+    <t>T002771712</t>
+  </si>
+  <si>
+    <t>OGABEK</t>
+  </si>
+  <si>
+    <t>YT8886384406516</t>
+  </si>
+  <si>
+    <t>JT5505589725403</t>
+  </si>
+  <si>
+    <t>JAHONGIR</t>
+  </si>
+  <si>
+    <t>ZAYKA</t>
+  </si>
+  <si>
+    <t>YT8885333846328</t>
+  </si>
+  <si>
+    <t>JT5505149288184</t>
+  </si>
+  <si>
+    <t>HILOLA</t>
+  </si>
+  <si>
+    <t>JT5504307209131</t>
+  </si>
+  <si>
+    <t>JT5505044125581</t>
+  </si>
+  <si>
+    <t>FIRUZ</t>
+  </si>
+  <si>
+    <t>YT8885952562674</t>
+  </si>
+  <si>
+    <t>DILSHODA</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -770,6 +953,22 @@
     <font>
       <b/>
       <sz val="16"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="22"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -843,7 +1042,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -891,6 +1090,15 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="16" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1195,7 +1403,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J517"/>
+  <dimension ref="A1:J646"/>
   <sheetFormatPr defaultRowHeight="15.6" outlineLevelRow="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.88671875" style="1" customWidth="1"/>
@@ -4876,29 +5084,698 @@
         <v>777424952193652</v>
       </c>
     </row>
-    <row r="513" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A513" s="1" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="514" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A514" s="1" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="515" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A515" s="1">
         <v>79120273943032</v>
       </c>
     </row>
-    <row r="516" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A516" s="1" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="517" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A517" s="1" t="s">
         <v>236</v>
+      </c>
+    </row>
+    <row r="518" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="519" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A519" s="17"/>
+      <c r="B519" s="18"/>
+      <c r="C519" s="19">
+        <v>46222</v>
+      </c>
+      <c r="D519" s="18"/>
+      <c r="E519" s="7"/>
+    </row>
+    <row r="521" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A521" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="B521" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="D521" s="1">
+        <v>13.8</v>
+      </c>
+    </row>
+    <row r="522" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A522" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="523" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A523" s="1">
+        <v>465508194640408</v>
+      </c>
+    </row>
+    <row r="524" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A524" s="1">
+        <v>777426842208139</v>
+      </c>
+    </row>
+    <row r="526" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A526" s="1">
+        <v>79122173802535</v>
+      </c>
+      <c r="B526" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="C526" s="1" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="527" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A527" s="1">
+        <v>465503689108873</v>
+      </c>
+    </row>
+    <row r="528" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A528" s="1">
+        <v>9818042527494</v>
+      </c>
+    </row>
+    <row r="530" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A530" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="B530" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C530" s="1">
+        <v>557009840</v>
+      </c>
+    </row>
+    <row r="532" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A532" s="1">
+        <v>465509376161976</v>
+      </c>
+      <c r="B532" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C532" s="1">
+        <v>921115126</v>
+      </c>
+    </row>
+    <row r="533" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A533" s="1">
+        <v>777427404579120</v>
+      </c>
+    </row>
+    <row r="534" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A534" s="1" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="535" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A535" s="1" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="536" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A536" s="1">
+        <v>465509360373029</v>
+      </c>
+    </row>
+    <row r="537" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A537" s="1">
+        <v>79122531626386</v>
+      </c>
+    </row>
+    <row r="538" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A538" s="1" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="539" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A539" s="1">
+        <v>465514247899696</v>
+      </c>
+    </row>
+    <row r="540" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A540" s="1">
+        <v>79122687747282</v>
+      </c>
+    </row>
+    <row r="541" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A541" s="1">
+        <v>9818062333520</v>
+      </c>
+    </row>
+    <row r="542" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A542" s="1" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="543" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A543" s="1">
+        <v>777427346837197</v>
+      </c>
+    </row>
+    <row r="544" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A544" s="1">
+        <v>79122934811109</v>
+      </c>
+    </row>
+    <row r="545" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A545" s="1">
+        <v>79122847348936</v>
+      </c>
+    </row>
+    <row r="546" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A546" s="1" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="547" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A547" s="1" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="548" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A548" s="1">
+        <v>777427358319738</v>
+      </c>
+    </row>
+    <row r="550" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A550" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="B550" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="C550" s="1">
+        <v>112601305</v>
+      </c>
+    </row>
+    <row r="551" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A551" s="1">
+        <v>79122940553887</v>
+      </c>
+    </row>
+    <row r="552" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A552" s="1">
+        <v>465506370218522</v>
+      </c>
+    </row>
+    <row r="554" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A554" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B554" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="C554" s="1">
+        <v>927381525</v>
+      </c>
+    </row>
+    <row r="555" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A555" s="1">
+        <v>79122824512889</v>
+      </c>
+    </row>
+    <row r="557" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A557" s="1">
+        <v>777426587500268</v>
+      </c>
+      <c r="B557" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C557" s="1" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="558" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A558" s="1">
+        <v>465492724651609</v>
+      </c>
+    </row>
+    <row r="560" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A560" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B560" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="C560" s="1">
+        <v>921114585</v>
+      </c>
+    </row>
+    <row r="561" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A561" s="1">
+        <v>777426933997095</v>
+      </c>
+    </row>
+    <row r="562" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A562" s="1">
+        <v>9818049917828</v>
+      </c>
+    </row>
+    <row r="563" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A563" s="1">
+        <v>465507898194276</v>
+      </c>
+    </row>
+    <row r="565" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A565" s="1">
+        <v>79122602798414</v>
+      </c>
+      <c r="B565" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="C565" s="1">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="566" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A566" s="1" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="567" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A567" s="1" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="568" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A568" s="1" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="569" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A569" s="1" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="570" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A570" s="1">
+        <v>79018771858616</v>
+      </c>
+    </row>
+    <row r="571" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A571" s="1">
+        <v>435270971367024</v>
+      </c>
+    </row>
+    <row r="572" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A572" s="1">
+        <v>777427144833852</v>
+      </c>
+    </row>
+    <row r="573" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A573" s="1" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="574" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A574" s="1" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="575" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A575" s="1" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="577" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A577" s="1">
+        <v>8244401142220</v>
+      </c>
+      <c r="B577" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="C577" s="1">
+        <v>922120050</v>
+      </c>
+    </row>
+    <row r="578" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A578" s="1">
+        <v>79122903499256</v>
+      </c>
+    </row>
+    <row r="579" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A579" s="1">
+        <v>465514489030346</v>
+      </c>
+    </row>
+    <row r="580" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A580" s="1">
+        <v>777427186380345</v>
+      </c>
+    </row>
+    <row r="582" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A582" s="1">
+        <v>465496611398797</v>
+      </c>
+      <c r="B582" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="C582" s="1">
+        <v>927441198</v>
+      </c>
+    </row>
+    <row r="583" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A583" s="1">
+        <v>777426896912398</v>
+      </c>
+    </row>
+    <row r="584" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A584" s="1" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="585" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A585" s="1" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="586" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A586" s="1" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="587" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A587" s="1" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="588" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A588" s="1" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="589" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A589" s="1">
+        <v>465508782347677</v>
+      </c>
+    </row>
+    <row r="590" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A590" s="1">
+        <v>465506538373629</v>
+      </c>
+    </row>
+    <row r="591" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A591" s="1">
+        <v>465506506662766</v>
+      </c>
+    </row>
+    <row r="592" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A592" s="1" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="593" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A593" s="1">
+        <v>465507914083094</v>
+      </c>
+    </row>
+    <row r="594" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A594" s="1" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="595" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A595" s="1">
+        <v>465508083387532</v>
+      </c>
+    </row>
+    <row r="596" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A596" s="1" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="597" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A597" s="1" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="598" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A598" s="1">
+        <v>79122258818446</v>
+      </c>
+    </row>
+    <row r="599" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A599" s="1">
+        <v>79122143971445</v>
+      </c>
+    </row>
+    <row r="600" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A600" s="1">
+        <v>777427087637042</v>
+      </c>
+    </row>
+    <row r="601" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A601" s="1" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="603" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A603" s="1">
+        <v>465509754781473</v>
+      </c>
+      <c r="B603" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C603" s="1">
+        <v>926600610</v>
+      </c>
+    </row>
+    <row r="604" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A604" s="1">
+        <v>9818049060949</v>
+      </c>
+    </row>
+    <row r="606" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A606" s="1">
+        <v>9817995428423</v>
+      </c>
+      <c r="B606" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="C606" s="1" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="607" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A607" s="1">
+        <v>465507254476899</v>
+      </c>
+    </row>
+    <row r="608" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A608" s="1">
+        <v>777426918928394</v>
+      </c>
+    </row>
+    <row r="609" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A609" s="1" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="611" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A611" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="B611" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="C611" s="1">
+        <v>557528888</v>
+      </c>
+    </row>
+    <row r="612" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A612" s="1">
+        <v>9817997645724</v>
+      </c>
+    </row>
+    <row r="613" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A613" s="1" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="614" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A614" s="1">
+        <v>777427085931458</v>
+      </c>
+    </row>
+    <row r="615" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A615" s="1">
+        <v>79122191195930</v>
+      </c>
+    </row>
+    <row r="616" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A616" s="1">
+        <v>465506921261332</v>
+      </c>
+    </row>
+    <row r="618" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A618" s="1">
+        <v>465514633151567</v>
+      </c>
+      <c r="B618" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C618" s="1">
+        <v>927107034</v>
+      </c>
+    </row>
+    <row r="619" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A619" s="1">
+        <v>465509132293841</v>
+      </c>
+    </row>
+    <row r="620" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A620" s="1">
+        <v>79122498404692</v>
+      </c>
+    </row>
+    <row r="621" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A621" s="1" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="623" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A623" s="1">
+        <v>465500863123295</v>
+      </c>
+      <c r="B623" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="C623" s="1" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="624" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A624" s="1">
+        <v>465502961247710</v>
+      </c>
+    </row>
+    <row r="626" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A626" s="1">
+        <v>9817961258666</v>
+      </c>
+      <c r="B626" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="C626" s="1">
+        <v>872221188</v>
+      </c>
+    </row>
+    <row r="627" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A627" s="1" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="628" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A628" s="1">
+        <v>465502154312880</v>
+      </c>
+    </row>
+    <row r="629" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A629" s="1" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="630" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A630" s="1">
+        <v>777426672106640</v>
+      </c>
+    </row>
+    <row r="632" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A632" s="1">
+        <v>9818058273226</v>
+      </c>
+      <c r="B632" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="C632" s="1">
+        <v>928665600</v>
+      </c>
+    </row>
+    <row r="634" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A634" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="B634" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="C634" s="1">
+        <v>927324849</v>
+      </c>
+    </row>
+    <row r="635" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A635" s="1" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="637" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A637" s="1">
+        <v>79122239505024</v>
+      </c>
+      <c r="B637" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="C637" s="1">
+        <v>555572809</v>
+      </c>
+    </row>
+    <row r="638" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A638" s="1" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="640" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A640" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="B640" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="C640" s="1">
+        <v>928977321</v>
+      </c>
+    </row>
+    <row r="642" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A642" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="B642" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="C642" s="1">
+        <v>926006881</v>
+      </c>
+    </row>
+    <row r="644" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A644" s="1">
+        <v>465499311973338</v>
+      </c>
+      <c r="B644" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="C644" s="1">
+        <v>928230848</v>
+      </c>
+    </row>
+    <row r="646" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A646" s="1">
+        <v>79122539705596</v>
+      </c>
+      <c r="B646" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C646" s="1">
+        <v>927080406</v>
       </c>
     </row>
   </sheetData>

--- a/zafarabad.xlsx
+++ b/zafarabad.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9302"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016"/>
+    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" tabRatio="292"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -12,11 +12,12 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="145621"/>
+  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="499" uniqueCount="299">
   <si>
     <t>Track</t>
   </si>
@@ -819,9 +820,6 @@
     <t>MAHFUZA</t>
   </si>
   <si>
-    <t>JT5505554534455</t>
-  </si>
-  <si>
     <t>JT5505607338561</t>
   </si>
   <si>
@@ -913,6 +911,9 @@
   </si>
   <si>
     <t>DILSHODA</t>
+  </si>
+  <si>
+    <t>992 92 776 0166</t>
   </si>
 </sst>
 </file>
@@ -1403,7 +1404,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J646"/>
+  <dimension ref="A1:J647"/>
   <sheetFormatPr defaultRowHeight="15.6" outlineLevelRow="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.88671875" style="1" customWidth="1"/>
@@ -4107,6 +4108,9 @@
       <c r="B364" s="1" t="s">
         <v>166</v>
       </c>
+      <c r="C364" s="1" t="s">
+        <v>298</v>
+      </c>
       <c r="D364" s="1">
         <v>19.600000000000001</v>
       </c>
@@ -5129,6 +5133,9 @@
       <c r="D521" s="1">
         <v>13.8</v>
       </c>
+      <c r="E521" s="1" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="522" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A522" s="1" t="s">
@@ -5155,6 +5162,12 @@
       <c r="C526" s="1" t="s">
         <v>242</v>
       </c>
+      <c r="D526" s="1">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="E526" s="1" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="527" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A527" s="1">
@@ -5166,7 +5179,7 @@
         <v>9818042527494</v>
       </c>
     </row>
-    <row r="530" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="530" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A530" s="1" t="s">
         <v>243</v>
       </c>
@@ -5176,8 +5189,11 @@
       <c r="C530" s="1">
         <v>557009840</v>
       </c>
-    </row>
-    <row r="532" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D530" s="1">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="532" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A532" s="1">
         <v>465509376161976</v>
       </c>
@@ -5187,88 +5203,94 @@
       <c r="C532" s="1">
         <v>921115126</v>
       </c>
-    </row>
-    <row r="533" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D532" s="1">
+        <v>70.150000000000006</v>
+      </c>
+      <c r="E532" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="533" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A533" s="1">
         <v>777427404579120</v>
       </c>
     </row>
-    <row r="534" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="534" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A534" s="1" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="535" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="535" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A535" s="1" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="536" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="536" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A536" s="1">
         <v>465509360373029</v>
       </c>
     </row>
-    <row r="537" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="537" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A537" s="1">
         <v>79122531626386</v>
       </c>
     </row>
-    <row r="538" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="538" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A538" s="1" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="539" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="539" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A539" s="1">
         <v>465514247899696</v>
       </c>
     </row>
-    <row r="540" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="540" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A540" s="1">
         <v>79122687747282</v>
       </c>
     </row>
-    <row r="541" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="541" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A541" s="1">
         <v>9818062333520</v>
       </c>
     </row>
-    <row r="542" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="542" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A542" s="1" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="543" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="543" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A543" s="1">
         <v>777427346837197</v>
       </c>
     </row>
-    <row r="544" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="544" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A544" s="1">
         <v>79122934811109</v>
       </c>
     </row>
-    <row r="545" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="545" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A545" s="1">
         <v>79122847348936</v>
       </c>
     </row>
-    <row r="546" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="546" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A546" s="1" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="547" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A547" s="1" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="548" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A548" s="1">
         <v>777427358319738</v>
       </c>
     </row>
-    <row r="550" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="550" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A550" s="1" t="s">
         <v>251</v>
       </c>
@@ -5278,18 +5300,24 @@
       <c r="C550" s="1">
         <v>112601305</v>
       </c>
-    </row>
-    <row r="551" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D550" s="1">
+        <v>10.35</v>
+      </c>
+      <c r="E550" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="551" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A551" s="1">
         <v>79122940553887</v>
       </c>
     </row>
-    <row r="552" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="552" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A552" s="1">
         <v>465506370218522</v>
       </c>
     </row>
-    <row r="554" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="554" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A554" s="1" t="s">
         <v>253</v>
       </c>
@@ -5299,13 +5327,19 @@
       <c r="C554" s="1">
         <v>927381525</v>
       </c>
-    </row>
-    <row r="555" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D554" s="1">
+        <v>35</v>
+      </c>
+      <c r="E554" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="555" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A555" s="1">
         <v>79122824512889</v>
       </c>
     </row>
-    <row r="557" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="557" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A557" s="1">
         <v>777426587500268</v>
       </c>
@@ -5316,12 +5350,12 @@
         <v>254</v>
       </c>
     </row>
-    <row r="558" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="558" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A558" s="1">
         <v>465492724651609</v>
       </c>
     </row>
-    <row r="560" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="560" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A560" s="1" t="s">
         <v>256</v>
       </c>
@@ -5331,23 +5365,29 @@
       <c r="C560" s="1">
         <v>921114585</v>
       </c>
-    </row>
-    <row r="561" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D560" s="1">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="561" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A561" s="1">
         <v>777426933997095</v>
       </c>
-    </row>
-    <row r="562" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D561" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="562" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A562" s="1">
         <v>9818049917828</v>
       </c>
     </row>
-    <row r="563" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="563" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A563" s="1">
         <v>465507898194276</v>
       </c>
     </row>
-    <row r="565" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="565" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A565" s="1">
         <v>79122602798414</v>
       </c>
@@ -5357,58 +5397,64 @@
       <c r="C565" s="1">
         <v>166</v>
       </c>
-    </row>
-    <row r="566" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D565" s="1">
+        <v>139</v>
+      </c>
+      <c r="E565" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="566" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A566" s="1" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="567" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="567" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A567" s="1" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="568" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="568" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A568" s="1" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="569" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="569" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A569" s="1" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="570" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="570" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A570" s="1">
         <v>79018771858616</v>
       </c>
     </row>
-    <row r="571" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="571" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A571" s="1">
         <v>435270971367024</v>
       </c>
     </row>
-    <row r="572" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="572" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A572" s="1">
         <v>777427144833852</v>
       </c>
     </row>
-    <row r="573" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="573" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A573" s="1" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="574" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="574" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A574" s="1" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="575" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="575" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A575" s="1" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="577" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="577" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A577" s="1">
         <v>8244401142220</v>
       </c>
@@ -5418,23 +5464,32 @@
       <c r="C577" s="1">
         <v>922120050</v>
       </c>
-    </row>
-    <row r="578" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D577" s="1">
+        <v>226</v>
+      </c>
+      <c r="E577" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="578" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A578" s="1">
         <v>79122903499256</v>
       </c>
     </row>
-    <row r="579" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="579" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A579" s="1">
         <v>465514489030346</v>
       </c>
-    </row>
-    <row r="580" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B579" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="580" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A580" s="1">
         <v>777427186380345</v>
       </c>
     </row>
-    <row r="582" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="582" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A582" s="1">
         <v>465496611398797</v>
       </c>
@@ -5444,103 +5499,104 @@
       <c r="C582" s="1">
         <v>927441198</v>
       </c>
-    </row>
-    <row r="583" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D582" s="1">
+        <v>65.55</v>
+      </c>
+      <c r="E582" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="583" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A583" s="1">
         <v>777426896912398</v>
       </c>
     </row>
-    <row r="584" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A584" s="1" t="s">
+    <row r="585" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A585" s="1" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="585" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A585" s="1" t="s">
+    <row r="586" spans="1:5" ht="102.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A586" s="1" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="586" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A586" s="1" t="s">
+    <row r="587" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A587" s="1" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="587" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A587" s="1" t="s">
+    <row r="588" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A588" s="1" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="588" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A588" s="1" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="589" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="589" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A589" s="1">
         <v>465508782347677</v>
       </c>
     </row>
-    <row r="590" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="590" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A590" s="1">
         <v>465506538373629</v>
       </c>
     </row>
-    <row r="591" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="591" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A591" s="1">
         <v>465506506662766</v>
       </c>
     </row>
-    <row r="592" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="592" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A592" s="1" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="593" spans="1:3" x14ac:dyDescent="0.3">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="593" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A593" s="1">
         <v>465507914083094</v>
       </c>
     </row>
-    <row r="594" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="594" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A594" s="1" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="595" spans="1:3" x14ac:dyDescent="0.3">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="595" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A595" s="1">
         <v>465508083387532</v>
       </c>
     </row>
-    <row r="596" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="596" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A596" s="1" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="597" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A597" s="1" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="597" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A597" s="1" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="598" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="598" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A598" s="1">
         <v>79122258818446</v>
       </c>
     </row>
-    <row r="599" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="599" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A599" s="1">
         <v>79122143971445</v>
       </c>
     </row>
-    <row r="600" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="600" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A600" s="1">
         <v>777427087637042</v>
       </c>
     </row>
-    <row r="601" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="601" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A601" s="1" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="603" spans="1:3" x14ac:dyDescent="0.3">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="603" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A603" s="1">
         <v>465509754781473</v>
       </c>
@@ -5550,75 +5606,99 @@
       <c r="C603" s="1">
         <v>926600610</v>
       </c>
-    </row>
-    <row r="604" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D603" s="1">
+        <v>18.399999999999999</v>
+      </c>
+    </row>
+    <row r="604" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A604" s="1">
         <v>9818049060949</v>
       </c>
     </row>
-    <row r="606" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="606" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A606" s="1">
         <v>9817995428423</v>
       </c>
       <c r="B606" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="C606" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="C606" s="1" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="607" spans="1:3" x14ac:dyDescent="0.3">
+    </row>
+    <row r="607" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A607" s="1">
         <v>465507254476899</v>
       </c>
     </row>
-    <row r="608" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="608" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A608" s="1">
         <v>777426918928394</v>
       </c>
     </row>
-    <row r="609" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="609" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A609" s="1" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="611" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A611" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="B611" s="1" t="s">
         <v>279</v>
-      </c>
-    </row>
-    <row r="611" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A611" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="B611" s="1" t="s">
-        <v>280</v>
       </c>
       <c r="C611" s="1">
         <v>557528888</v>
       </c>
-    </row>
-    <row r="612" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D611" s="1">
+        <v>57</v>
+      </c>
+      <c r="E611" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="612" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A612" s="1">
         <v>9817997645724</v>
       </c>
-    </row>
-    <row r="613" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B612" s="1">
+        <v>465506370218522</v>
+      </c>
+      <c r="D612" s="1">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="613" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A613" s="1" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="614" spans="1:3" x14ac:dyDescent="0.3">
+        <v>281</v>
+      </c>
+      <c r="B613" s="1">
+        <v>79122191195930</v>
+      </c>
+    </row>
+    <row r="614" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A614" s="1">
         <v>777427085931458</v>
       </c>
-    </row>
-    <row r="615" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B614" s="1">
+        <v>9817997645724</v>
+      </c>
+    </row>
+    <row r="615" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A615" s="1">
         <v>79122191195930</v>
       </c>
-    </row>
-    <row r="616" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B615" s="1" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="616" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A616" s="1">
         <v>465506921261332</v>
       </c>
     </row>
-    <row r="618" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="618" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A618" s="1">
         <v>465514633151567</v>
       </c>
@@ -5628,115 +5708,156 @@
       <c r="C618" s="1">
         <v>927107034</v>
       </c>
-    </row>
-    <row r="619" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D618" s="1">
+        <v>62</v>
+      </c>
+      <c r="E618" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="619" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A619" s="1">
         <v>465509132293841</v>
       </c>
     </row>
-    <row r="620" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="620" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A620" s="1">
         <v>79122498404692</v>
       </c>
     </row>
-    <row r="621" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="621" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A621" s="1" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="623" spans="1:3" x14ac:dyDescent="0.3">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="622" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D622" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="623" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A623" s="1">
         <v>465500863123295</v>
       </c>
       <c r="B623" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="C623" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="C623" s="1" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="624" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D623" s="1">
+        <v>6</v>
+      </c>
+      <c r="E623" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="624" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A624" s="1">
         <v>465502961247710</v>
       </c>
     </row>
-    <row r="626" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="626" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A626" s="1">
         <v>9817961258666</v>
       </c>
       <c r="B626" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C626" s="1">
         <v>872221188</v>
       </c>
-    </row>
-    <row r="627" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D626" s="1">
+        <v>48.3</v>
+      </c>
+      <c r="E626" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="627" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A627" s="1" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="628" spans="1:3" x14ac:dyDescent="0.3">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="628" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A628" s="1">
         <v>465502154312880</v>
       </c>
     </row>
-    <row r="629" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="629" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A629" s="1" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="630" spans="1:3" x14ac:dyDescent="0.3">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="630" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A630" s="1">
         <v>777426672106640</v>
       </c>
     </row>
-    <row r="632" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="632" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A632" s="1">
         <v>9818058273226</v>
       </c>
       <c r="B632" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C632" s="1">
         <v>928665600</v>
       </c>
-    </row>
-    <row r="634" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D632" s="1">
+        <v>12.7</v>
+      </c>
+      <c r="E632" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="634" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A634" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B634" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C634" s="1">
         <v>927324849</v>
       </c>
-    </row>
-    <row r="635" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D634" s="1">
+        <v>8.5</v>
+      </c>
+      <c r="E634" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="635" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A635" s="1" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="637" spans="1:3" x14ac:dyDescent="0.3">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="637" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A637" s="1">
         <v>79122239505024</v>
       </c>
       <c r="B637" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C637" s="1">
         <v>555572809</v>
       </c>
-    </row>
-    <row r="638" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D637" s="1">
+        <v>2</v>
+      </c>
+      <c r="E637" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="638" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A638" s="1" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="640" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A640" s="1" t="s">
         <v>294</v>
-      </c>
-    </row>
-    <row r="640" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A640" s="1" t="s">
-        <v>295</v>
       </c>
       <c r="B640" s="1" t="s">
         <v>192</v>
@@ -5744,30 +5865,48 @@
       <c r="C640" s="1">
         <v>928977321</v>
       </c>
-    </row>
-    <row r="642" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D640" s="1">
+        <v>4</v>
+      </c>
+      <c r="E640" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="642" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A642" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B642" s="1" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C642" s="1">
         <v>926006881</v>
       </c>
-    </row>
-    <row r="644" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D642" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="E642" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="644" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A644" s="1">
         <v>465499311973338</v>
       </c>
       <c r="B644" s="1" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C644" s="1">
         <v>928230848</v>
       </c>
-    </row>
-    <row r="646" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D644" s="1">
+        <v>5</v>
+      </c>
+      <c r="E644" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="646" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A646" s="1">
         <v>79122539705596</v>
       </c>
@@ -5776,6 +5915,17 @@
       </c>
       <c r="C646" s="1">
         <v>927080406</v>
+      </c>
+      <c r="D646" s="1">
+        <v>1</v>
+      </c>
+      <c r="E646" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="647" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E647" s="1" t="s">
+        <v>85</v>
       </c>
     </row>
   </sheetData>

--- a/zafarabad.xlsx
+++ b/zafarabad.xlsx
@@ -12,7 +12,6 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="145621"/>
-  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
@@ -1419,90 +1418,87 @@
     <col min="12" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="1">
-        <v>773428109156580</v>
-      </c>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C2" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="1">
-        <v>777420209995112</v>
-      </c>
+      <c r="I2" s="1">
+        <v>773428109156580</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C3" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="1">
-        <v>79115916921709</v>
-      </c>
+      <c r="I3" s="1">
+        <v>777420209995112</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C4" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="1">
-        <v>9817512182414</v>
-      </c>
+      <c r="I4" s="1">
+        <v>79115916921709</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C5" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="1">
-        <v>9817475375924</v>
-      </c>
+      <c r="I5" s="1">
+        <v>9817512182414</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C6" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="1">
-        <v>79013823518038</v>
-      </c>
+      <c r="I6" s="1">
+        <v>9817475375924</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C7" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
-        <v>5</v>
-      </c>
+      <c r="I7" s="1">
+        <v>79013823518038</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="1">
         <v>929589803</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
-        <v>6</v>
-      </c>
+      <c r="I9" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C10" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
-        <v>7</v>
-      </c>
+      <c r="I10" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C11" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="1">
-        <v>777420320755106</v>
-      </c>
+      <c r="I11" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1512,189 +1508,189 @@
       <c r="F13" s="8">
         <v>5.5</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="1" t="s">
-        <v>9</v>
-      </c>
+      <c r="I13" s="1">
+        <v>777420320755106</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C14" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F14" s="8">
         <v>0.51</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="1">
-        <v>777420362773842</v>
-      </c>
+      <c r="I14" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C15" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F15" s="8">
         <v>1.32</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" s="1">
-        <v>777421365313677</v>
-      </c>
+      <c r="I15" s="1">
+        <v>777420362773842</v>
+      </c>
+    </row>
+    <row r="17" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C17" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D17" s="1">
         <v>929264050</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" s="1">
-        <v>777421365892035</v>
-      </c>
+      <c r="I17" s="1">
+        <v>777421365313677</v>
+      </c>
+    </row>
+    <row r="18" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C18" s="1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A20" s="1">
-        <v>777420190077415</v>
-      </c>
+      <c r="I18" s="1">
+        <v>777421365892035</v>
+      </c>
+    </row>
+    <row r="20" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C20" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D20" s="1">
         <v>921779435</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21" s="1" t="s">
-        <v>12</v>
-      </c>
+      <c r="I20" s="1">
+        <v>777420190077415</v>
+      </c>
+    </row>
+    <row r="21" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C21" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A22" s="1">
-        <v>465444445672611</v>
-      </c>
+      <c r="I21" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C22" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" s="1">
-        <v>777420148088605</v>
-      </c>
+      <c r="I22" s="1">
+        <v>465444445672611</v>
+      </c>
+    </row>
+    <row r="23" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C23" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A25" s="5" t="s">
-        <v>29</v>
-      </c>
+      <c r="I23" s="1">
+        <v>777420148088605</v>
+      </c>
+    </row>
+    <row r="25" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C25" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D25" s="1">
         <v>920171229</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A26" s="1" t="s">
-        <v>13</v>
-      </c>
+      <c r="I25" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="26" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C26" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A27" s="1" t="s">
-        <v>14</v>
-      </c>
+      <c r="I26" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="27" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C27" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A28" s="1">
-        <v>777421046930615</v>
-      </c>
+      <c r="I27" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="28" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C28" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A29" s="1" t="s">
-        <v>15</v>
-      </c>
+      <c r="I28" s="1">
+        <v>777421046930615</v>
+      </c>
+    </row>
+    <row r="29" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C29" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A31" s="1">
-        <v>465447154216665</v>
-      </c>
+      <c r="I29" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="31" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C31" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D31" s="1">
         <v>927528798</v>
       </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A32" s="1">
-        <v>465445838248752</v>
-      </c>
+      <c r="I31" s="1">
+        <v>465447154216665</v>
+      </c>
+    </row>
+    <row r="32" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C32" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="1" t="s">
-        <v>16</v>
-      </c>
+      <c r="I32" s="1">
+        <v>465445838248752</v>
+      </c>
+    </row>
+    <row r="33" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C33" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="1">
-        <v>777421232224929</v>
-      </c>
+      <c r="I33" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="34" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C34" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="1">
-        <v>79116252056460</v>
-      </c>
+      <c r="I34" s="1">
+        <v>777421232224929</v>
+      </c>
+    </row>
+    <row r="35" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C35" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="1" t="s">
-        <v>17</v>
-      </c>
+      <c r="I35" s="1">
+        <v>79116252056460</v>
+      </c>
+    </row>
+    <row r="36" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C36" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="1">
-        <v>465445620423811</v>
-      </c>
+      <c r="I36" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="37" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C37" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="1">
-        <v>465443036459439</v>
-      </c>
+      <c r="I37" s="1">
+        <v>465445620423811</v>
+      </c>
+    </row>
+    <row r="39" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C39" s="1" t="s">
         <v>18</v>
       </c>
@@ -1704,118 +1700,118 @@
       <c r="F39" s="8">
         <v>2.6880000000000002</v>
       </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="1">
-        <v>9817508074958</v>
-      </c>
+      <c r="I39" s="1">
+        <v>465443036459439</v>
+      </c>
+    </row>
+    <row r="40" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C40" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="1">
-        <v>777420364234201</v>
-      </c>
+      <c r="I40" s="1">
+        <v>9817508074958</v>
+      </c>
+    </row>
+    <row r="41" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C41" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="1">
-        <v>9817450914859</v>
-      </c>
+      <c r="I41" s="1">
+        <v>777420364234201</v>
+      </c>
+    </row>
+    <row r="42" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C42" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43" s="1">
-        <v>9817455768664</v>
-      </c>
+      <c r="I42" s="1">
+        <v>9817450914859</v>
+      </c>
+    </row>
+    <row r="43" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C43" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A44" s="1" t="s">
-        <v>19</v>
-      </c>
+      <c r="I43" s="1">
+        <v>9817455768664</v>
+      </c>
+    </row>
+    <row r="44" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C44" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A45" s="1">
-        <v>777420107395099</v>
-      </c>
+      <c r="I44" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="45" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C45" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A46" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="I45" s="1">
+        <v>777420107395099</v>
+      </c>
+    </row>
+    <row r="46" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C46" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" s="1">
-        <v>9817494430164</v>
-      </c>
+      <c r="I46" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="47" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C47" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="1" t="s">
-        <v>21</v>
-      </c>
+      <c r="I47" s="1">
+        <v>9817494430164</v>
+      </c>
+    </row>
+    <row r="48" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C48" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A49" s="1">
-        <v>777420415699128</v>
-      </c>
+      <c r="I48" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="49" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C49" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A51" s="1" t="s">
-        <v>24</v>
-      </c>
+      <c r="I49" s="1">
+        <v>777420415699128</v>
+      </c>
+    </row>
+    <row r="51" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C51" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D51" s="1">
         <v>878870899</v>
       </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A53" s="1">
-        <v>9817528972077</v>
-      </c>
+      <c r="I51" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="53" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C53" s="1" t="s">
         <v>25</v>
       </c>
       <c r="D53" s="1">
         <v>923335522</v>
       </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A54" s="1">
+      <c r="I53" s="1">
+        <v>9817528972077</v>
+      </c>
+    </row>
+    <row r="54" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I54" s="1">
         <v>777421096212600</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A56" s="1">
-        <v>777421190698415</v>
-      </c>
+    <row r="56" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C56" s="1" t="s">
         <v>26</v>
       </c>
@@ -1825,42 +1821,42 @@
       <c r="F56" s="8">
         <v>0.7</v>
       </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A58" s="1">
-        <v>9817479807223</v>
-      </c>
+      <c r="I56" s="1">
+        <v>777421190698415</v>
+      </c>
+    </row>
+    <row r="58" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C58" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D58" s="1">
         <v>927711266</v>
       </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A60" s="1">
-        <v>79116064173156</v>
-      </c>
+      <c r="I58" s="1">
+        <v>9817479807223</v>
+      </c>
+    </row>
+    <row r="60" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C60" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D60" s="1">
         <v>928959444</v>
       </c>
-    </row>
-    <row r="61" spans="1:7" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="3"/>
+      <c r="I60" s="1">
+        <v>79116064173156</v>
+      </c>
+    </row>
+    <row r="61" spans="2:9" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B61" s="3"/>
       <c r="C61" s="2"/>
       <c r="D61" s="2"/>
       <c r="E61" s="2"/>
       <c r="F61" s="9"/>
       <c r="G61" s="9"/>
-    </row>
-    <row r="62" spans="1:7" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="1" t="s">
-        <v>41</v>
-      </c>
+      <c r="I61" s="3"/>
+    </row>
+    <row r="62" spans="2:9" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C62" s="6" t="s">
         <v>43</v>
       </c>
@@ -1871,8 +1867,11 @@
       <c r="F62" s="12" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="63" spans="1:7" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="I62" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="63" spans="2:9" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C63" s="1" t="s">
         <v>8</v>
       </c>
@@ -1886,7 +1885,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="64" spans="1:7" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:9" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C64" s="1" t="s">
         <v>30</v>
       </c>
@@ -1900,7 +1899,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="65" spans="1:7" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="3:9" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C65" s="1" t="s">
         <v>42</v>
       </c>
@@ -1911,7 +1910,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="66" spans="1:7" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="3:9" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C66" s="1" t="s">
         <v>31</v>
       </c>
@@ -1925,7 +1924,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="67" spans="1:7" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="3:9" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C67" s="1" t="s">
         <v>4</v>
       </c>
@@ -1939,7 +1938,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="68" spans="1:7" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="3:9" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C68" s="1" t="s">
         <v>32</v>
       </c>
@@ -1953,7 +1952,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="69" spans="1:7" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="3:9" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C69" s="1" t="s">
         <v>33</v>
       </c>
@@ -1967,10 +1966,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="70" spans="1:7" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="1">
-        <v>777420502615652</v>
-      </c>
+    <row r="70" spans="3:9" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C70" s="1" t="s">
         <v>34</v>
       </c>
@@ -1983,8 +1979,11 @@
       <c r="G70" s="8" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="71" spans="1:7" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="I70" s="1">
+        <v>777420502615652</v>
+      </c>
+    </row>
+    <row r="71" spans="3:9" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C71" s="1" t="s">
         <v>35</v>
       </c>
@@ -1998,7 +1997,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="72" spans="1:7" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="3:9" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C72" s="1" t="s">
         <v>36</v>
       </c>
@@ -2012,7 +2011,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="73" spans="1:7" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="3:9" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C73" s="1" t="s">
         <v>18</v>
       </c>
@@ -2023,7 +2022,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="74" spans="1:7" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="3:9" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C74" s="1" t="s">
         <v>37</v>
       </c>
@@ -2037,7 +2036,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="75" spans="1:7" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="3:9" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C75" s="1" t="s">
         <v>38</v>
       </c>
@@ -2048,7 +2047,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="76" spans="1:7" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="3:9" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C76" s="1" t="s">
         <v>39</v>
       </c>
@@ -2059,7 +2058,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="77" spans="1:7" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="3:9" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C77" s="1" t="s">
         <v>40</v>
       </c>
@@ -2073,7 +2072,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="78" spans="1:7" ht="16.2" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="3:9" ht="16.2" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C78" s="1" t="s">
         <v>11</v>
       </c>
@@ -2087,7 +2086,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="79" spans="1:7" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="3:9" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E79" s="6">
         <f>SUM(E63:E78)</f>
         <v>78</v>
@@ -2097,10 +2096,7 @@
         <v>753.75</v>
       </c>
     </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A82" s="1">
-        <v>79115562559722</v>
-      </c>
+    <row r="82" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C82" s="1" t="s">
         <v>11</v>
       </c>
@@ -2113,49 +2109,49 @@
       <c r="G82" s="8" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A83" s="1">
+      <c r="I82" s="1">
+        <v>79115562559722</v>
+      </c>
+    </row>
+    <row r="83" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="I83" s="1">
         <v>79116352158884</v>
       </c>
     </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A84" s="1">
+    <row r="84" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="I84" s="1">
         <v>777421947371815</v>
       </c>
     </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A85" s="1" t="s">
+    <row r="85" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="I85" s="1" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A86" s="1" t="s">
+    <row r="86" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="I86" s="1" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A87" s="1">
+    <row r="87" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="I87" s="1">
         <v>777422365205500</v>
       </c>
       <c r="J87" s="1" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A88" s="1">
+    <row r="88" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="I88" s="1">
         <v>777422098989110</v>
       </c>
     </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A89" s="1">
+    <row r="89" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="I89" s="1">
         <v>777422227310805</v>
       </c>
     </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A91" s="1">
-        <v>79117070893183</v>
-      </c>
+    <row r="91" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C91" s="1" t="s">
         <v>10</v>
       </c>
@@ -2165,11 +2161,11 @@
       <c r="F91" s="8">
         <v>29</v>
       </c>
-    </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A93" s="1">
-        <v>9817599918493</v>
-      </c>
+      <c r="I91" s="1">
+        <v>79117070893183</v>
+      </c>
+    </row>
+    <row r="93" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C93" s="1" t="s">
         <v>49</v>
       </c>
@@ -2179,16 +2175,16 @@
       <c r="F93" s="8">
         <v>3</v>
       </c>
-    </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A94" s="1">
+      <c r="I93" s="1">
+        <v>9817599918493</v>
+      </c>
+    </row>
+    <row r="94" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="I94" s="1">
         <v>9817597042198</v>
       </c>
     </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A96" s="1" t="s">
-        <v>52</v>
-      </c>
+    <row r="96" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C96" s="1" t="s">
         <v>51</v>
       </c>
@@ -2198,11 +2194,11 @@
       <c r="F96" s="8">
         <v>1</v>
       </c>
-    </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A98" s="1" t="s">
-        <v>54</v>
-      </c>
+      <c r="I96" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="98" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C98" s="1" t="s">
         <v>53</v>
       </c>
@@ -2212,61 +2208,61 @@
       <c r="F98" s="8">
         <v>117</v>
       </c>
-    </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A99" s="1">
+      <c r="I98" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="99" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="I99" s="1">
         <v>777421102032945</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A100" s="1">
+    <row r="100" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="I100" s="1">
         <v>465453312175650</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A101" s="1" t="s">
+    <row r="101" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="I101" s="1" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A102" s="1">
+    <row r="102" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="I102" s="1">
         <v>79117054093610</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A103" s="1">
+    <row r="103" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="I103" s="1">
         <v>9817561906196</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A104" s="1">
+    <row r="104" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="I104" s="1">
         <v>9817577879969</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A105" s="1">
+    <row r="105" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="I105" s="1">
         <v>465455321353258</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A106" s="1" t="s">
+    <row r="106" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="I106" s="1" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A107" s="1" t="s">
+    <row r="107" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="I107" s="1" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A108" s="1" t="s">
+    <row r="108" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="I108" s="1" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A110" s="1">
-        <v>465459292330949</v>
-      </c>
+    <row r="110" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C110" s="1" t="s">
         <v>59</v>
       </c>
@@ -2276,56 +2272,56 @@
       <c r="F110" s="8">
         <v>46</v>
       </c>
-    </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A111" s="1">
+      <c r="I110" s="1">
+        <v>465459292330949</v>
+      </c>
+    </row>
+    <row r="111" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="I111" s="1">
         <v>465457764900348</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A112" s="1">
+    <row r="112" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="I112" s="1">
         <v>9817583571857</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A113" s="1">
+    <row r="113" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="I113" s="1">
         <v>777421979396975</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A114" s="1">
+    <row r="114" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="I114" s="1">
         <v>777422057138983</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A115" s="1">
+    <row r="115" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="I115" s="1">
         <v>777422279578535</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A116" s="1">
+    <row r="116" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="I116" s="1">
         <v>79117415228084</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A117" s="1">
+    <row r="117" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="I117" s="1">
         <v>777422047937564</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A118" s="1">
+    <row r="118" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="I118" s="1">
         <v>9817587676356</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A119" s="1" t="s">
+    <row r="119" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="I119" s="1" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A121" s="1">
-        <v>435243081637711</v>
-      </c>
+    <row r="121" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C121" s="1" t="s">
         <v>34</v>
       </c>
@@ -2338,19 +2334,19 @@
       <c r="G121" s="8" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A122" s="1">
-        <v>79014648854833</v>
-      </c>
+      <c r="I121" s="1">
+        <v>435243081637711</v>
+      </c>
+    </row>
+    <row r="122" spans="3:9" x14ac:dyDescent="0.3">
       <c r="G122" s="8" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A124" s="1">
-        <v>777422232180626</v>
-      </c>
+      <c r="I122" s="1">
+        <v>79014648854833</v>
+      </c>
+    </row>
+    <row r="124" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C124" s="1" t="s">
         <v>62</v>
       </c>
@@ -2360,69 +2356,69 @@
       <c r="F124" s="8">
         <v>70.5</v>
       </c>
-    </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A125" s="1">
+      <c r="I124" s="1">
+        <v>777422232180626</v>
+      </c>
+    </row>
+    <row r="125" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="I125" s="1">
         <v>79117395794341</v>
       </c>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A126" s="1">
+    <row r="126" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="I126" s="1">
         <v>777422086167392</v>
       </c>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A127" s="1" t="s">
+    <row r="127" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="I127" s="1" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A128" s="1">
-        <v>9817590201640</v>
-      </c>
+    <row r="128" spans="3:9" x14ac:dyDescent="0.3">
       <c r="G128" s="8" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A129" s="1">
+      <c r="I128" s="1">
+        <v>9817590201640</v>
+      </c>
+    </row>
+    <row r="129" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="I129" s="1">
         <v>79117436311943</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A130" s="1" t="s">
+    <row r="130" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="I130" s="1" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A131" s="1">
+    <row r="131" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="I131" s="1">
         <v>9817606613366</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A132" s="1">
+    <row r="132" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="I132" s="1">
         <v>777421855554896</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A133" s="1">
+    <row r="133" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="I133" s="1">
         <v>465456795812468</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A134" s="1">
+    <row r="134" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="I134" s="1">
         <v>79117509710669</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A135" s="1" t="s">
+    <row r="135" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="I135" s="1" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A137" s="1">
-        <v>465448606440063</v>
-      </c>
+    <row r="137" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C137" s="1" t="s">
         <v>66</v>
       </c>
@@ -2432,21 +2428,21 @@
       <c r="F137" s="8">
         <v>8.5</v>
       </c>
-    </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A138" s="1">
+      <c r="I137" s="1">
+        <v>465448606440063</v>
+      </c>
+    </row>
+    <row r="138" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="I138" s="1">
         <v>777420974852832</v>
       </c>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A139" s="1">
+    <row r="139" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="I139" s="1">
         <v>465451760956911</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A141" s="1">
-        <v>79117465527523</v>
-      </c>
+    <row r="141" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C141" s="1" t="s">
         <v>67</v>
       </c>
@@ -2456,71 +2452,71 @@
       <c r="F141" s="8">
         <v>54</v>
       </c>
-    </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A142" s="1" t="s">
+      <c r="I141" s="1">
+        <v>79117465527523</v>
+      </c>
+    </row>
+    <row r="142" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="I142" s="1" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A143" s="1">
+    <row r="143" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="I143" s="1">
         <v>9817607428330</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A144" s="1" t="s">
+    <row r="144" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="I144" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A145" s="1">
+    <row r="145" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="I145" s="1">
         <v>9817587706895</v>
       </c>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A146" s="1">
+    <row r="146" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="I146" s="1">
         <v>9817585314171</v>
       </c>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A147" s="1" t="s">
+    <row r="147" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="I147" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A148" s="1">
+    <row r="148" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="I148" s="1">
         <v>9817611933106</v>
       </c>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A149" s="1">
+    <row r="149" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="I149" s="1">
         <v>465450172258904</v>
       </c>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A150" s="1">
+    <row r="150" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="I150" s="1">
         <v>777422249209050</v>
       </c>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A151" s="1">
+    <row r="151" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="I151" s="1">
         <v>79117774445858</v>
       </c>
     </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A152" s="1" t="s">
+    <row r="152" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="I152" s="1" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A153" s="1">
+    <row r="153" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="I153" s="1">
         <v>9817601310341</v>
       </c>
     </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A155" s="1" t="s">
-        <v>73</v>
-      </c>
+    <row r="155" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C155" s="1" t="s">
         <v>72</v>
       </c>
@@ -2533,36 +2529,36 @@
       <c r="G155" s="8" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A156" s="1">
+      <c r="I155" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="156" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="I156" s="1">
         <v>465457357410239</v>
       </c>
     </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A157" s="1" t="s">
+    <row r="157" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="I157" s="1" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A158" s="1" t="s">
+    <row r="158" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="I158" s="1" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A159" s="1">
+    <row r="159" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="I159" s="1">
         <v>9817598337810</v>
       </c>
     </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A160" s="1" t="s">
+    <row r="160" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="I160" s="1" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A162" s="1" t="s">
-        <v>79</v>
-      </c>
+    <row r="162" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C162" s="1" t="s">
         <v>77</v>
       </c>
@@ -2575,31 +2571,31 @@
       <c r="G162" s="8" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A163" s="1">
+      <c r="I162" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="163" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="I163" s="1">
         <v>9817572476799</v>
       </c>
     </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A164" s="1">
+    <row r="164" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="I164" s="1">
         <v>777421616975217</v>
       </c>
     </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A165" s="1" t="s">
+    <row r="165" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="I165" s="1" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A166" s="1">
+    <row r="166" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="I166" s="1">
         <v>777421939569475</v>
       </c>
     </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A168" s="1">
-        <v>79116860524513</v>
-      </c>
+    <row r="168" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C168" s="1" t="s">
         <v>32</v>
       </c>
@@ -2609,16 +2605,16 @@
       <c r="F168" s="8">
         <v>8</v>
       </c>
-    </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A169" s="1" t="s">
+      <c r="I168" s="1">
+        <v>79116860524513</v>
+      </c>
+    </row>
+    <row r="169" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="I169" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A171" s="1">
-        <v>79117696250946</v>
-      </c>
+    <row r="171" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C171" s="1" t="s">
         <v>82</v>
       </c>
@@ -2628,11 +2624,11 @@
       <c r="G171" s="8" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A173" s="1" t="s">
-        <v>84</v>
-      </c>
+      <c r="I171" s="1">
+        <v>79117696250946</v>
+      </c>
+    </row>
+    <row r="173" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C173" s="1" t="s">
         <v>83</v>
       </c>
@@ -2642,18 +2638,21 @@
       <c r="F173" s="8">
         <v>114</v>
       </c>
-    </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A174" s="1">
+      <c r="I173" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="174" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="I174" s="1">
         <v>8258794480420</v>
       </c>
     </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="175" spans="3:9" x14ac:dyDescent="0.3">
       <c r="G175" s="8" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="178" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C178" s="1" t="s">
         <v>87</v>
       </c>
@@ -2664,7 +2663,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="186" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C186" s="1" t="s">
         <v>89</v>
       </c>
@@ -2672,13 +2671,12 @@
         <v>555572809</v>
       </c>
     </row>
-    <row r="189" spans="1:7" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A189" s="11">
+    <row r="189" spans="2:9" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="I189" s="11">
         <v>46209</v>
       </c>
     </row>
-    <row r="190" spans="1:7" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A190" s="6"/>
+    <row r="190" spans="2:9" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B190" s="4">
         <v>197</v>
       </c>
@@ -2697,11 +2695,9 @@
       <c r="G190" s="8" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="193" spans="1:7" ht="21" outlineLevel="1" x14ac:dyDescent="0.4">
-      <c r="A193" s="1">
-        <v>777423531486346</v>
-      </c>
+      <c r="I190" s="6"/>
+    </row>
+    <row r="193" spans="2:9" ht="21" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B193" s="1">
         <v>303</v>
       </c>
@@ -2714,11 +2710,11 @@
       <c r="E193" s="15" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="194" spans="1:7" ht="21" outlineLevel="1" x14ac:dyDescent="0.4">
-      <c r="A194" s="1">
-        <v>79118373286841</v>
-      </c>
+      <c r="I193" s="1">
+        <v>777423531486346</v>
+      </c>
+    </row>
+    <row r="194" spans="2:9" ht="21" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B194" s="1">
         <v>319</v>
       </c>
@@ -2728,11 +2724,11 @@
       <c r="E194" s="15" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="195" spans="1:7" ht="21" outlineLevel="1" x14ac:dyDescent="0.4">
-      <c r="A195" s="1">
-        <v>79015519961480</v>
-      </c>
+      <c r="I194" s="1">
+        <v>79118373286841</v>
+      </c>
+    </row>
+    <row r="195" spans="2:9" ht="21" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B195" s="1">
         <v>162</v>
       </c>
@@ -2742,11 +2738,11 @@
       <c r="E195" s="15" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="196" spans="1:7" ht="21" outlineLevel="1" x14ac:dyDescent="0.4">
-      <c r="A196" s="1" t="s">
-        <v>93</v>
-      </c>
+      <c r="I195" s="1">
+        <v>79015519961480</v>
+      </c>
+    </row>
+    <row r="196" spans="2:9" ht="21" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B196" s="1">
         <v>151</v>
       </c>
@@ -2756,11 +2752,11 @@
       <c r="E196" s="15" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="197" spans="1:7" ht="21" outlineLevel="1" x14ac:dyDescent="0.4">
-      <c r="A197" s="1">
-        <v>79118367875866</v>
-      </c>
+      <c r="I196" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="197" spans="2:9" ht="21" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B197" s="1">
         <v>54</v>
       </c>
@@ -2770,11 +2766,11 @@
       <c r="E197" s="15" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="198" spans="1:7" ht="21" outlineLevel="1" x14ac:dyDescent="0.4">
-      <c r="A198" s="1" t="s">
-        <v>94</v>
-      </c>
+      <c r="I197" s="1">
+        <v>79118367875866</v>
+      </c>
+    </row>
+    <row r="198" spans="2:9" ht="21" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B198" s="1">
         <v>118</v>
       </c>
@@ -2784,11 +2780,11 @@
       <c r="E198" s="15" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="199" spans="1:7" ht="21" outlineLevel="1" x14ac:dyDescent="0.4">
-      <c r="A199" s="1">
-        <v>79118257588609</v>
-      </c>
+      <c r="I198" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="199" spans="2:9" ht="21" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B199" s="1">
         <v>53</v>
       </c>
@@ -2801,11 +2797,11 @@
       <c r="G199" s="8" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="200" spans="1:7" ht="21" outlineLevel="1" x14ac:dyDescent="0.4">
-      <c r="A200" s="1">
-        <v>79118276902896</v>
-      </c>
+      <c r="I199" s="1">
+        <v>79118257588609</v>
+      </c>
+    </row>
+    <row r="200" spans="2:9" ht="21" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B200" s="1">
         <v>65</v>
       </c>
@@ -2818,11 +2814,11 @@
       <c r="E200" s="15" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="201" spans="1:7" ht="21" outlineLevel="1" x14ac:dyDescent="0.4">
-      <c r="A201" s="1">
-        <v>465465103750961</v>
-      </c>
+      <c r="I200" s="1">
+        <v>79118276902896</v>
+      </c>
+    </row>
+    <row r="201" spans="2:9" ht="21" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B201" s="1">
         <v>43</v>
       </c>
@@ -2832,11 +2828,11 @@
       <c r="E201" s="15" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="202" spans="1:7" ht="21" outlineLevel="1" x14ac:dyDescent="0.4">
-      <c r="A202" s="1" t="s">
-        <v>95</v>
-      </c>
+      <c r="I201" s="1">
+        <v>465465103750961</v>
+      </c>
+    </row>
+    <row r="202" spans="2:9" ht="21" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B202" s="1">
         <v>52</v>
       </c>
@@ -2846,11 +2842,11 @@
       <c r="E202" s="15" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="203" spans="1:7" ht="21" outlineLevel="1" x14ac:dyDescent="0.4">
-      <c r="A203" s="1">
-        <v>777423269005541</v>
-      </c>
+      <c r="I202" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="203" spans="2:9" ht="21" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B203" s="1">
         <v>84</v>
       </c>
@@ -2860,8 +2856,11 @@
       <c r="E203" s="15" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="204" spans="1:7" ht="21" outlineLevel="1" x14ac:dyDescent="0.4">
+      <c r="I203" s="1">
+        <v>777423269005541</v>
+      </c>
+    </row>
+    <row r="204" spans="2:9" ht="21" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B204" s="1">
         <v>64.400000000000006</v>
       </c>
@@ -2872,7 +2871,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="205" spans="1:7" ht="21" outlineLevel="1" x14ac:dyDescent="0.4">
+    <row r="205" spans="2:9" ht="21" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B205" s="1">
         <v>50.6</v>
       </c>
@@ -2886,7 +2885,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="206" spans="1:7" ht="21" outlineLevel="1" x14ac:dyDescent="0.4">
+    <row r="206" spans="2:9" ht="21" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B206" s="1">
         <v>46</v>
       </c>
@@ -2897,7 +2896,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="207" spans="1:7" ht="21" outlineLevel="1" x14ac:dyDescent="0.4">
+    <row r="207" spans="2:9" ht="21" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B207" s="1">
         <v>48.3</v>
       </c>
@@ -2908,7 +2907,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="208" spans="1:7" ht="21" outlineLevel="1" x14ac:dyDescent="0.4">
+    <row r="208" spans="2:9" ht="21" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="B208" s="1">
         <v>51.75</v>
       </c>
@@ -2919,7 +2918,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="209" spans="1:7" ht="21.6" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="209" spans="2:9" ht="21.6" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B209" s="1">
         <v>61</v>
       </c>
@@ -2927,8 +2926,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="210" spans="1:7" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A210" s="6"/>
+    <row r="210" spans="2:9" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B210" s="4">
         <f>SUM(B193:B209)</f>
         <v>1726.05</v>
@@ -2942,8 +2940,9 @@
       <c r="E210" s="4"/>
       <c r="F210" s="13"/>
       <c r="G210" s="12"/>
-    </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I210" s="6"/>
+    </row>
+    <row r="211" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B211" s="1">
         <v>15</v>
       </c>
@@ -2963,7 +2962,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="212" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="212" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B212" s="1">
         <v>46</v>
       </c>
@@ -2980,7 +2979,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="213" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="213" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B213" s="1">
         <v>21</v>
       </c>
@@ -2997,7 +2996,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="214" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="214" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B214" s="1">
         <v>12</v>
       </c>
@@ -3017,7 +3016,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="215" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="215" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B215" s="1">
         <v>68</v>
       </c>
@@ -3034,7 +3033,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="216" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="216" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B216" s="1">
         <v>45</v>
       </c>
@@ -3048,7 +3047,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="217" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="217" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B217" s="1">
         <v>6</v>
       </c>
@@ -3065,7 +3064,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="218" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="218" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B218" s="1">
         <v>72.45</v>
       </c>
@@ -3082,7 +3081,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="219" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="219" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B219" s="1">
         <v>11.25</v>
       </c>
@@ -3102,7 +3101,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="220" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="220" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B220" s="1">
         <v>17.25</v>
       </c>
@@ -3122,7 +3121,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="221" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="221" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B221" s="1">
         <v>143.75</v>
       </c>
@@ -3139,7 +3138,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="222" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="222" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B222" s="1">
         <v>101</v>
       </c>
@@ -3150,7 +3149,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="223" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="223" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B223" s="1">
         <v>31</v>
       </c>
@@ -3167,7 +3166,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="224" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="224" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B224" s="1">
         <v>66.7</v>
       </c>
@@ -3187,7 +3186,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="225" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="225" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B225" s="1">
         <v>247</v>
       </c>
@@ -3201,7 +3200,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="226" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="226" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B226" s="1">
         <v>10</v>
       </c>
@@ -3221,7 +3220,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="227" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="227" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B227" s="1">
         <v>216</v>
       </c>
@@ -3232,10 +3231,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="228" spans="1:10" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A228" s="1" t="s">
-        <v>105</v>
-      </c>
+    <row r="228" spans="2:10" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B228" s="10">
         <v>5</v>
       </c>
@@ -3254,8 +3250,11 @@
       <c r="G228" s="8" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="229" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="I228" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="229" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B229" s="1">
         <v>21</v>
       </c>
@@ -3272,7 +3271,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="230" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="230" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B230" s="1">
         <v>1.5</v>
       </c>
@@ -3289,7 +3288,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="231" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="231" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B231" s="1">
         <v>1</v>
       </c>
@@ -3306,7 +3305,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="232" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="232" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B232" s="1">
         <v>1</v>
       </c>
@@ -3323,7 +3322,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="233" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="233" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B233" s="1">
         <v>2.7</v>
       </c>
@@ -3340,7 +3339,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="234" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="234" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B234" s="1">
         <v>141</v>
       </c>
@@ -3354,8 +3353,8 @@
         <v>46</v>
       </c>
     </row>
-    <row r="236" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="237" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="236" spans="2:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="237" spans="2:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B237" s="4"/>
       <c r="C237" s="4"/>
       <c r="D237" s="4"/>
@@ -3365,13 +3364,9 @@
       <c r="F237" s="13"/>
       <c r="G237" s="13"/>
       <c r="H237" s="4"/>
-      <c r="I237" s="4"/>
       <c r="J237" s="7"/>
     </row>
-    <row r="238" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A238" s="1">
-        <v>465482477918590</v>
-      </c>
+    <row r="238" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B238" s="1" t="s">
         <v>114</v>
       </c>
@@ -3384,16 +3379,16 @@
       <c r="E238" s="1" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="239" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A239" s="1" t="s">
+      <c r="I238" s="1">
+        <v>465482477918590</v>
+      </c>
+    </row>
+    <row r="239" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="I239" s="1" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="240" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A240" s="1">
-        <v>9817833727780</v>
-      </c>
+    <row r="240" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B240" s="1" t="s">
         <v>115</v>
       </c>
@@ -3406,31 +3401,31 @@
       <c r="E240" s="1" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="241" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A241" s="1" t="s">
+      <c r="I240" s="1">
+        <v>9817833727780</v>
+      </c>
+    </row>
+    <row r="241" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I241" s="1" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="242" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A242" s="1" t="s">
+    <row r="242" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I242" s="1" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="243" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A243" s="1">
+    <row r="243" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I243" s="1">
         <v>9817824222503</v>
       </c>
     </row>
-    <row r="244" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A244" s="1">
+    <row r="244" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I244" s="1">
         <v>9817814907148</v>
       </c>
     </row>
-    <row r="245" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A245" s="1">
-        <v>777423826557941</v>
-      </c>
+    <row r="245" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B245" s="1" t="s">
         <v>118</v>
       </c>
@@ -3443,23 +3438,26 @@
       <c r="E245" s="1" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="246" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A246" s="1">
+      <c r="I245" s="1">
+        <v>777423826557941</v>
+      </c>
+    </row>
+    <row r="246" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I246" s="1">
         <v>79119333092366</v>
       </c>
     </row>
-    <row r="247" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A247" s="1">
+    <row r="247" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I247" s="1">
         <v>79119513045156</v>
       </c>
     </row>
-    <row r="248" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A248" s="1">
+    <row r="248" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I248" s="1">
         <v>777424563328445</v>
       </c>
     </row>
-    <row r="250" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="250" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B250" s="1" t="s">
         <v>90</v>
       </c>
@@ -3473,52 +3471,52 @@
         <v>104</v>
       </c>
     </row>
-    <row r="251" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A251" s="1">
+    <row r="251" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I251" s="1">
         <v>79119334943698</v>
       </c>
     </row>
-    <row r="252" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A252" s="1" t="s">
+    <row r="252" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I252" s="1" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="253" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A253" s="1" t="s">
+    <row r="253" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I253" s="1" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="254" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A254" s="1">
+    <row r="254" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I254" s="1">
         <v>79119373863903</v>
       </c>
     </row>
-    <row r="255" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A255" s="1">
+    <row r="255" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I255" s="1">
         <v>9817726240838</v>
       </c>
     </row>
-    <row r="256" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A256" s="1">
+    <row r="256" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I256" s="1">
         <v>777423915519907</v>
       </c>
     </row>
-    <row r="257" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A257" s="1">
+    <row r="257" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I257" s="1">
         <v>465469564298701</v>
       </c>
     </row>
-    <row r="258" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A258" s="1" t="s">
+    <row r="258" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I258" s="1" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="259" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A259" s="1" t="s">
+    <row r="259" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I259" s="1" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="261" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="261" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B261" s="1" t="s">
         <v>67</v>
       </c>
@@ -3532,22 +3530,22 @@
         <v>104</v>
       </c>
     </row>
-    <row r="262" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A262" s="1">
+    <row r="262" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I262" s="1">
         <v>9817833357257</v>
       </c>
     </row>
-    <row r="263" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A263" s="1">
+    <row r="263" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I263" s="1">
         <v>465478836046637</v>
       </c>
     </row>
-    <row r="264" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A264" s="1">
+    <row r="264" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I264" s="1">
         <v>465478907911956</v>
       </c>
     </row>
-    <row r="266" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="266" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B266" s="1" t="s">
         <v>123</v>
       </c>
@@ -3558,67 +3556,67 @@
         <v>61</v>
       </c>
     </row>
-    <row r="267" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A267" s="1" t="s">
+    <row r="267" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I267" s="1" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="268" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A268" s="1">
+    <row r="268" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I268" s="1">
         <v>465480645383240</v>
       </c>
     </row>
-    <row r="269" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A269" s="1">
+    <row r="269" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I269" s="1">
         <v>777424220162412</v>
       </c>
     </row>
-    <row r="270" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A270" s="1">
+    <row r="270" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I270" s="1">
         <v>79120061484942</v>
       </c>
     </row>
-    <row r="271" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A271" s="1">
+    <row r="271" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I271" s="1">
         <v>777424713674098</v>
       </c>
     </row>
-    <row r="272" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A272" s="1">
+    <row r="272" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I272" s="1">
         <v>777424752557155</v>
       </c>
     </row>
-    <row r="273" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A273" s="1" t="s">
+    <row r="273" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I273" s="1" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="274" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A274" s="1" t="s">
+    <row r="274" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I274" s="1" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="275" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A275" s="1">
+    <row r="275" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I275" s="1">
         <v>79016630818351</v>
       </c>
     </row>
-    <row r="276" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A276" s="1">
+    <row r="276" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I276" s="1">
         <v>79119699371877</v>
       </c>
     </row>
-    <row r="277" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A277" s="1">
+    <row r="277" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I277" s="1">
         <v>79119623086735</v>
       </c>
     </row>
-    <row r="278" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A278" s="1" t="s">
+    <row r="278" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I278" s="1" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="280" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="280" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B280" s="1" t="s">
         <v>111</v>
       </c>
@@ -3632,167 +3630,167 @@
         <v>246.6</v>
       </c>
     </row>
-    <row r="281" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A281" s="1">
+    <row r="281" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I281" s="1">
         <v>777424241079598</v>
       </c>
     </row>
-    <row r="282" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A282" s="1">
+    <row r="282" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I282" s="1">
         <v>465478784045939</v>
       </c>
     </row>
-    <row r="283" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A283" s="1" t="s">
+    <row r="283" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I283" s="1" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="284" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A284" s="1">
+    <row r="284" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I284" s="1">
         <v>9817817261348</v>
       </c>
     </row>
-    <row r="285" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A285" s="1" t="s">
+    <row r="285" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I285" s="1" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="286" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A286" s="1">
+    <row r="286" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I286" s="1">
         <v>465476500993347</v>
       </c>
     </row>
-    <row r="287" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A287" s="1">
+    <row r="287" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I287" s="1">
         <v>465479013210690</v>
       </c>
     </row>
-    <row r="288" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A288" s="1">
+    <row r="288" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I288" s="1">
         <v>79120018634046</v>
       </c>
     </row>
-    <row r="289" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A289" s="1">
+    <row r="289" spans="9:9" x14ac:dyDescent="0.3">
+      <c r="I289" s="1">
         <v>9817817233388</v>
       </c>
     </row>
-    <row r="290" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A290" s="1" t="s">
+    <row r="290" spans="9:9" x14ac:dyDescent="0.3">
+      <c r="I290" s="1" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="291" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A291" s="1">
+    <row r="291" spans="9:9" x14ac:dyDescent="0.3">
+      <c r="I291" s="1">
         <v>465478695635802</v>
       </c>
     </row>
-    <row r="292" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A292" s="1">
+    <row r="292" spans="9:9" x14ac:dyDescent="0.3">
+      <c r="I292" s="1">
         <v>79119902597646</v>
       </c>
     </row>
-    <row r="293" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A293" s="1" t="s">
+    <row r="293" spans="9:9" x14ac:dyDescent="0.3">
+      <c r="I293" s="1" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="294" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A294" s="1">
+    <row r="294" spans="9:9" x14ac:dyDescent="0.3">
+      <c r="I294" s="1">
         <v>79120061027112</v>
       </c>
     </row>
-    <row r="295" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A295" s="1" t="s">
+    <row r="295" spans="9:9" x14ac:dyDescent="0.3">
+      <c r="I295" s="1" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="296" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A296" s="1">
+    <row r="296" spans="9:9" x14ac:dyDescent="0.3">
+      <c r="I296" s="1">
         <v>777424417209334</v>
       </c>
     </row>
-    <row r="297" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A297" s="1">
+    <row r="297" spans="9:9" x14ac:dyDescent="0.3">
+      <c r="I297" s="1">
         <v>777424168124852</v>
       </c>
     </row>
-    <row r="298" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A298" s="1">
+    <row r="298" spans="9:9" x14ac:dyDescent="0.3">
+      <c r="I298" s="1">
         <v>465476542484994</v>
       </c>
     </row>
-    <row r="299" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A299" s="1" t="s">
+    <row r="299" spans="9:9" x14ac:dyDescent="0.3">
+      <c r="I299" s="1" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="300" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A300" s="1" t="s">
+    <row r="300" spans="9:9" x14ac:dyDescent="0.3">
+      <c r="I300" s="1" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="301" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A301" s="1">
+    <row r="301" spans="9:9" x14ac:dyDescent="0.3">
+      <c r="I301" s="1">
         <v>465478890570558</v>
       </c>
     </row>
-    <row r="302" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A302" s="1">
+    <row r="302" spans="9:9" x14ac:dyDescent="0.3">
+      <c r="I302" s="1">
         <v>9817802550951</v>
       </c>
     </row>
-    <row r="303" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A303" s="1" t="s">
+    <row r="303" spans="9:9" x14ac:dyDescent="0.3">
+      <c r="I303" s="1" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="304" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A304" s="1" t="s">
+    <row r="304" spans="9:9" x14ac:dyDescent="0.3">
+      <c r="I304" s="1" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="305" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A305" s="1">
+    <row r="305" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I305" s="1">
         <v>777424342650506</v>
       </c>
     </row>
-    <row r="306" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A306" s="1" t="s">
+    <row r="306" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I306" s="1" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="307" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A307" s="1" t="s">
+    <row r="307" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I307" s="1" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="308" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A308" s="1" t="s">
+    <row r="308" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I308" s="1" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="309" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A309" s="1" t="s">
+    <row r="309" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I309" s="1" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="310" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A310" s="1">
+    <row r="310" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I310" s="1">
         <v>79119935578123</v>
       </c>
     </row>
-    <row r="311" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A311" s="1" t="s">
+    <row r="311" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I311" s="1" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="312" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A312" s="1">
+    <row r="312" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I312" s="1">
         <v>777424450392984</v>
       </c>
     </row>
-    <row r="314" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="314" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B314" s="1" t="s">
         <v>144</v>
       </c>
@@ -3800,17 +3798,17 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="315" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A315" s="1">
+    <row r="315" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I315" s="1">
         <v>777423826557941</v>
       </c>
     </row>
-    <row r="316" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A316" s="1">
+    <row r="316" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I316" s="1">
         <v>777424563328445</v>
       </c>
     </row>
-    <row r="318" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="318" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B318" s="1" t="s">
         <v>59</v>
       </c>
@@ -3821,67 +3819,67 @@
         <v>86.6</v>
       </c>
     </row>
-    <row r="319" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A319" s="1" t="s">
+    <row r="319" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I319" s="1" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="320" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A320" s="1">
+    <row r="320" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I320" s="1">
         <v>79119353172438</v>
       </c>
     </row>
-    <row r="321" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A321" s="1">
+    <row r="321" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I321" s="1">
         <v>79119680373126</v>
       </c>
     </row>
-    <row r="322" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A322" s="1">
+    <row r="322" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I322" s="1">
         <v>79119364223825</v>
       </c>
     </row>
-    <row r="323" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A323" s="1">
+    <row r="323" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I323" s="1">
         <v>465481632912782</v>
       </c>
     </row>
-    <row r="324" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A324" s="1">
+    <row r="324" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I324" s="1">
         <v>9817744360683</v>
       </c>
     </row>
-    <row r="325" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A325" s="1">
+    <row r="325" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I325" s="1">
         <v>79119682173315</v>
       </c>
     </row>
-    <row r="326" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A326" s="1" t="s">
+    <row r="326" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I326" s="1" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="327" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A327" s="1">
+    <row r="327" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I327" s="1">
         <v>465480494417993</v>
       </c>
     </row>
-    <row r="328" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A328" s="1" t="s">
+    <row r="328" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I328" s="1" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="329" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A329" s="1" t="s">
+    <row r="329" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I329" s="1" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="330" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A330" s="1">
+    <row r="330" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I330" s="1">
         <v>465470049614367</v>
       </c>
     </row>
-    <row r="332" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="332" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B332" s="1" t="s">
         <v>149</v>
       </c>
@@ -3895,52 +3893,52 @@
         <v>89.85</v>
       </c>
     </row>
-    <row r="333" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A333" s="1">
+    <row r="333" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I333" s="1">
         <v>9817844495105</v>
       </c>
     </row>
-    <row r="334" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A334" s="1">
+    <row r="334" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I334" s="1">
         <v>9817874570506</v>
       </c>
     </row>
-    <row r="335" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A335" s="1">
+    <row r="335" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I335" s="1">
         <v>9817842086178</v>
       </c>
     </row>
-    <row r="336" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A336" s="1">
+    <row r="336" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I336" s="1">
         <v>79120384923273</v>
       </c>
     </row>
-    <row r="337" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A337" s="1">
+    <row r="337" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I337" s="1">
         <v>777424953542826</v>
       </c>
     </row>
-    <row r="338" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A338" s="1">
+    <row r="338" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I338" s="1">
         <v>777424993812033</v>
       </c>
     </row>
-    <row r="339" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A339" s="1">
+    <row r="339" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I339" s="1">
         <v>79120332036445</v>
       </c>
     </row>
-    <row r="340" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A340" s="1">
+    <row r="340" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I340" s="1">
         <v>79120328238119</v>
       </c>
     </row>
-    <row r="341" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A341" s="1" t="s">
+    <row r="341" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I341" s="1" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="343" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="343" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B343" s="1" t="s">
         <v>152</v>
       </c>
@@ -3951,17 +3949,17 @@
         <v>46</v>
       </c>
     </row>
-    <row r="344" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A344" s="1" t="s">
+    <row r="344" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I344" s="1" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="345" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A345" s="1">
+    <row r="345" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I345" s="1">
         <v>777424019456798</v>
       </c>
     </row>
-    <row r="347" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="347" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B347" s="1" t="s">
         <v>154</v>
       </c>
@@ -3975,25 +3973,22 @@
         <v>123</v>
       </c>
     </row>
-    <row r="348" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A348" s="1">
+    <row r="348" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I348" s="1">
         <v>79120038283526</v>
       </c>
     </row>
-    <row r="349" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A349" s="1">
+    <row r="349" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I349" s="1">
         <v>777424361174079</v>
       </c>
     </row>
-    <row r="350" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A350" s="1">
+    <row r="350" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I350" s="1">
         <v>465479229384518</v>
       </c>
     </row>
-    <row r="352" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A352" s="1">
-        <v>777423993882325</v>
-      </c>
+    <row r="352" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B352" s="1" t="s">
         <v>109</v>
       </c>
@@ -4003,11 +3998,11 @@
       <c r="F352" s="8" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="353" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A353" s="1" t="s">
-        <v>157</v>
-      </c>
+      <c r="I352" s="1">
+        <v>777423993882325</v>
+      </c>
+    </row>
+    <row r="353" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B353" s="1" t="s">
         <v>156</v>
       </c>
@@ -4020,33 +4015,33 @@
       <c r="F353" s="8" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="354" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A354" s="1">
-        <v>79119416390403</v>
-      </c>
+      <c r="I353" s="1" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="354" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B354" s="1" t="s">
         <v>158</v>
       </c>
       <c r="C354" s="1">
         <v>928448707</v>
       </c>
-    </row>
-    <row r="355" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A355" s="1">
-        <v>465471994471730</v>
-      </c>
+      <c r="I354" s="1">
+        <v>79119416390403</v>
+      </c>
+    </row>
+    <row r="355" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B355" s="1" t="s">
         <v>103</v>
       </c>
       <c r="C355" s="1">
         <v>975990050</v>
       </c>
-    </row>
-    <row r="356" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A356" s="1">
-        <v>79016454897614</v>
-      </c>
+      <c r="I355" s="1">
+        <v>465471994471730</v>
+      </c>
+    </row>
+    <row r="356" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B356" s="1" t="s">
         <v>83</v>
       </c>
@@ -4056,22 +4051,22 @@
       <c r="F356" s="8" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="357" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A357" s="1">
-        <v>465473534442564</v>
-      </c>
+      <c r="I356" s="1">
+        <v>79016454897614</v>
+      </c>
+    </row>
+    <row r="357" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B357" s="1" t="s">
         <v>159</v>
       </c>
       <c r="C357" s="1">
         <v>923335522</v>
       </c>
-    </row>
-    <row r="358" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A358" s="1" t="s">
-        <v>161</v>
-      </c>
+      <c r="I357" s="1">
+        <v>465473534442564</v>
+      </c>
+    </row>
+    <row r="358" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B358" s="1" t="s">
         <v>160</v>
       </c>
@@ -4084,15 +4079,17 @@
       <c r="F358" s="8" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="359" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A359" s="1" t="s">
+      <c r="I358" s="1" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="359" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I359" s="1" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="361" spans="1:6" ht="16.2" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="362" spans="1:6" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A362" s="6"/>
+    <row r="361" spans="2:9" ht="16.2" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="362" spans="2:9" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B362" s="4"/>
       <c r="C362" s="16">
         <v>46218</v>
@@ -4100,11 +4097,9 @@
       <c r="D362" s="4"/>
       <c r="E362" s="4"/>
       <c r="F362" s="12"/>
-    </row>
-    <row r="364" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A364" s="1" t="s">
-        <v>164</v>
-      </c>
+      <c r="I362" s="6"/>
+    </row>
+    <row r="364" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B364" s="1" t="s">
         <v>166</v>
       </c>
@@ -4117,16 +4112,16 @@
       <c r="E364" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="365" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A365" s="1" t="s">
+      <c r="I364" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="365" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I365" s="1" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="367" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A367" s="1">
-        <v>777425532295679</v>
-      </c>
+    <row r="367" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B367" s="1" t="s">
         <v>167</v>
       </c>
@@ -4136,41 +4131,41 @@
       <c r="D367" s="1">
         <v>23</v>
       </c>
-    </row>
-    <row r="368" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A368" s="1">
+      <c r="I367" s="1">
+        <v>777425532295679</v>
+      </c>
+    </row>
+    <row r="368" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I368" s="1">
         <v>79120737015066</v>
       </c>
     </row>
-    <row r="369" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A369" s="1">
+    <row r="369" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I369" s="1">
         <v>465484039936407</v>
       </c>
     </row>
-    <row r="370" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A370" s="1">
+    <row r="370" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I370" s="1">
         <v>777425492400505</v>
       </c>
     </row>
-    <row r="371" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A371" s="1">
+    <row r="371" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I371" s="1">
         <v>9817917146012</v>
       </c>
     </row>
-    <row r="372" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A372" s="1" t="s">
+    <row r="372" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I372" s="1" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="373" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A373" s="1">
+    <row r="373" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I373" s="1">
         <v>79120808394858</v>
       </c>
     </row>
-    <row r="374" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A374" s="1">
-        <v>9817949573418</v>
-      </c>
+    <row r="374" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B374" s="1" t="s">
         <v>169</v>
       </c>
@@ -4180,11 +4175,11 @@
       <c r="D374" s="1">
         <v>7</v>
       </c>
-    </row>
-    <row r="376" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A376" s="1" t="s">
-        <v>171</v>
-      </c>
+      <c r="I374" s="1">
+        <v>9817949573418</v>
+      </c>
+    </row>
+    <row r="376" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B376" s="1" t="s">
         <v>115</v>
       </c>
@@ -4194,11 +4189,11 @@
       <c r="D376" s="1">
         <v>38</v>
       </c>
-    </row>
-    <row r="377" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A377" s="1">
-        <v>777425644089342</v>
-      </c>
+      <c r="I376" s="1" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="377" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B377" s="1" t="s">
         <v>172</v>
       </c>
@@ -4208,11 +4203,11 @@
       <c r="D377" s="1">
         <v>9.1999999999999993</v>
       </c>
-    </row>
-    <row r="379" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A379" s="1">
-        <v>9817958820639</v>
-      </c>
+      <c r="I377" s="1">
+        <v>777425644089342</v>
+      </c>
+    </row>
+    <row r="379" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B379" s="1" t="s">
         <v>173</v>
       </c>
@@ -4222,21 +4217,21 @@
       <c r="D379" s="1">
         <v>4</v>
       </c>
-    </row>
-    <row r="380" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A380" s="1">
+      <c r="I379" s="1">
+        <v>9817958820639</v>
+      </c>
+    </row>
+    <row r="380" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I380" s="1">
         <v>79121420106957</v>
       </c>
     </row>
-    <row r="381" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A381" s="1">
+    <row r="381" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I381" s="1">
         <v>79121527527448</v>
       </c>
     </row>
-    <row r="382" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A382" s="1">
-        <v>79120513891281</v>
-      </c>
+    <row r="382" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B382" s="1" t="s">
         <v>174</v>
       </c>
@@ -4246,21 +4241,21 @@
       <c r="D382" s="1">
         <v>10</v>
       </c>
-    </row>
-    <row r="383" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A383" s="1">
+      <c r="I382" s="1">
+        <v>79120513891281</v>
+      </c>
+    </row>
+    <row r="383" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I383" s="1">
         <v>465485939540824</v>
       </c>
     </row>
-    <row r="384" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A384" s="1">
+    <row r="384" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I384" s="1">
         <v>465485672986262</v>
       </c>
     </row>
-    <row r="385" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A385" s="1">
-        <v>777425075185916</v>
-      </c>
+    <row r="385" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B385" s="1" t="s">
         <v>175</v>
       </c>
@@ -4270,11 +4265,11 @@
       <c r="D385" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="386" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A386" s="1" t="s">
-        <v>177</v>
-      </c>
+      <c r="I385" s="1">
+        <v>777425075185916</v>
+      </c>
+    </row>
+    <row r="386" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B386" s="1" t="s">
         <v>176</v>
       </c>
@@ -4284,11 +4279,11 @@
       <c r="D386" s="1">
         <v>7</v>
       </c>
-    </row>
-    <row r="387" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A387" s="1" t="s">
-        <v>179</v>
-      </c>
+      <c r="I386" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="387" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B387" s="1" t="s">
         <v>178</v>
       </c>
@@ -4298,16 +4293,16 @@
       <c r="D387" s="1">
         <v>12.5</v>
       </c>
-    </row>
-    <row r="388" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A388" s="1">
+      <c r="I387" s="1" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="388" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I388" s="1">
         <v>465502104232434</v>
       </c>
     </row>
-    <row r="389" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A389" s="1">
-        <v>9817943793166</v>
-      </c>
+    <row r="389" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B389" s="1" t="s">
         <v>180</v>
       </c>
@@ -4317,11 +4312,11 @@
       <c r="D389" s="1">
         <v>22</v>
       </c>
-    </row>
-    <row r="390" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A390" s="1">
-        <v>773430169099707</v>
-      </c>
+      <c r="I389" s="1">
+        <v>9817943793166</v>
+      </c>
+    </row>
+    <row r="390" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B390" s="1" t="s">
         <v>181</v>
       </c>
@@ -4331,11 +4326,11 @@
       <c r="D390" s="1">
         <v>40.299999999999997</v>
       </c>
-    </row>
-    <row r="391" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A391" s="1">
-        <v>9817951581468</v>
-      </c>
+      <c r="I390" s="1">
+        <v>773430169099707</v>
+      </c>
+    </row>
+    <row r="391" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B391" s="1" t="s">
         <v>182</v>
       </c>
@@ -4345,11 +4340,11 @@
       <c r="D391" s="1">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="392" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A392" s="1">
-        <v>465486424671792</v>
-      </c>
+      <c r="I391" s="1">
+        <v>9817951581468</v>
+      </c>
+    </row>
+    <row r="392" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B392" s="1" t="s">
         <v>183</v>
       </c>
@@ -4359,21 +4354,21 @@
       <c r="D392" s="1">
         <v>6</v>
       </c>
-    </row>
-    <row r="393" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A393" s="1" t="s">
+      <c r="I392" s="1">
+        <v>465486424671792</v>
+      </c>
+    </row>
+    <row r="393" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I393" s="1" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="394" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A394" s="1">
+    <row r="394" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I394" s="1">
         <v>465501494935518</v>
       </c>
     </row>
-    <row r="395" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A395" s="1">
-        <v>777424952568763</v>
-      </c>
+    <row r="395" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B395" s="1" t="s">
         <v>185</v>
       </c>
@@ -4383,11 +4378,11 @@
       <c r="D395" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="396" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A396" s="1">
-        <v>465494207464740</v>
-      </c>
+      <c r="I395" s="1">
+        <v>777424952568763</v>
+      </c>
+    </row>
+    <row r="396" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B396" s="1" t="s">
         <v>186</v>
       </c>
@@ -4397,16 +4392,16 @@
       <c r="D396" s="1">
         <v>2.5</v>
       </c>
-    </row>
-    <row r="397" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A397" s="1">
+      <c r="I396" s="1">
+        <v>465494207464740</v>
+      </c>
+    </row>
+    <row r="397" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I397" s="1">
         <v>465484052406977</v>
       </c>
     </row>
-    <row r="398" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A398" s="1">
-        <v>777426778488134</v>
-      </c>
+    <row r="398" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B398" s="1" t="s">
         <v>187</v>
       </c>
@@ -4416,21 +4411,21 @@
       <c r="D398" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="399" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A399" s="1">
+      <c r="I398" s="1">
+        <v>777426778488134</v>
+      </c>
+    </row>
+    <row r="399" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I399" s="1">
         <v>79121636735126</v>
       </c>
     </row>
-    <row r="400" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A400" s="1">
+    <row r="400" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I400" s="1">
         <v>79121727019157</v>
       </c>
     </row>
-    <row r="401" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A401" s="1" t="s">
-        <v>189</v>
-      </c>
+    <row r="401" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B401" s="1" t="s">
         <v>190</v>
       </c>
@@ -4440,11 +4435,11 @@
       <c r="D401" s="1">
         <v>244</v>
       </c>
-    </row>
-    <row r="402" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A402" s="1">
-        <v>465486045639866</v>
-      </c>
+      <c r="I401" s="1" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="402" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B402" s="1" t="s">
         <v>191</v>
       </c>
@@ -4454,16 +4449,16 @@
       <c r="D402" s="1">
         <v>44</v>
       </c>
-    </row>
-    <row r="403" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A403" s="1">
+      <c r="I402" s="1">
+        <v>465486045639866</v>
+      </c>
+    </row>
+    <row r="403" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I403" s="1">
         <v>777425029418984</v>
       </c>
     </row>
-    <row r="404" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A404" s="1" t="s">
-        <v>193</v>
-      </c>
+    <row r="404" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B404" s="1" t="s">
         <v>192</v>
       </c>
@@ -4473,82 +4468,82 @@
       <c r="D404" s="1">
         <v>43</v>
       </c>
-    </row>
-    <row r="405" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A405" s="1" t="s">
+      <c r="I404" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="405" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I405" s="1" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="406" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A406" s="1">
+    <row r="406" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I406" s="1">
         <v>79121799191425</v>
       </c>
     </row>
-    <row r="407" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A407" s="1">
+    <row r="407" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I407" s="1">
         <v>777426502141976</v>
       </c>
     </row>
-    <row r="408" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A408" s="1">
+    <row r="408" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I408" s="1">
         <v>465501199601972</v>
       </c>
     </row>
-    <row r="409" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A409" s="1">
+    <row r="409" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I409" s="1">
         <v>79121618345607</v>
       </c>
     </row>
-    <row r="410" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A410" s="1">
+    <row r="410" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I410" s="1">
         <v>9817966082788</v>
       </c>
     </row>
-    <row r="411" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A411" s="1">
-        <v>79121981513759</v>
-      </c>
+    <row r="411" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B411" s="1" t="s">
         <v>195</v>
       </c>
       <c r="C411" s="1">
         <v>928230848</v>
       </c>
-    </row>
-    <row r="412" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A412" s="1">
+      <c r="I411" s="1">
+        <v>79121981513759</v>
+      </c>
+    </row>
+    <row r="412" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I412" s="1">
         <v>79121800010852</v>
       </c>
     </row>
-    <row r="413" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A413" s="1">
+    <row r="413" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I413" s="1">
         <v>9817971903882</v>
       </c>
     </row>
-    <row r="414" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A414" s="1">
+    <row r="414" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I414" s="1">
         <v>9817955045050</v>
       </c>
     </row>
-    <row r="415" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A415" s="1">
+    <row r="415" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I415" s="1">
         <v>79121608498840</v>
       </c>
     </row>
-    <row r="416" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A416" s="1" t="s">
+    <row r="416" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I416" s="1" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="417" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A417" s="1">
+    <row r="417" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I417" s="1">
         <v>65684684654</v>
       </c>
     </row>
-    <row r="418" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A418" s="1">
-        <v>777425546939086</v>
-      </c>
+    <row r="418" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B418" s="1" t="s">
         <v>197</v>
       </c>
@@ -4558,31 +4553,31 @@
       <c r="D418" s="1" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="419" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A419" s="1">
+      <c r="I418" s="1">
+        <v>777425546939086</v>
+      </c>
+    </row>
+    <row r="419" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I419" s="1">
         <v>465493047946239</v>
       </c>
     </row>
-    <row r="420" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A420" s="1">
+    <row r="420" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I420" s="1">
         <v>777425538961039</v>
       </c>
     </row>
-    <row r="421" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A421" s="1">
+    <row r="421" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I421" s="1">
         <v>9817900423455</v>
       </c>
     </row>
-    <row r="422" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A422" s="1">
+    <row r="422" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I422" s="1">
         <v>777426457494875</v>
       </c>
     </row>
-    <row r="423" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A423" s="1">
-        <v>79121004489806</v>
-      </c>
+    <row r="423" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B423" s="1" t="s">
         <v>199</v>
       </c>
@@ -4592,86 +4587,86 @@
       <c r="D423" s="1">
         <v>56.4</v>
       </c>
-    </row>
-    <row r="424" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A424" s="1">
+      <c r="I423" s="1">
+        <v>79121004489806</v>
+      </c>
+    </row>
+    <row r="424" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I424" s="1">
         <v>777425561922513</v>
       </c>
     </row>
-    <row r="425" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A425" s="1">
+    <row r="425" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I425" s="1">
         <v>9817883876957</v>
       </c>
     </row>
-    <row r="426" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A426" s="1" t="s">
+    <row r="426" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I426" s="1" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="427" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A427" s="1" t="s">
+    <row r="427" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I427" s="1" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="428" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A428" s="1" t="s">
+    <row r="428" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I428" s="1" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="429" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A429" s="1" t="s">
+    <row r="429" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I429" s="1" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="430" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A430" s="1">
+    <row r="430" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I430" s="1">
         <v>465483610812509</v>
       </c>
     </row>
-    <row r="431" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A431" s="1" t="s">
+    <row r="431" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I431" s="1" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="432" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A432" s="1">
+    <row r="432" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I432" s="1">
         <v>79120583583816</v>
       </c>
     </row>
-    <row r="433" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A433" s="1">
+    <row r="433" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I433" s="1">
         <v>777425217523315</v>
       </c>
     </row>
-    <row r="434" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A434" s="1">
+    <row r="434" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I434" s="1">
         <v>79121035460932</v>
       </c>
     </row>
-    <row r="435" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A435" s="1" t="s">
+    <row r="435" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I435" s="1" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="436" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A436" s="1">
+    <row r="436" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I436" s="1">
         <v>465493030554901</v>
       </c>
     </row>
-    <row r="437" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A437" s="1">
+    <row r="437" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I437" s="1">
         <v>79120859994050</v>
       </c>
     </row>
-    <row r="438" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A438" s="1">
+    <row r="438" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I438" s="1">
         <v>465493030554901</v>
       </c>
     </row>
-    <row r="439" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A439" s="1" t="s">
-        <v>208</v>
-      </c>
+    <row r="439" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B439" s="1" t="s">
         <v>206</v>
       </c>
@@ -4681,104 +4676,104 @@
       <c r="D439" s="1">
         <v>56.4</v>
       </c>
-    </row>
-    <row r="440" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A440" s="1">
-        <v>9817857282681</v>
-      </c>
+      <c r="I439" s="1" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="440" spans="2:9" x14ac:dyDescent="0.3">
       <c r="D440" s="1">
         <v>40.25</v>
       </c>
-    </row>
-    <row r="441" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A441" s="1">
+      <c r="I440" s="1">
+        <v>9817857282681</v>
+      </c>
+    </row>
+    <row r="441" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I441" s="1">
         <v>79120771222043</v>
       </c>
     </row>
-    <row r="442" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A442" s="1">
+    <row r="442" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I442" s="1">
         <v>79120571661088</v>
       </c>
     </row>
-    <row r="443" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A443" s="1">
+    <row r="443" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I443" s="1">
         <v>465485289856256</v>
       </c>
     </row>
-    <row r="444" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A444" s="1">
+    <row r="444" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I444" s="1">
         <v>9817855386753</v>
       </c>
     </row>
-    <row r="445" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A445" s="1" t="s">
+    <row r="445" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I445" s="1" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="446" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A446" s="1" t="s">
+    <row r="446" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I446" s="1" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="447" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A447" s="1" t="s">
+    <row r="447" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I447" s="1" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="448" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A448" s="1">
+    <row r="448" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I448" s="1">
         <v>9817903095048</v>
       </c>
     </row>
-    <row r="449" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A449" s="1" t="s">
+    <row r="449" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I449" s="1" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="450" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A450" s="1" t="s">
+    <row r="450" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I450" s="1" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="451" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A451" s="1">
+    <row r="451" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I451" s="1">
         <v>777425354589800</v>
       </c>
     </row>
-    <row r="452" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A452" s="1">
+    <row r="452" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I452" s="1">
         <v>777425292337950</v>
       </c>
     </row>
-    <row r="453" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A453" s="1">
+    <row r="453" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I453" s="1">
         <v>465485363226456</v>
       </c>
     </row>
-    <row r="454" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A454" s="1">
+    <row r="454" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I454" s="1">
         <v>773430615417672</v>
       </c>
     </row>
-    <row r="455" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A455" s="1">
+    <row r="455" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I455" s="1">
         <v>777425328442133</v>
       </c>
     </row>
-    <row r="456" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A456" s="1">
+    <row r="456" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I456" s="1">
         <v>773430619143253</v>
       </c>
     </row>
-    <row r="457" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A457" s="1">
+    <row r="457" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I457" s="1">
         <v>9817858283449</v>
       </c>
     </row>
-    <row r="458" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A458" s="1">
-        <v>79121667178404</v>
-      </c>
+    <row r="458" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B458" s="1" t="s">
         <v>214</v>
       </c>
@@ -4788,29 +4783,29 @@
       <c r="D458" s="1">
         <v>43.7</v>
       </c>
-    </row>
-    <row r="459" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A459" s="1">
-        <v>9817956925032</v>
-      </c>
+      <c r="I458" s="1">
+        <v>79121667178404</v>
+      </c>
+    </row>
+    <row r="459" spans="2:9" x14ac:dyDescent="0.3">
       <c r="D459" s="1">
         <v>53.76</v>
       </c>
-    </row>
-    <row r="460" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A460" s="1">
+      <c r="I459" s="1">
+        <v>9817956925032</v>
+      </c>
+    </row>
+    <row r="460" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I460" s="1">
         <v>9817966084147</v>
       </c>
     </row>
-    <row r="461" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A461" s="1">
+    <row r="461" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I461" s="1">
         <v>777426806685057</v>
       </c>
     </row>
-    <row r="462" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A462" s="1" t="s">
-        <v>216</v>
-      </c>
+    <row r="462" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B462" s="1" t="s">
         <v>215</v>
       </c>
@@ -4820,89 +4815,89 @@
       <c r="D462" s="1">
         <v>100</v>
       </c>
-    </row>
-    <row r="463" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A463" s="1">
-        <v>465484249602894</v>
-      </c>
+      <c r="I462" s="1" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="463" spans="2:9" x14ac:dyDescent="0.3">
       <c r="D463" s="1">
         <v>54</v>
       </c>
-    </row>
-    <row r="464" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A464" s="1" t="s">
+      <c r="I463" s="1">
+        <v>465484249602894</v>
+      </c>
+    </row>
+    <row r="464" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I464" s="1" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="465" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A465" s="1" t="s">
+    <row r="465" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I465" s="1" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="466" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A466" s="1">
+    <row r="466" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I466" s="1">
         <v>79121247992132</v>
       </c>
     </row>
-    <row r="467" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A467" s="1">
+    <row r="467" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I467" s="1">
         <v>465494472191076</v>
       </c>
     </row>
-    <row r="468" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A468" s="1">
+    <row r="468" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I468" s="1">
         <v>9817914022790</v>
       </c>
     </row>
-    <row r="469" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A469" s="1">
+    <row r="469" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I469" s="1">
         <v>777425497747169</v>
       </c>
     </row>
-    <row r="470" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A470" s="1">
+    <row r="470" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I470" s="1">
         <v>79120925438667</v>
       </c>
     </row>
-    <row r="471" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A471" s="1" t="s">
+    <row r="471" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I471" s="1" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="472" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A472" s="1" t="s">
+    <row r="472" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I472" s="1" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="473" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A473" s="1">
+    <row r="473" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I473" s="1">
         <v>9817917440595</v>
       </c>
     </row>
-    <row r="474" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A474" s="1">
+    <row r="474" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I474" s="1">
         <v>465495973466450</v>
       </c>
     </row>
-    <row r="475" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A475" s="1">
+    <row r="475" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I475" s="1">
         <v>465494671170125</v>
       </c>
     </row>
-    <row r="476" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A476" s="1">
+    <row r="476" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I476" s="1">
         <v>777425437843233</v>
       </c>
     </row>
-    <row r="477" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A477" s="1">
+    <row r="477" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I477" s="1">
         <v>9817904648526</v>
       </c>
     </row>
-    <row r="479" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A479" s="1" t="s">
-        <v>221</v>
-      </c>
+    <row r="479" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B479" s="1" t="s">
         <v>62</v>
       </c>
@@ -4912,114 +4907,114 @@
       <c r="D479" s="1">
         <v>50.6</v>
       </c>
-    </row>
-    <row r="480" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A480" s="1">
-        <v>79120926941206</v>
-      </c>
+      <c r="I479" s="1" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="480" spans="2:9" x14ac:dyDescent="0.3">
       <c r="D480" s="1">
         <v>49.5</v>
       </c>
-    </row>
-    <row r="481" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A481" s="1" t="s">
+      <c r="I480" s="1">
+        <v>79120926941206</v>
+      </c>
+    </row>
+    <row r="481" spans="9:9" x14ac:dyDescent="0.3">
+      <c r="I481" s="1" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="482" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A482" s="1">
+    <row r="482" spans="9:9" x14ac:dyDescent="0.3">
+      <c r="I482" s="1">
         <v>777425512853696</v>
       </c>
     </row>
-    <row r="483" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A483" s="1" t="s">
+    <row r="483" spans="9:9" x14ac:dyDescent="0.3">
+      <c r="I483" s="1" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="484" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A484" s="1" t="s">
+    <row r="484" spans="9:9" x14ac:dyDescent="0.3">
+      <c r="I484" s="1" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="485" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A485" s="1">
+    <row r="485" spans="9:9" x14ac:dyDescent="0.3">
+      <c r="I485" s="1">
         <v>9817914931482</v>
       </c>
     </row>
-    <row r="486" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A486" s="1" t="s">
+    <row r="486" spans="9:9" x14ac:dyDescent="0.3">
+      <c r="I486" s="1" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="487" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A487" s="1">
+    <row r="487" spans="9:9" x14ac:dyDescent="0.3">
+      <c r="I487" s="1">
         <v>777425552263142</v>
       </c>
     </row>
-    <row r="488" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A488" s="1">
+    <row r="488" spans="9:9" x14ac:dyDescent="0.3">
+      <c r="I488" s="1">
         <v>777425614036297</v>
       </c>
     </row>
-    <row r="489" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A489" s="1">
+    <row r="489" spans="9:9" x14ac:dyDescent="0.3">
+      <c r="I489" s="1">
         <v>9817907816815</v>
       </c>
     </row>
-    <row r="490" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A490" s="1">
+    <row r="490" spans="9:9" x14ac:dyDescent="0.3">
+      <c r="I490" s="1">
         <v>777425556295308</v>
       </c>
     </row>
-    <row r="491" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A491" s="1">
+    <row r="491" spans="9:9" x14ac:dyDescent="0.3">
+      <c r="I491" s="1">
         <v>79120994662956</v>
       </c>
     </row>
-    <row r="492" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A492" s="1">
+    <row r="492" spans="9:9" x14ac:dyDescent="0.3">
+      <c r="I492" s="1">
         <v>777425406799771</v>
       </c>
     </row>
-    <row r="493" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A493" s="1">
+    <row r="493" spans="9:9" x14ac:dyDescent="0.3">
+      <c r="I493" s="1">
         <v>777425635070207</v>
       </c>
     </row>
-    <row r="494" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A494" s="1">
+    <row r="494" spans="9:9" x14ac:dyDescent="0.3">
+      <c r="I494" s="1">
         <v>777425442675982</v>
       </c>
     </row>
-    <row r="495" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A495" s="1">
+    <row r="495" spans="9:9" x14ac:dyDescent="0.3">
+      <c r="I495" s="1">
         <v>465483864393112</v>
       </c>
     </row>
-    <row r="496" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A496" s="1">
+    <row r="496" spans="9:9" x14ac:dyDescent="0.3">
+      <c r="I496" s="1">
         <v>9817911190682</v>
       </c>
     </row>
-    <row r="497" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A497" s="1">
+    <row r="497" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I497" s="1">
         <v>465493029458794</v>
       </c>
     </row>
-    <row r="498" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A498" s="1">
+    <row r="498" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I498" s="1">
         <v>9817886341964</v>
       </c>
     </row>
-    <row r="499" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A499" s="1" t="s">
+    <row r="499" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I499" s="1" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="501" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A501" s="1">
-        <v>777424986197449</v>
-      </c>
+    <row r="501" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B501" s="1" t="s">
         <v>227</v>
       </c>
@@ -5029,104 +5024,104 @@
       <c r="D501" s="1">
         <v>92</v>
       </c>
-    </row>
-    <row r="502" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A502" s="1" t="s">
-        <v>228</v>
-      </c>
+      <c r="I501" s="1">
+        <v>777424986197449</v>
+      </c>
+    </row>
+    <row r="502" spans="2:9" x14ac:dyDescent="0.3">
       <c r="D502" s="1">
         <v>39.1</v>
       </c>
-    </row>
-    <row r="503" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A503" s="1">
+      <c r="I502" s="1" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="503" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I503" s="1">
         <v>777425376893025</v>
       </c>
     </row>
-    <row r="504" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A504" s="1">
+    <row r="504" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I504" s="1">
         <v>777425078148667</v>
       </c>
     </row>
-    <row r="505" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A505" s="1">
+    <row r="505" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I505" s="1">
         <v>79120492216951</v>
       </c>
     </row>
-    <row r="506" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A506" s="1">
+    <row r="506" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I506" s="1">
         <v>773430488632225</v>
       </c>
     </row>
-    <row r="507" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A507" s="1" t="s">
+    <row r="507" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I507" s="1" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="508" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A508" s="1" t="s">
+    <row r="508" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I508" s="1" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="509" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A509" s="1">
+    <row r="509" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I509" s="1">
         <v>777424939805614</v>
       </c>
     </row>
-    <row r="510" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A510" s="1" t="s">
+    <row r="510" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I510" s="1" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="511" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A511" s="1" t="s">
+    <row r="511" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I511" s="1" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="512" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A512" s="1">
+    <row r="512" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I512" s="1">
         <v>777424952193652</v>
       </c>
     </row>
-    <row r="513" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A513" s="1" t="s">
+    <row r="513" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I513" s="1" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="514" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A514" s="1" t="s">
+    <row r="514" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I514" s="1" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="515" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A515" s="1">
+    <row r="515" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I515" s="1">
         <v>79120273943032</v>
       </c>
     </row>
-    <row r="516" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A516" s="1" t="s">
+    <row r="516" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I516" s="1" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="517" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A517" s="1" t="s">
+    <row r="517" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I517" s="1" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="518" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="519" spans="1:5" ht="29.4" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A519" s="17"/>
+    <row r="518" spans="2:9" ht="16.2" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="519" spans="2:9" ht="29.4" thickBot="1" x14ac:dyDescent="0.6">
       <c r="B519" s="18"/>
       <c r="C519" s="19">
         <v>46222</v>
       </c>
       <c r="D519" s="18"/>
       <c r="E519" s="7"/>
-    </row>
-    <row r="521" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A521" s="1" t="s">
-        <v>239</v>
-      </c>
+      <c r="I519" s="17"/>
+    </row>
+    <row r="521" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B521" s="1" t="s">
         <v>238</v>
       </c>
@@ -5136,26 +5131,26 @@
       <c r="E521" s="1" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="522" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A522" s="1" t="s">
+      <c r="I521" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="522" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I522" s="1" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="523" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A523" s="1">
+    <row r="523" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I523" s="1">
         <v>465508194640408</v>
       </c>
     </row>
-    <row r="524" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A524" s="1">
+    <row r="524" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I524" s="1">
         <v>777426842208139</v>
       </c>
     </row>
-    <row r="526" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A526" s="1">
-        <v>79122173802535</v>
-      </c>
+    <row r="526" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B526" s="1" t="s">
         <v>241</v>
       </c>
@@ -5168,21 +5163,21 @@
       <c r="E526" s="1" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="527" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A527" s="1">
+      <c r="I526" s="1">
+        <v>79122173802535</v>
+      </c>
+    </row>
+    <row r="527" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I527" s="1">
         <v>465503689108873</v>
       </c>
     </row>
-    <row r="528" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A528" s="1">
+    <row r="528" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I528" s="1">
         <v>9818042527494</v>
       </c>
     </row>
-    <row r="530" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A530" s="1" t="s">
-        <v>243</v>
-      </c>
+    <row r="530" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B530" s="1" t="s">
         <v>62</v>
       </c>
@@ -5192,11 +5187,11 @@
       <c r="D530" s="1">
         <v>35</v>
       </c>
-    </row>
-    <row r="532" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A532" s="1">
-        <v>465509376161976</v>
-      </c>
+      <c r="I530" s="1" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="532" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B532" s="1" t="s">
         <v>67</v>
       </c>
@@ -5209,91 +5204,91 @@
       <c r="E532" s="1" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="533" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A533" s="1">
+      <c r="I532" s="1">
+        <v>465509376161976</v>
+      </c>
+    </row>
+    <row r="533" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I533" s="1">
         <v>777427404579120</v>
       </c>
     </row>
-    <row r="534" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A534" s="1" t="s">
+    <row r="534" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I534" s="1" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="535" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A535" s="1" t="s">
+    <row r="535" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I535" s="1" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="536" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A536" s="1">
+    <row r="536" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I536" s="1">
         <v>465509360373029</v>
       </c>
     </row>
-    <row r="537" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A537" s="1">
+    <row r="537" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I537" s="1">
         <v>79122531626386</v>
       </c>
     </row>
-    <row r="538" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A538" s="1" t="s">
+    <row r="538" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I538" s="1" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="539" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A539" s="1">
+    <row r="539" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I539" s="1">
         <v>465514247899696</v>
       </c>
     </row>
-    <row r="540" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A540" s="1">
+    <row r="540" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I540" s="1">
         <v>79122687747282</v>
       </c>
     </row>
-    <row r="541" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A541" s="1">
+    <row r="541" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I541" s="1">
         <v>9818062333520</v>
       </c>
     </row>
-    <row r="542" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A542" s="1" t="s">
+    <row r="542" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I542" s="1" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="543" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A543" s="1">
+    <row r="543" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I543" s="1">
         <v>777427346837197</v>
       </c>
     </row>
-    <row r="544" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A544" s="1">
+    <row r="544" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I544" s="1">
         <v>79122934811109</v>
       </c>
     </row>
-    <row r="545" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A545" s="1">
+    <row r="545" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I545" s="1">
         <v>79122847348936</v>
       </c>
     </row>
-    <row r="546" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A546" s="1" t="s">
+    <row r="546" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I546" s="1" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="547" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A547" s="1" t="s">
+    <row r="547" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I547" s="1" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="548" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A548" s="1">
+    <row r="548" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I548" s="1">
         <v>777427358319738</v>
       </c>
     </row>
-    <row r="550" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A550" s="1" t="s">
-        <v>251</v>
-      </c>
+    <row r="550" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B550" s="1" t="s">
         <v>250</v>
       </c>
@@ -5306,21 +5301,21 @@
       <c r="E550" s="1" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="551" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A551" s="1">
+      <c r="I550" s="1" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="551" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I551" s="1">
         <v>79122940553887</v>
       </c>
     </row>
-    <row r="552" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A552" s="1">
+    <row r="552" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I552" s="1">
         <v>465506370218522</v>
       </c>
     </row>
-    <row r="554" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A554" s="1" t="s">
-        <v>253</v>
-      </c>
+    <row r="554" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B554" s="1" t="s">
         <v>252</v>
       </c>
@@ -5333,32 +5328,32 @@
       <c r="E554" s="1" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="555" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A555" s="1">
+      <c r="I554" s="1" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="555" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I555" s="1">
         <v>79122824512889</v>
       </c>
     </row>
-    <row r="557" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A557" s="1">
-        <v>777426587500268</v>
-      </c>
+    <row r="557" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B557" s="1" t="s">
         <v>167</v>
       </c>
       <c r="C557" s="1" t="s">
         <v>254</v>
       </c>
-    </row>
-    <row r="558" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A558" s="1">
+      <c r="I557" s="1">
+        <v>777426587500268</v>
+      </c>
+    </row>
+    <row r="558" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I558" s="1">
         <v>465492724651609</v>
       </c>
     </row>
-    <row r="560" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A560" s="1" t="s">
-        <v>256</v>
-      </c>
+    <row r="560" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B560" s="1" t="s">
         <v>255</v>
       </c>
@@ -5368,29 +5363,29 @@
       <c r="D560" s="1">
         <v>38</v>
       </c>
-    </row>
-    <row r="561" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A561" s="1">
-        <v>777426933997095</v>
-      </c>
+      <c r="I560" s="1" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="561" spans="2:9" x14ac:dyDescent="0.3">
       <c r="D561" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="562" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A562" s="1">
+      <c r="I561" s="1">
+        <v>777426933997095</v>
+      </c>
+    </row>
+    <row r="562" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I562" s="1">
         <v>9818049917828</v>
       </c>
     </row>
-    <row r="563" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A563" s="1">
+    <row r="563" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I563" s="1">
         <v>465507898194276</v>
       </c>
     </row>
-    <row r="565" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A565" s="1">
-        <v>79122602798414</v>
-      </c>
+    <row r="565" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B565" s="1" t="s">
         <v>257</v>
       </c>
@@ -5403,61 +5398,61 @@
       <c r="E565" s="1" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="566" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A566" s="1" t="s">
+      <c r="I565" s="1">
+        <v>79122602798414</v>
+      </c>
+    </row>
+    <row r="566" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I566" s="1" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="567" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A567" s="1" t="s">
+    <row r="567" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I567" s="1" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="568" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A568" s="1" t="s">
+    <row r="568" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I568" s="1" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="569" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A569" s="1" t="s">
+    <row r="569" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I569" s="1" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="570" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A570" s="1">
+    <row r="570" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I570" s="1">
         <v>79018771858616</v>
       </c>
     </row>
-    <row r="571" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A571" s="1">
+    <row r="571" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I571" s="1">
         <v>435270971367024</v>
       </c>
     </row>
-    <row r="572" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A572" s="1">
+    <row r="572" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I572" s="1">
         <v>777427144833852</v>
       </c>
     </row>
-    <row r="573" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A573" s="1" t="s">
+    <row r="573" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I573" s="1" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="574" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A574" s="1" t="s">
+    <row r="574" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I574" s="1" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="575" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A575" s="1" t="s">
+    <row r="575" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I575" s="1" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="577" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A577" s="1">
-        <v>8244401142220</v>
-      </c>
+    <row r="577" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B577" s="1" t="s">
         <v>265</v>
       </c>
@@ -5470,29 +5465,29 @@
       <c r="E577" s="1" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="578" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A578" s="1">
+      <c r="I577" s="1">
+        <v>8244401142220</v>
+      </c>
+    </row>
+    <row r="578" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I578" s="1">
         <v>79122903499256</v>
       </c>
     </row>
-    <row r="579" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A579" s="1">
-        <v>465514489030346</v>
-      </c>
+    <row r="579" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B579" s="1" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="580" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A580" s="1">
+      <c r="I579" s="1">
+        <v>465514489030346</v>
+      </c>
+    </row>
+    <row r="580" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I580" s="1">
         <v>777427186380345</v>
       </c>
     </row>
-    <row r="582" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A582" s="1">
-        <v>465496611398797</v>
-      </c>
+    <row r="582" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B582" s="1" t="s">
         <v>266</v>
       </c>
@@ -5505,101 +5500,101 @@
       <c r="E582" s="1" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="583" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A583" s="1">
+      <c r="I582" s="1">
+        <v>465496611398797</v>
+      </c>
+    </row>
+    <row r="583" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I583" s="1">
         <v>777426896912398</v>
       </c>
     </row>
-    <row r="585" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A585" s="1" t="s">
+    <row r="585" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I585" s="1" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="586" spans="1:5" ht="102.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A586" s="1" t="s">
+    <row r="586" spans="2:9" ht="102.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I586" s="1" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="587" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A587" s="1" t="s">
+    <row r="587" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I587" s="1" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="588" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A588" s="1" t="s">
+    <row r="588" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I588" s="1" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="589" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A589" s="1">
+    <row r="589" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I589" s="1">
         <v>465508782347677</v>
       </c>
     </row>
-    <row r="590" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A590" s="1">
+    <row r="590" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I590" s="1">
         <v>465506538373629</v>
       </c>
     </row>
-    <row r="591" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A591" s="1">
+    <row r="591" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I591" s="1">
         <v>465506506662766</v>
       </c>
     </row>
-    <row r="592" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A592" s="1" t="s">
+    <row r="592" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I592" s="1" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="593" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A593" s="1">
+    <row r="593" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I593" s="1">
         <v>465507914083094</v>
       </c>
     </row>
-    <row r="594" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A594" s="1" t="s">
+    <row r="594" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I594" s="1" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="595" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A595" s="1">
+    <row r="595" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I595" s="1">
         <v>465508083387532</v>
       </c>
     </row>
-    <row r="596" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A596" s="1" t="s">
+    <row r="596" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I596" s="1" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="597" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A597" s="1" t="s">
+    <row r="597" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I597" s="1" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="598" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A598" s="1">
+    <row r="598" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I598" s="1">
         <v>79122258818446</v>
       </c>
     </row>
-    <row r="599" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A599" s="1">
+    <row r="599" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I599" s="1">
         <v>79122143971445</v>
       </c>
     </row>
-    <row r="600" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A600" s="1">
+    <row r="600" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I600" s="1">
         <v>777427087637042</v>
       </c>
     </row>
-    <row r="601" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A601" s="1" t="s">
+    <row r="601" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I601" s="1" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="603" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A603" s="1">
-        <v>465509754781473</v>
-      </c>
+    <row r="603" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B603" s="1" t="s">
         <v>107</v>
       </c>
@@ -5609,42 +5604,42 @@
       <c r="D603" s="1">
         <v>18.399999999999999</v>
       </c>
-    </row>
-    <row r="604" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A604" s="1">
+      <c r="I603" s="1">
+        <v>465509754781473</v>
+      </c>
+    </row>
+    <row r="604" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I604" s="1">
         <v>9818049060949</v>
       </c>
     </row>
-    <row r="606" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A606" s="1">
-        <v>9817995428423</v>
-      </c>
+    <row r="606" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B606" s="1" t="s">
         <v>276</v>
       </c>
       <c r="C606" s="1" t="s">
         <v>277</v>
       </c>
-    </row>
-    <row r="607" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A607" s="1">
+      <c r="I606" s="1">
+        <v>9817995428423</v>
+      </c>
+    </row>
+    <row r="607" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I607" s="1">
         <v>465507254476899</v>
       </c>
     </row>
-    <row r="608" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A608" s="1">
+    <row r="608" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I608" s="1">
         <v>777426918928394</v>
       </c>
     </row>
-    <row r="609" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A609" s="1" t="s">
+    <row r="609" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I609" s="1" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="611" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A611" s="1" t="s">
-        <v>280</v>
-      </c>
+    <row r="611" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B611" s="1" t="s">
         <v>279</v>
       </c>
@@ -5657,51 +5652,51 @@
       <c r="E611" s="1" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="612" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A612" s="1">
-        <v>9817997645724</v>
-      </c>
+      <c r="I611" s="1" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="612" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B612" s="1">
         <v>465506370218522</v>
       </c>
       <c r="D612" s="1">
         <v>156</v>
       </c>
-    </row>
-    <row r="613" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A613" s="1" t="s">
-        <v>281</v>
-      </c>
+      <c r="I612" s="1">
+        <v>9817997645724</v>
+      </c>
+    </row>
+    <row r="613" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B613" s="1">
         <v>79122191195930</v>
       </c>
-    </row>
-    <row r="614" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A614" s="1">
-        <v>777427085931458</v>
-      </c>
+      <c r="I613" s="1" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="614" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B614" s="1">
         <v>9817997645724</v>
       </c>
-    </row>
-    <row r="615" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A615" s="1">
-        <v>79122191195930</v>
-      </c>
+      <c r="I614" s="1">
+        <v>777427085931458</v>
+      </c>
+    </row>
+    <row r="615" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B615" s="1" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="616" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A616" s="1">
+      <c r="I615" s="1">
+        <v>79122191195930</v>
+      </c>
+    </row>
+    <row r="616" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I616" s="1">
         <v>465506921261332</v>
       </c>
     </row>
-    <row r="618" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A618" s="1">
-        <v>465514633151567</v>
-      </c>
+    <row r="618" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B618" s="1" t="s">
         <v>111</v>
       </c>
@@ -5714,31 +5709,31 @@
       <c r="E618" s="1" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="619" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A619" s="1">
+      <c r="I618" s="1">
+        <v>465514633151567</v>
+      </c>
+    </row>
+    <row r="619" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I619" s="1">
         <v>465509132293841</v>
       </c>
     </row>
-    <row r="620" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A620" s="1">
+    <row r="620" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I620" s="1">
         <v>79122498404692</v>
       </c>
     </row>
-    <row r="621" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A621" s="1" t="s">
+    <row r="621" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I621" s="1" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="622" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="622" spans="2:9" x14ac:dyDescent="0.3">
       <c r="D622" s="1" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="623" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A623" s="1">
-        <v>465500863123295</v>
-      </c>
+    <row r="623" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B623" s="1" t="s">
         <v>283</v>
       </c>
@@ -5751,16 +5746,16 @@
       <c r="E623" s="1" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="624" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A624" s="1">
+      <c r="I623" s="1">
+        <v>465500863123295</v>
+      </c>
+    </row>
+    <row r="624" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I624" s="1">
         <v>465502961247710</v>
       </c>
     </row>
-    <row r="626" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A626" s="1">
-        <v>9817961258666</v>
-      </c>
+    <row r="626" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B626" s="1" t="s">
         <v>285</v>
       </c>
@@ -5773,31 +5768,31 @@
       <c r="E626" s="1" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="627" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A627" s="1" t="s">
+      <c r="I626" s="1">
+        <v>9817961258666</v>
+      </c>
+    </row>
+    <row r="627" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I627" s="1" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="628" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A628" s="1">
+    <row r="628" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I628" s="1">
         <v>465502154312880</v>
       </c>
     </row>
-    <row r="629" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A629" s="1" t="s">
+    <row r="629" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I629" s="1" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="630" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A630" s="1">
+    <row r="630" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I630" s="1">
         <v>777426672106640</v>
       </c>
     </row>
-    <row r="632" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A632" s="1">
-        <v>9818058273226</v>
-      </c>
+    <row r="632" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B632" s="1" t="s">
         <v>288</v>
       </c>
@@ -5810,11 +5805,11 @@
       <c r="E632" s="1" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="634" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A634" s="1" t="s">
-        <v>290</v>
-      </c>
+      <c r="I632" s="1">
+        <v>9818058273226</v>
+      </c>
+    </row>
+    <row r="634" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B634" s="1" t="s">
         <v>289</v>
       </c>
@@ -5827,16 +5822,16 @@
       <c r="E634" s="1" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="635" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A635" s="1" t="s">
+      <c r="I634" s="1" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="635" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I635" s="1" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="637" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A637" s="1">
-        <v>79122239505024</v>
-      </c>
+    <row r="637" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B637" s="1" t="s">
         <v>292</v>
       </c>
@@ -5849,16 +5844,16 @@
       <c r="E637" s="1" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="638" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A638" s="1" t="s">
+      <c r="I637" s="1">
+        <v>79122239505024</v>
+      </c>
+    </row>
+    <row r="638" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I638" s="1" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="640" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A640" s="1" t="s">
-        <v>294</v>
-      </c>
+    <row r="640" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B640" s="1" t="s">
         <v>192</v>
       </c>
@@ -5871,11 +5866,11 @@
       <c r="E640" s="1" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="642" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A642" s="1" t="s">
-        <v>296</v>
-      </c>
+      <c r="I640" s="1" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="642" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B642" s="1" t="s">
         <v>295</v>
       </c>
@@ -5888,11 +5883,11 @@
       <c r="E642" s="1" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="644" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A644" s="1">
-        <v>465499311973338</v>
-      </c>
+      <c r="I642" s="1" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="644" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B644" s="1" t="s">
         <v>297</v>
       </c>
@@ -5905,11 +5900,11 @@
       <c r="E644" s="1" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="646" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A646" s="1">
-        <v>79122539705596</v>
-      </c>
+      <c r="I644" s="1">
+        <v>465499311973338</v>
+      </c>
+    </row>
+    <row r="646" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B646" s="1" t="s">
         <v>35</v>
       </c>
@@ -5922,8 +5917,11 @@
       <c r="E646" s="1" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="647" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="I646" s="1">
+        <v>79122539705596</v>
+      </c>
+    </row>
+    <row r="647" spans="2:9" x14ac:dyDescent="0.3">
       <c r="E647" s="1" t="s">
         <v>85</v>
       </c>
